--- a/To Add v2/00 Things To Add.xlsx
+++ b/To Add v2/00 Things To Add.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Danakil_KiCad_DB\To Add v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16277CF7-01D1-4491-9EAA-BD8E9F0B8096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C435369-D01B-40A3-A6E6-F83F7D3A8EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="219">
   <si>
     <t>Table Name</t>
   </si>
@@ -721,7 +721,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -849,7 +849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -924,41 +924,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1070,22 +1040,22 @@
   </sortState>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{24CA07BC-B564-425C-A1C9-824F8759E630}" name="Table Name"/>
-    <tableColumn id="2" xr3:uid="{9F4A02A6-F5DB-4F3A-A421-70A80F651F79}" name="Part 1" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{9F4A02A6-F5DB-4F3A-A421-70A80F651F79}" name="Part 1" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{00BD6BA4-1F12-4724-AE31-3694BB4C53B5}" name="Part 2"/>
     <tableColumn id="4" xr3:uid="{1CAAE1E4-7D4D-47D1-8B9A-27C7679E6199}" name="Part 3"/>
     <tableColumn id="5" xr3:uid="{037D0EDD-3927-40D7-AFD5-1044A7CAD438}" name="Part 4"/>
     <tableColumn id="6" xr3:uid="{48D64EC1-0CF4-4E4E-A6D0-E999EC133A13}" name="Part 5"/>
     <tableColumn id="7" xr3:uid="{DD2BE2A2-2EB3-44FA-8623-456D01EA63F6}" name="Part 6"/>
     <tableColumn id="8" xr3:uid="{40DC5E7D-06D0-4B47-8AE6-2C5D8310EC72}" name="Part 7"/>
-    <tableColumn id="9" xr3:uid="{FC0664F5-2F12-48A0-AAC9-0BCA6842B8AC}" name="Spreadsheet" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{FC0664F5-2F12-48A0-AAC9-0BCA6842B8AC}" name="Spreadsheet" dataDxfId="8"/>
     <tableColumn id="10" xr3:uid="{0317F941-13E4-4D2B-BEEE-7C26C454AD40}" name="SQL Database"/>
     <tableColumn id="11" xr3:uid="{8162CF8B-28D2-4781-897D-4EAD7F56A2E8}" name=".kicad_dbl"/>
-    <tableColumn id="28" xr3:uid="{71D029E6-3725-4F01-AFCF-D6BA4C6D42C1}" name="Spreadsheet " dataDxfId="11"/>
+    <tableColumn id="28" xr3:uid="{71D029E6-3725-4F01-AFCF-D6BA4C6D42C1}" name="Spreadsheet " dataDxfId="7"/>
     <tableColumn id="12" xr3:uid="{431C6373-8E7D-4666-BDE1-467A0F9E453B}" name="Symbol Library"/>
     <tableColumn id="13" xr3:uid="{2DA1FDCD-CF72-45A1-B1B4-6EF51DFD8E52}" name="Footprint Library"/>
     <tableColumn id="17" xr3:uid="{78B76DFF-BD9A-4D3C-AABA-D1B79F14BCCA}" name="Functionality Verified?"/>
     <tableColumn id="15" xr3:uid="{D1E24C39-AA98-4732-9662-847B76D8D595}" name="Priority"/>
-    <tableColumn id="16" xr3:uid="{FF2332B8-8FC6-47C4-8923-30A2E08CE14A}" name="Completion (%)" dataDxfId="10">
+    <tableColumn id="16" xr3:uid="{FF2332B8-8FC6-47C4-8923-30A2E08CE14A}" name="Completion (%)" dataDxfId="6">
       <calculatedColumnFormula>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{58412161-1BDA-44F7-B739-C52F8C666368}" name="Eff pt 1">
@@ -1378,7 +1348,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AE152"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="14.08984375" customWidth="1"/>
     <col min="4" max="4" width="27.54296875" style="9" bestFit="1" customWidth="1"/>
@@ -1403,17 +1373,17 @@
     <col min="32" max="32" width="12.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:31">
       <c r="I1"/>
       <c r="P1"/>
       <c r="S1"/>
     </row>
-    <row r="2" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:31">
       <c r="I2"/>
       <c r="P2"/>
       <c r="S2"/>
     </row>
-    <row r="3" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:31">
       <c r="B3" s="17" t="s">
         <v>48</v>
       </c>
@@ -1431,7 +1401,7 @@
       <c r="P3"/>
       <c r="S3"/>
     </row>
-    <row r="4" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:31">
       <c r="B4" s="18"/>
       <c r="C4" s="25"/>
       <c r="D4" s="9" t="s">
@@ -1445,7 +1415,7 @@
       <c r="P4"/>
       <c r="S4"/>
     </row>
-    <row r="5" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:31">
       <c r="B5" s="18"/>
       <c r="C5" s="25"/>
       <c r="D5" s="9" t="s">
@@ -1461,23 +1431,23 @@
       <c r="I5"/>
       <c r="P5" s="8">
         <f t="shared" ref="P5:V5" si="0">100*COUNTIF(P12:P9999,"=TRUE")/COUNTA(P12:P9999)</f>
-        <v>37.588652482269502</v>
+        <v>38.297872340425535</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="0"/>
-        <v>37.588652482269502</v>
+        <v>38.297872340425535</v>
       </c>
       <c r="R5" s="8">
         <f t="shared" si="0"/>
-        <v>37.588652482269502</v>
+        <v>38.297872340425535</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="0"/>
-        <v>41.134751773049643</v>
+        <v>41.843971631205676</v>
       </c>
       <c r="T5" s="8">
         <f t="shared" si="0"/>
-        <v>45.390070921985817</v>
+        <v>46.099290780141843</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" si="0"/>
@@ -1488,7 +1458,7 @@
         <v>28.368794326241133</v>
       </c>
     </row>
-    <row r="6" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:31">
       <c r="B6" s="18"/>
       <c r="C6" s="25"/>
       <c r="D6" s="9" t="s">
@@ -1502,10 +1472,10 @@
       <c r="P6"/>
       <c r="S6">
         <f>COUNTIF(S12:S9999,"=TRUE")</f>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="2:31" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="2:31">
       <c r="B7" s="18"/>
       <c r="C7" s="26"/>
       <c r="D7" s="11" t="s">
@@ -1513,13 +1483,13 @@
       </c>
       <c r="E7" s="15">
         <f>(COUNTIF(P12:V10039,"=TRUE")/COUNTA(P12:V10039))*100</f>
-        <v>42.046605876393109</v>
+        <v>42.553191489361701</v>
       </c>
       <c r="I7"/>
       <c r="P7"/>
       <c r="S7"/>
     </row>
-    <row r="8" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:31">
       <c r="B8" s="18"/>
       <c r="C8" s="27" t="s">
         <v>144</v>
@@ -1529,7 +1499,7 @@
       </c>
       <c r="E8" s="13">
         <f>P5</f>
-        <v>37.588652482269502</v>
+        <v>38.297872340425535</v>
       </c>
       <c r="I8"/>
       <c r="P8"/>
@@ -1538,7 +1508,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:31">
       <c r="B9" s="18"/>
       <c r="C9" s="28"/>
       <c r="D9" s="9" t="s">
@@ -1546,7 +1516,7 @@
       </c>
       <c r="E9" s="14">
         <f>Q5</f>
-        <v>37.588652482269502</v>
+        <v>38.297872340425535</v>
       </c>
       <c r="I9"/>
       <c r="P9"/>
@@ -1563,7 +1533,7 @@
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
     </row>
-    <row r="10" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:31">
       <c r="B10" s="18"/>
       <c r="C10" s="29"/>
       <c r="D10" s="11" t="s">
@@ -1571,7 +1541,7 @@
       </c>
       <c r="E10" s="15">
         <f>R5</f>
-        <v>37.588652482269502</v>
+        <v>38.297872340425535</v>
       </c>
       <c r="I10" s="19" t="s">
         <v>8</v>
@@ -1604,7 +1574,7 @@
       <c r="AD10" s="21"/>
       <c r="AE10" s="21"/>
     </row>
-    <row r="11" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:31">
       <c r="B11" s="18"/>
       <c r="C11" s="24" t="s">
         <v>13</v>
@@ -1614,7 +1584,7 @@
       </c>
       <c r="E11" s="13">
         <f>S5</f>
-        <v>41.134751773049643</v>
+        <v>41.843971631205676</v>
       </c>
       <c r="H11" t="s">
         <v>0</v>
@@ -1689,7 +1659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:31">
       <c r="B12" s="18"/>
       <c r="C12" s="25"/>
       <c r="D12" s="9" t="s">
@@ -1697,7 +1667,7 @@
       </c>
       <c r="E12" s="14">
         <f>T5</f>
-        <v>45.390070921985817</v>
+        <v>46.099290780141843</v>
       </c>
       <c r="H12" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
@@ -1772,7 +1742,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:31">
       <c r="B13" s="18"/>
       <c r="C13" s="26"/>
       <c r="D13" s="11" t="s">
@@ -1810,8 +1780,8 @@
       <c r="U13" t="b">
         <v>1</v>
       </c>
-      <c r="V13" t="b">
-        <v>0</v>
+      <c r="V13" t="s">
+        <v>184</v>
       </c>
       <c r="W13">
         <v>3</v>
@@ -1849,7 +1819,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:31">
       <c r="B14" s="18"/>
       <c r="C14" s="24" t="s">
         <v>16</v>
@@ -1931,7 +1901,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:31">
       <c r="B15" s="18"/>
       <c r="C15" s="25"/>
       <c r="D15" s="16" t="s">
@@ -2011,14 +1981,14 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="2:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:31">
       <c r="C16" s="25"/>
       <c r="D16" s="9" t="s">
         <v>148</v>
       </c>
       <c r="E16" s="14" cm="1">
         <f t="array" ref="E16">SUM(IF(W12:W9999 &gt; 0,X12:X9999,0))/COUNTIF(W12:W9999,"&gt;0")</f>
-        <v>41.269841269841265</v>
+        <v>49.206349206349202</v>
       </c>
       <c r="H16" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
@@ -2090,7 +2060,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:31">
       <c r="C17" s="25"/>
       <c r="D17" s="9" t="s">
         <v>150</v>
@@ -2110,32 +2080,32 @@
         <v>98</v>
       </c>
       <c r="P17" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="b">
         <v>1</v>
       </c>
-      <c r="V17" t="b">
-        <v>0</v>
+      <c r="V17" t="s">
+        <v>184</v>
       </c>
       <c r="W17">
         <v>2</v>
       </c>
       <c r="X17" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -2166,7 +2136,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:31">
       <c r="D18" s="9" t="s">
         <v>178</v>
       </c>
@@ -2247,7 +2217,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:31">
       <c r="H19" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Isolators - Optoisolator</v>
@@ -2315,7 +2285,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:31">
       <c r="H20" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Sensors - Temperature - Digital</v>
@@ -2386,7 +2356,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:31">
       <c r="H21" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Capacitors - Polarized</v>
@@ -2454,7 +2424,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:31">
       <c r="H22" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - ICs - DDS</v>
@@ -2525,7 +2495,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:31">
       <c r="H23" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - Fixed - Ceramic Resonator</v>
@@ -2599,7 +2569,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:31">
       <c r="H24" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - Fixed - TCXO</v>
@@ -2673,7 +2643,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:31">
       <c r="H25" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - VCOs - VCO</v>
@@ -2681,7 +2651,7 @@
       <c r="I25" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="J25" s="30" t="s">
+      <c r="J25" t="s">
         <v>124</v>
       </c>
       <c r="K25" t="s">
@@ -2747,7 +2717,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:31">
       <c r="H26" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - VCOs - VCTCXO</v>
@@ -2776,10 +2746,10 @@
       <c r="S26" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T26" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U26" s="30" t="b">
+      <c r="T26" t="b">
+        <v>1</v>
+      </c>
+      <c r="U26" t="b">
         <v>0</v>
       </c>
       <c r="V26" t="b">
@@ -2821,7 +2791,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:31">
       <c r="H27" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - VCOs - VCXO</v>
@@ -2895,7 +2865,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:31">
       <c r="H28" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Banana Jacks</v>
@@ -2963,7 +2933,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:31">
       <c r="H29" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Battery Holders - Coin Cell</v>
@@ -3034,7 +3004,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:31">
       <c r="H30" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Battery Holders - Cylindrical</v>
@@ -3105,7 +3075,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:31">
       <c r="H31" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Card Edge</v>
@@ -3173,7 +3143,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:31">
       <c r="H32" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Coaxial</v>
@@ -3241,7 +3211,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="33" spans="8:31">
       <c r="H33" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Backshells</v>
@@ -3312,7 +3282,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="34" spans="8:31">
       <c r="H34" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Hybrid - Female - Inline</v>
@@ -3389,7 +3359,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="35" spans="8:31">
       <c r="H35" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Hybrid - Male - Inline</v>
@@ -3466,7 +3436,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="36" spans="8:31">
       <c r="H36" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Standard - Female - Inline</v>
@@ -3543,7 +3513,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="37" spans="8:31">
       <c r="H37" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Standard - Female - PCB Mount</v>
@@ -3620,7 +3590,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="38" spans="8:31">
       <c r="H38" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Standard - Male - Inline</v>
@@ -3697,7 +3667,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="39" spans="8:31">
       <c r="H39" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Standard - Male - PCB Mount</v>
@@ -3774,7 +3744,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="40" spans="8:31">
       <c r="H40" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Flat Flex</v>
@@ -3842,7 +3812,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="41" spans="8:31">
       <c r="H41" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Jumpers</v>
@@ -3910,7 +3880,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="42" spans="8:31">
       <c r="H42" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Power Entry Modules</v>
@@ -3978,7 +3948,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="43" spans="8:31">
       <c r="H43" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Screw Connectors</v>
@@ -4046,7 +4016,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="44" spans="8:31">
       <c r="H44" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - SD Card Socket</v>
@@ -4114,7 +4084,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="45" spans="8:31">
       <c r="H45" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Terminal Blocks - Wire to Board</v>
@@ -4185,7 +4155,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="46" spans="8:31">
       <c r="H46" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Contacts - Banana Plugs</v>
@@ -4253,7 +4223,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="47" spans="8:31">
       <c r="H47" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Contacts - Ferrules</v>
@@ -4321,7 +4291,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="48" spans="8:31">
       <c r="H48" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Contacts - Ring Terminals</v>
@@ -4389,7 +4359,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="49" spans="8:31">
       <c r="H49" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Diodes - Standard</v>
@@ -4460,7 +4430,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="50" spans="8:31">
       <c r="H50" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Transistors - BJT - PNP</v>
@@ -4534,7 +4504,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="51" spans="8:31">
       <c r="H51" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Transistors - GaNFET</v>
@@ -4605,7 +4575,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="52" spans="8:31">
       <c r="H52" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Transistors - JFET</v>
@@ -4676,7 +4646,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="53" spans="8:31">
       <c r="H53" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Transistors - MOSFET</v>
@@ -4747,7 +4717,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="54" spans="8:31">
       <c r="H54" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Transistors - SiCFET</v>
@@ -4818,7 +4788,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="55" spans="8:31">
       <c r="H55" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Analog - Comparator</v>
@@ -4889,7 +4859,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="56" spans="8:31">
       <c r="H56" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Analog - DAC</v>
@@ -4960,7 +4930,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="57" spans="8:31">
       <c r="H57" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Embedded - FPGA</v>
@@ -5031,7 +5001,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="58" spans="8:31">
       <c r="H58" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Embedded - PolarFire - SOC</v>
@@ -5105,7 +5075,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="59" spans="8:31">
       <c r="H59" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Interface  - Analog Switch</v>
@@ -5176,7 +5146,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="60" spans="8:31">
       <c r="H60" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Interface  - Controller</v>
@@ -5247,7 +5217,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="61" spans="8:31">
       <c r="H61" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Interface  - Deserializer</v>
@@ -5318,7 +5288,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="62" spans="8:31">
       <c r="H62" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Interface  - Drivers</v>
@@ -5389,7 +5359,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="63" spans="8:31">
       <c r="H63" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Interface  - IO Expander</v>
@@ -5460,7 +5430,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="64" spans="8:31">
       <c r="H64" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Interface  - Recievers</v>
@@ -5531,7 +5501,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="65" spans="8:31">
       <c r="H65" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Interface  - Serializer</v>
@@ -5602,7 +5572,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="66" spans="8:31">
       <c r="H66" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Interface  - Trancievers</v>
@@ -5673,7 +5643,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="67" spans="8:31">
       <c r="H67" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Interface  - UART</v>
@@ -5744,7 +5714,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="68" spans="8:31">
       <c r="H68" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Comparator - Digital</v>
@@ -5818,7 +5788,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="69" spans="8:31">
       <c r="H69" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Counter - Up</v>
@@ -5892,7 +5862,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="70" spans="8:31">
       <c r="H70" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Counter - Up&amp;Down</v>
@@ -5966,7 +5936,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="71" spans="8:31">
       <c r="H71" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Demultiplexer - Digital</v>
@@ -6040,7 +6010,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="72" spans="8:31">
       <c r="H72" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Flip Flops</v>
@@ -6111,7 +6081,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="73" spans="8:31">
       <c r="H73" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Gates</v>
@@ -6182,7 +6152,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="74" spans="8:31">
       <c r="H74" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Latches</v>
@@ -6253,7 +6223,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="75" spans="8:31">
       <c r="H75" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Level Shifters</v>
@@ -6324,7 +6294,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="76" spans="8:31">
       <c r="H76" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Multiplexer - Digital</v>
@@ -6398,7 +6368,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="77" spans="8:31">
       <c r="H77" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Multivibrators</v>
@@ -6469,7 +6439,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="78" spans="8:31">
       <c r="H78" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Shift Registers - PISO</v>
@@ -6543,7 +6513,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="79" spans="8:31">
       <c r="H79" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Shift Registers - SIPO</v>
@@ -6617,7 +6587,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="80" spans="8:31">
       <c r="H80" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Switch - Digital</v>
@@ -6691,7 +6661,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="81" spans="8:31">
       <c r="H81" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Logic - Translators</v>
@@ -6762,7 +6732,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="82" spans="8:31">
       <c r="H82" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Memory - DRAM</v>
@@ -6833,7 +6803,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="83" spans="8:31">
       <c r="H83" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Memory - EEPROM</v>
@@ -6904,7 +6874,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="84" spans="8:31">
       <c r="H84" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Memory - FLASH</v>
@@ -6975,7 +6945,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="85" spans="8:31">
       <c r="H85" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Memory - SD Card</v>
@@ -7046,7 +7016,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="86" spans="8:31">
       <c r="H86" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Power - Gate Driver - Isolated</v>
@@ -7120,7 +7090,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="87" spans="8:31">
       <c r="H87" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Power - Gate Driver - Non Isolated</v>
@@ -7194,7 +7164,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="88" spans="8:31">
       <c r="H88" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Power - Half&amp;H Bridge</v>
@@ -7265,7 +7235,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="89" spans="8:31">
       <c r="H89" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Power - Supply Sequencing</v>
@@ -7336,7 +7306,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="90" spans="8:31">
       <c r="H90" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Power - Switching Controler</v>
@@ -7407,7 +7377,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="91" spans="8:31">
       <c r="H91" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - RTCs</v>
@@ -7475,7 +7445,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="92" spans="8:31">
       <c r="H92" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Inductors - Common Mode Choke</v>
@@ -7543,7 +7513,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="93" spans="8:31">
       <c r="H93" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Isolators - Analog</v>
@@ -7611,7 +7581,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="94" spans="8:31">
       <c r="H94" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>LEDs - RGB</v>
@@ -7679,7 +7649,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="95" spans="8:31">
       <c r="H95" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Heat Shrink</v>
@@ -7747,7 +7717,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="96" spans="8:31">
       <c r="H96" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Nuts</v>
@@ -7815,7 +7785,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="97" spans="8:31">
       <c r="H97" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Spacers</v>
@@ -7883,7 +7853,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="98" spans="8:31">
       <c r="H98" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Standoffs  - F_F</v>
@@ -7954,7 +7924,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="99" spans="8:31">
       <c r="H99" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Standoffs  - M_F</v>
@@ -8025,7 +7995,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="100" spans="8:31">
       <c r="H100" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Protection - PolyFuses</v>
@@ -8093,7 +8063,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="101" spans="8:31">
       <c r="H101" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - Chasis Mount - AC-DC</v>
@@ -8164,7 +8134,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="102" spans="8:31">
       <c r="H102" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - Chasis Mount - DC-DC</v>
@@ -8235,7 +8205,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="103" spans="8:31">
       <c r="H103" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - PCB Mount - AC-DC</v>
@@ -8305,7 +8275,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="104" spans="8:31">
       <c r="H104" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Resistors - Network</v>
@@ -8373,7 +8343,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="105" spans="8:31">
       <c r="H105" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Resistors - Single - Through Hole</v>
@@ -8444,7 +8414,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="106" spans="8:31">
       <c r="H106" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Sensors - Capacitance To Digital</v>
@@ -8512,7 +8482,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="107" spans="8:31">
       <c r="H107" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Sensors - Humidity</v>
@@ -8580,7 +8550,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="108" spans="8:31">
       <c r="H108" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Sensors - Temperature - RTDs</v>
@@ -8651,7 +8621,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="109" spans="8:31">
       <c r="H109" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Sensors - Touch Sensor - Capacitive</v>
@@ -8722,7 +8692,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="110" spans="8:31">
       <c r="H110" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Transformer - Power - Chasis Mount</v>
@@ -8793,7 +8763,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="111" spans="8:31">
       <c r="H111" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Transformer - Power - PCB Mount</v>
@@ -8864,7 +8834,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="112" spans="8:31">
       <c r="H112" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Voltage References - Misc</v>
@@ -8932,7 +8902,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="113" spans="8:31">
       <c r="H113" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Cables - Premade</v>
@@ -9000,7 +8970,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="114" spans="8:31">
       <c r="H114" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Capacitors - Unpolarized</v>
@@ -9068,7 +9038,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="115" spans="8:31">
       <c r="H115" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - ICs - Generators &amp; Synthisizers</v>
@@ -9139,7 +9109,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="116" spans="8:31">
       <c r="H116" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - Fixed - XO</v>
@@ -9213,7 +9183,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="117" spans="8:31">
       <c r="H117" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Barrel Jack</v>
@@ -9281,7 +9251,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="118" spans="8:31">
       <c r="H118" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - IC socket</v>
@@ -9349,7 +9319,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="119" spans="8:31">
       <c r="H119" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Mezzanine</v>
@@ -9417,7 +9387,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="120" spans="8:31">
       <c r="H120" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Pads - SMD</v>
@@ -9488,7 +9458,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="121" spans="8:31">
       <c r="H121" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Pads - Through Hole</v>
@@ -9559,7 +9529,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="122" spans="8:31">
       <c r="H122" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Programming</v>
@@ -9627,7 +9597,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="123" spans="8:31">
       <c r="H123" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Rectangular</v>
@@ -9695,7 +9665,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="124" spans="8:31">
       <c r="H124" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - RJ</v>
@@ -9763,7 +9733,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="125" spans="8:31">
       <c r="H125" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - USB</v>
@@ -9831,7 +9801,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="126" spans="8:31">
       <c r="H126" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Diodes - Schottky</v>
@@ -9902,7 +9872,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="127" spans="8:31">
       <c r="H127" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Transistors - BJT - NPN</v>
@@ -9976,7 +9946,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="128" spans="8:31">
       <c r="H128" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Analog - OP Amp</v>
@@ -10047,7 +10017,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="129" spans="8:31">
       <c r="H129" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Embedded - MCU</v>
@@ -10118,7 +10088,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="130" spans="8:31">
       <c r="H130" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Embedded - MCU - Module</v>
@@ -10192,7 +10162,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="131" spans="8:31">
       <c r="H131" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Power - Ideal Diodes</v>
@@ -10263,7 +10233,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="132" spans="8:31">
       <c r="H132" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Power - Linear Regulation</v>
@@ -10334,7 +10304,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="133" spans="8:31">
       <c r="H133" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Inductors</v>
@@ -10399,7 +10369,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="134" spans="8:31">
       <c r="H134" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Inductors - Ferrite Bead</v>
@@ -10467,7 +10437,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="135" spans="8:31">
       <c r="H135" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>LEDs - Standard - Indicator - SMD</v>
@@ -10541,7 +10511,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="136" spans="8:31">
       <c r="H136" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>LEDs - Standard - Indicator - Through Hole</v>
@@ -10615,7 +10585,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="137" spans="8:31">
       <c r="H137" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Feet</v>
@@ -10683,7 +10653,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="138" spans="8:31">
       <c r="H138" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Screws</v>
@@ -10751,7 +10721,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="139" spans="8:31">
       <c r="H139" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Protection - Fuses</v>
@@ -10819,7 +10789,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="140" spans="8:31">
       <c r="H140" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Protection - GDT</v>
@@ -10887,7 +10857,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="141" spans="8:31">
       <c r="H141" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Protection - MOVs</v>
@@ -10955,7 +10925,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="142" spans="8:31">
       <c r="H142" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Protection - TVS Diode</v>
@@ -11023,7 +10993,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="143" spans="8:31">
       <c r="H143" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - PCB Mount - DC-DC - Non-Isolated</v>
@@ -11097,7 +11067,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="144" spans="8:31">
       <c r="H144" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - Wall Wart</v>
@@ -11165,7 +11135,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="145" spans="8:31">
       <c r="H145" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Resistors - Isolated Array</v>
@@ -11233,7 +11203,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="146" spans="8:31">
       <c r="H146" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Resistors - Single - SMD</v>
@@ -11304,7 +11274,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="147" spans="8:31">
       <c r="H147" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Switches - Push</v>
@@ -11318,22 +11288,22 @@
       <c r="P147" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q147" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R147" s="30" t="b">
+      <c r="Q147" t="b">
+        <v>1</v>
+      </c>
+      <c r="R147" t="b">
         <v>1</v>
       </c>
       <c r="S147" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T147" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U147" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V147" s="30" t="b">
+      <c r="T147" t="b">
+        <v>1</v>
+      </c>
+      <c r="U147" t="b">
+        <v>1</v>
+      </c>
+      <c r="V147" t="b">
         <v>1</v>
       </c>
       <c r="W147">
@@ -11372,7 +11342,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="148" spans="8:31">
       <c r="H148" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Switches - Slide</v>
@@ -11440,7 +11410,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="149" spans="8:31">
       <c r="H149" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Switches - Tactile</v>
@@ -11508,7 +11478,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="150" spans="8:31">
       <c r="H150" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Thermal - Heat Sinks</v>
@@ -11576,7 +11546,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="151" spans="8:31">
       <c r="H151" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Thermal - Pads</v>
@@ -11644,7 +11614,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="8:31" x14ac:dyDescent="0.35">
+    <row r="152" spans="8:31">
       <c r="H152" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Voltage References - Burried Zener</v>
@@ -11726,31 +11696,31 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E15">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:H152">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>IF($W12 = -1, 1, 0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:O9999">
-    <cfRule type="expression" dxfId="7" priority="36">
+    <cfRule type="expression" dxfId="3" priority="36">
       <formula>IF($W12 &gt;= $E$18, 1, 0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:V152">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="TRALSE">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="TRALSE">
       <formula>NOT(ISERROR(SEARCH("TRALSE",P12)))</formula>
     </cfRule>
     <cfRule type="containsBlanks" priority="5" stopIfTrue="1">
       <formula>LEN(TRIM(P12))=0</formula>
     </cfRule>
-    <cfRule type="notContainsText" dxfId="5" priority="6" operator="notContains" text="TRUE">
+    <cfRule type="notContainsText" dxfId="1" priority="6" operator="notContains" text="TRUE">
       <formula>ISERROR(SEARCH("TRUE",P12))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",P12)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/To Add v2/00 Things To Add.xlsx
+++ b/To Add v2/00 Things To Add.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Danakil_KiCad_DB\To Add v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C435369-D01B-40A3-A6E6-F83F7D3A8EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9258A3C6-27F6-434B-AAEA-308199999A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="222">
   <si>
     <t>Table Name</t>
   </si>
@@ -715,6 +715,15 @@
   </si>
   <si>
     <t>Optoisolator</t>
+  </si>
+  <si>
+    <t>Paste</t>
+  </si>
+  <si>
+    <t>Glue</t>
+  </si>
+  <si>
+    <t>Tape</t>
   </si>
 </sst>
 </file>
@@ -1033,10 +1042,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}" name="Table1" displayName="Table1" ref="H11:AE152" totalsRowShown="0">
-  <autoFilter ref="H11:AE152" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H12:AE152">
-    <sortCondition descending="1" ref="W11:W152"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}" name="Table1" displayName="Table1" ref="H11:AE155" totalsRowShown="0">
+  <autoFilter ref="H11:AE155" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H12:AE155">
+    <sortCondition descending="1" ref="W11:W155"/>
   </sortState>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{24CA07BC-B564-425C-A1C9-824F8759E630}" name="Table Name"/>
@@ -1347,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AE152"/>
+  <dimension ref="B1:AE155"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="14.08984375" customWidth="1"/>
@@ -1360,7 +1369,7 @@
     <col min="13" max="13" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.6328125" style="6" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="15.6328125" style="5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="18.90625" bestFit="1" customWidth="1"/>
@@ -1395,7 +1404,7 @@
       </c>
       <c r="E3" s="13">
         <f>COUNTA(H12:H10039)</f>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I3"/>
       <c r="P3"/>
@@ -1423,7 +1432,7 @@
       </c>
       <c r="E5" s="14">
         <f>COUNTIF(W12:W10040,"&gt;-1")</f>
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G5" t="s">
         <v>49</v>
@@ -1431,23 +1440,23 @@
       <c r="I5"/>
       <c r="P5" s="8">
         <f t="shared" ref="P5:V5" si="0">100*COUNTIF(P12:P9999,"=TRUE")/COUNTA(P12:P9999)</f>
-        <v>38.297872340425535</v>
+        <v>38.888888888888886</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="0"/>
-        <v>38.297872340425535</v>
+        <v>38.888888888888886</v>
       </c>
       <c r="R5" s="8">
         <f t="shared" si="0"/>
-        <v>38.297872340425535</v>
+        <v>38.888888888888886</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="0"/>
-        <v>41.843971631205676</v>
+        <v>43.055555555555557</v>
       </c>
       <c r="T5" s="8">
         <f t="shared" si="0"/>
-        <v>46.099290780141843</v>
+        <v>46.527777777777779</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" si="0"/>
@@ -1455,7 +1464,7 @@
       </c>
       <c r="V5" s="8">
         <f t="shared" si="0"/>
-        <v>28.368794326241133</v>
+        <v>27.777777777777779</v>
       </c>
     </row>
     <row r="6" spans="2:31">
@@ -1466,13 +1475,13 @@
       </c>
       <c r="E6" s="14">
         <f>COUNTIF(X12:X10038,"&gt;0") -E4</f>
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I6"/>
       <c r="P6"/>
       <c r="S6">
         <f>COUNTIF(S12:S9999,"=TRUE")</f>
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="2:31">
@@ -1483,7 +1492,7 @@
       </c>
       <c r="E7" s="15">
         <f>(COUNTIF(P12:V10039,"=TRUE")/COUNTA(P12:V10039))*100</f>
-        <v>42.553191489361701</v>
+        <v>42.956349206349202</v>
       </c>
       <c r="I7"/>
       <c r="P7"/>
@@ -1499,7 +1508,7 @@
       </c>
       <c r="E8" s="13">
         <f>P5</f>
-        <v>38.297872340425535</v>
+        <v>38.888888888888886</v>
       </c>
       <c r="I8"/>
       <c r="P8"/>
@@ -1516,7 +1525,7 @@
       </c>
       <c r="E9" s="14">
         <f>Q5</f>
-        <v>38.297872340425535</v>
+        <v>38.888888888888886</v>
       </c>
       <c r="I9"/>
       <c r="P9"/>
@@ -1541,7 +1550,7 @@
       </c>
       <c r="E10" s="15">
         <f>R5</f>
-        <v>38.297872340425535</v>
+        <v>38.888888888888886</v>
       </c>
       <c r="I10" s="19" t="s">
         <v>8</v>
@@ -1584,7 +1593,7 @@
       </c>
       <c r="E11" s="13">
         <f>S5</f>
-        <v>41.843971631205676</v>
+        <v>43.055555555555557</v>
       </c>
       <c r="H11" t="s">
         <v>0</v>
@@ -1667,67 +1676,61 @@
       </c>
       <c r="E12" s="14">
         <f>T5</f>
-        <v>46.099290780141843</v>
+        <v>46.527777777777779</v>
       </c>
       <c r="H12" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - Logic_Out</v>
+        <v>Thermal - Tape</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="J12" t="s">
-        <v>124</v>
-      </c>
-      <c r="K12" t="s">
-        <v>125</v>
-      </c>
-      <c r="L12" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="P12" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="b">
-        <v>1</v>
-      </c>
-      <c r="V12" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X12" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Thermal - </v>
       </c>
       <c r="Z12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v>Tape</v>
       </c>
       <c r="AA12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Fixed - </v>
+        <v/>
       </c>
       <c r="AB12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Logic_Out</v>
+        <v/>
       </c>
       <c r="AC12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -1754,53 +1757,56 @@
       </c>
       <c r="H13" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Test Points</v>
+        <v>Sensors - Temperature - Digital</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>34</v>
+        <v>211</v>
       </c>
       <c r="J13" t="s">
-        <v>190</v>
+        <v>213</v>
+      </c>
+      <c r="K13" t="s">
+        <v>98</v>
       </c>
       <c r="P13" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="b">
-        <v>1</v>
-      </c>
-      <c r="V13" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X13" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Sensors - </v>
       </c>
       <c r="Z13" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Test Points</v>
+        <v xml:space="preserve">Temperature - </v>
       </c>
       <c r="AA13" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AB13" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1829,60 +1835,57 @@
       </c>
       <c r="E14" s="13">
         <f>COUNTIF(W12:W9999,"=0")</f>
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H14" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - ADC</v>
+        <v>Thermal - Paste</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" t="s">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="P14" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="5" t="b">
         <v>1</v>
       </c>
       <c r="T14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="b">
-        <v>1</v>
-      </c>
-      <c r="V14" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X14" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Thermal - </v>
       </c>
       <c r="Z14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v>Paste</v>
       </c>
       <c r="AA14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>ADC</v>
+        <v/>
       </c>
       <c r="AB14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1909,20 +1912,17 @@
       </c>
       <c r="E15" s="14">
         <f>COUNTIF(W12:W9999,"&gt;0")</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H15" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Switching Regulator</v>
+        <v>Thermal - Glue</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="J15" t="s">
-        <v>88</v>
-      </c>
-      <c r="K15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="P15" s="6" t="b">
         <v>0</v>
@@ -1940,29 +1940,29 @@
         <v>0</v>
       </c>
       <c r="U15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="b">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X15" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Thermal - </v>
       </c>
       <c r="Z15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v>Glue</v>
       </c>
       <c r="AA15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Switching Regulator</v>
+        <v/>
       </c>
       <c r="AB15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1988,20 +1988,17 @@
       </c>
       <c r="E16" s="14" cm="1">
         <f t="array" ref="E16">SUM(IF(W12:W9999 &gt; 0,X12:X9999,0))/COUNTIF(W12:W9999,"&gt;0")</f>
-        <v>49.206349206349202</v>
+        <v>3.5714285714285712</v>
       </c>
       <c r="H16" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Standoffs  - SMD</v>
+        <v>Inductors - Common Mode Choke</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="J16" t="s">
-        <v>134</v>
-      </c>
-      <c r="K16" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="P16" s="6" t="b">
         <v>1</v>
@@ -2025,7 +2022,7 @@
         <v>184</v>
       </c>
       <c r="W16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X16" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
@@ -2033,15 +2030,15 @@
       </c>
       <c r="Y16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Inductors - </v>
       </c>
       <c r="Z16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standoffs  - </v>
+        <v>Common Mode Choke</v>
       </c>
       <c r="AA16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SMD</v>
+        <v/>
       </c>
       <c r="AB16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2067,17 +2064,23 @@
       </c>
       <c r="E17" s="14" cm="1">
         <f t="array" ref="E17">SUM(IF(W12:W9999 =E18,X12:X9999,0))/SUM(IF(W12:W9997 =E18,1,0))</f>
-        <v>67.857142857142847</v>
+        <v>0</v>
       </c>
       <c r="H17" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Isolators - Digital</v>
+        <v>PSUs - PCB Mount - DC-DC - Isolated</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s">
-        <v>98</v>
+        <v>69</v>
+      </c>
+      <c r="K17" t="s">
+        <v>83</v>
+      </c>
+      <c r="L17" t="s">
+        <v>84</v>
       </c>
       <c r="P17" s="6" t="b">
         <v>1</v>
@@ -2101,7 +2104,7 @@
         <v>184</v>
       </c>
       <c r="W17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
@@ -2109,19 +2112,19 @@
       </c>
       <c r="Y17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Isolators - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Digital</v>
+        <v xml:space="preserve">PCB Mount - </v>
       </c>
       <c r="AA17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">DC-DC - </v>
       </c>
       <c r="AB17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Isolated</v>
       </c>
       <c r="AC17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2142,67 +2145,64 @@
       </c>
       <c r="E18">
         <f>MAX(Table1[Priority])</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - PCB Mount - DC-DC - Isolated</v>
+        <v>ICs - Analog - ADC</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="J18" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="K18" t="s">
-        <v>83</v>
-      </c>
-      <c r="L18" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="P18" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="b">
-        <v>0</v>
-      </c>
-      <c r="V18" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V18" t="s">
+        <v>184</v>
       </c>
       <c r="W18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X18" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">PCB Mount - </v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">DC-DC - </v>
+        <v>ADC</v>
       </c>
       <c r="AB18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Isolated</v>
+        <v/>
       </c>
       <c r="AC18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="W19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X19" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
@@ -2288,16 +2288,16 @@
     <row r="20" spans="3:31">
       <c r="H20" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Temperature - Digital</v>
+        <v>ICs - Power - Switching Regulator</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>211</v>
+        <v>100</v>
       </c>
       <c r="J20" t="s">
-        <v>213</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s">
-        <v>98</v>
+        <v>217</v>
       </c>
       <c r="P20" s="6" t="b">
         <v>0</v>
@@ -2315,29 +2315,29 @@
         <v>0</v>
       </c>
       <c r="U20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="b">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Sensors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Temperature - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Digital</v>
+        <v>Switching Regulator</v>
       </c>
       <c r="AB20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2359,13 +2359,19 @@
     <row r="21" spans="3:31">
       <c r="H21" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Capacitors - Polarized</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - Logic_Out</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>27</v>
+        <v>153</v>
       </c>
       <c r="J21" t="s">
-        <v>28</v>
+        <v>124</v>
+      </c>
+      <c r="K21" t="s">
+        <v>125</v>
+      </c>
+      <c r="L21" t="s">
+        <v>206</v>
       </c>
       <c r="P21" s="6" t="b">
         <v>1</v>
@@ -2397,19 +2403,19 @@
       </c>
       <c r="Y21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Capacitors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Polarized</v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Fixed - </v>
       </c>
       <c r="AB21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Logic_Out</v>
       </c>
       <c r="AC21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2427,56 +2433,53 @@
     <row r="22" spans="3:31">
       <c r="H22" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - ICs - DDS</v>
+        <v>Connectors - Test Points</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="J22" t="s">
-        <v>100</v>
-      </c>
-      <c r="K22" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
       <c r="P22" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="b">
         <v>1</v>
       </c>
-      <c r="V22" t="b">
-        <v>0</v>
+      <c r="V22" t="s">
+        <v>184</v>
       </c>
       <c r="W22">
         <v>0</v>
       </c>
       <c r="X22" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y22" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z22" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v>Test Points</v>
       </c>
       <c r="AA22" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DDS</v>
+        <v/>
       </c>
       <c r="AB22" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2498,63 +2501,60 @@
     <row r="23" spans="3:31">
       <c r="H23" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - Ceramic Resonator</v>
+        <v>Mechanical  - Standoffs  - SMD</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="J23" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="K23" t="s">
-        <v>125</v>
-      </c>
-      <c r="L23" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="P23" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="b">
         <v>1</v>
       </c>
       <c r="U23" t="b">
-        <v>0</v>
-      </c>
-      <c r="V23" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V23" t="s">
+        <v>184</v>
       </c>
       <c r="W23">
         <v>0</v>
       </c>
       <c r="X23" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v xml:space="preserve">Standoffs  - </v>
       </c>
       <c r="AA23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Fixed - </v>
+        <v>SMD</v>
       </c>
       <c r="AB23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Ceramic Resonator</v>
+        <v/>
       </c>
       <c r="AC23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2572,63 +2572,57 @@
     <row r="24" spans="3:31">
       <c r="H24" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - TCXO</v>
+        <v>Isolators - Digital</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" t="s">
-        <v>125</v>
-      </c>
-      <c r="L24" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="P24" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="b">
         <v>1</v>
       </c>
       <c r="U24" t="b">
-        <v>0</v>
-      </c>
-      <c r="V24" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
+        <v>184</v>
       </c>
       <c r="W24">
         <v>0</v>
       </c>
       <c r="X24" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Isolators - </v>
       </c>
       <c r="Z24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v>Digital</v>
       </c>
       <c r="AA24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Fixed - </v>
+        <v/>
       </c>
       <c r="AB24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>TCXO</v>
+        <v/>
       </c>
       <c r="AC24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2646,63 +2640,57 @@
     <row r="25" spans="3:31">
       <c r="H25" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - VCOs - VCO</v>
+        <v>Capacitors - Polarized</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="J25" t="s">
-        <v>124</v>
-      </c>
-      <c r="K25" t="s">
-        <v>129</v>
-      </c>
-      <c r="L25" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="P25" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="5" t="b">
         <v>1</v>
       </c>
       <c r="U25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V25" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V25" t="s">
+        <v>184</v>
       </c>
       <c r="W25">
         <v>0</v>
       </c>
       <c r="X25" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Capacitors - </v>
       </c>
       <c r="Z25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v>Polarized</v>
       </c>
       <c r="AA25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">VCOs - </v>
+        <v/>
       </c>
       <c r="AB25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>VCO</v>
+        <v/>
       </c>
       <c r="AC25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2720,19 +2708,16 @@
     <row r="26" spans="3:31">
       <c r="H26" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - VCOs - VCTCXO</v>
+        <v>Clock&amp;Timing - ICs - DDS</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>153</v>
       </c>
       <c r="J26" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="K26" t="s">
-        <v>129</v>
-      </c>
-      <c r="L26" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="P26" s="6" t="b">
         <v>0</v>
@@ -2747,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" t="b">
         <v>0</v>
@@ -2768,15 +2753,15 @@
       </c>
       <c r="Z26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="AA26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">VCOs - </v>
+        <v>DDS</v>
       </c>
       <c r="AB26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>VCTCXO</v>
+        <v/>
       </c>
       <c r="AC26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2794,7 +2779,7 @@
     <row r="27" spans="3:31">
       <c r="H27" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - VCOs - VCXO</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - Ceramic Resonator</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>153</v>
@@ -2803,10 +2788,10 @@
         <v>124</v>
       </c>
       <c r="K27" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L27" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P27" s="6" t="b">
         <v>0</v>
@@ -2846,11 +2831,11 @@
       </c>
       <c r="AA27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">VCOs - </v>
+        <v xml:space="preserve">Fixed - </v>
       </c>
       <c r="AB27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>VCXO</v>
+        <v>Ceramic Resonator</v>
       </c>
       <c r="AC27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2868,13 +2853,19 @@
     <row r="28" spans="3:31">
       <c r="H28" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Banana Jacks</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - TCXO</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="J28" t="s">
-        <v>59</v>
+        <v>124</v>
+      </c>
+      <c r="K28" t="s">
+        <v>125</v>
+      </c>
+      <c r="L28" t="s">
+        <v>127</v>
       </c>
       <c r="P28" s="6" t="b">
         <v>0</v>
@@ -2889,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="b">
         <v>0</v>
@@ -2902,23 +2893,23 @@
       </c>
       <c r="X28" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Banana Jacks</v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Fixed - </v>
       </c>
       <c r="AB28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>TCXO</v>
       </c>
       <c r="AC28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2936,60 +2927,63 @@
     <row r="29" spans="3:31">
       <c r="H29" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Battery Holders - Coin Cell</v>
+        <v>Clock&amp;Timing - Oscillators  - VCOs - VCO</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="J29" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="K29" t="s">
-        <v>208</v>
+        <v>129</v>
+      </c>
+      <c r="L29" t="s">
+        <v>130</v>
       </c>
       <c r="P29" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="b">
         <v>1</v>
       </c>
       <c r="U29" t="b">
-        <v>1</v>
-      </c>
-      <c r="V29" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
       </c>
       <c r="W29">
         <v>0</v>
       </c>
       <c r="X29" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Battery Holders - </v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Coin Cell</v>
+        <v xml:space="preserve">VCOs - </v>
       </c>
       <c r="AB29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>VCO</v>
       </c>
       <c r="AC29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -3007,16 +3001,19 @@
     <row r="30" spans="3:31">
       <c r="H30" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Battery Holders - Cylindrical</v>
+        <v>Clock&amp;Timing - Oscillators  - VCOs - VCTCXO</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="J30" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="K30" t="s">
-        <v>209</v>
+        <v>129</v>
+      </c>
+      <c r="L30" t="s">
+        <v>132</v>
       </c>
       <c r="P30" s="6" t="b">
         <v>0</v>
@@ -3031,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="b">
         <v>0</v>
@@ -3044,23 +3041,23 @@
       </c>
       <c r="X30" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Battery Holders - </v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Cylindrical</v>
+        <v xml:space="preserve">VCOs - </v>
       </c>
       <c r="AB30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>VCTCXO</v>
       </c>
       <c r="AC30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -3078,13 +3075,19 @@
     <row r="31" spans="3:31">
       <c r="H31" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Card Edge</v>
+        <v>Clock&amp;Timing - Oscillators  - VCOs - VCXO</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="J31" t="s">
-        <v>57</v>
+        <v>124</v>
+      </c>
+      <c r="K31" t="s">
+        <v>129</v>
+      </c>
+      <c r="L31" t="s">
+        <v>131</v>
       </c>
       <c r="P31" s="6" t="b">
         <v>0</v>
@@ -3099,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="b">
         <v>0</v>
@@ -3112,23 +3115,23 @@
       </c>
       <c r="X31" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Card Edge</v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">VCOs - </v>
       </c>
       <c r="AB31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>VCXO</v>
       </c>
       <c r="AC31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -3146,31 +3149,31 @@
     <row r="32" spans="3:31">
       <c r="H32" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Coaxial</v>
+        <v>Connectors - Banana Jacks</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P32" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="b">
         <v>0</v>
@@ -3180,7 +3183,7 @@
       </c>
       <c r="X32" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -3188,7 +3191,7 @@
       </c>
       <c r="Z32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Coaxial</v>
+        <v>Banana Jacks</v>
       </c>
       <c r="AA32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3214,44 +3217,44 @@
     <row r="33" spans="8:31">
       <c r="H33" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Backshells</v>
+        <v>Connectors - Battery Holders - Coin Cell</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J33" t="s">
-        <v>66</v>
+        <v>207</v>
       </c>
       <c r="K33" t="s">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="P33" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="b">
-        <v>0</v>
-      </c>
-      <c r="V33" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V33" t="s">
+        <v>184</v>
       </c>
       <c r="W33">
         <v>0</v>
       </c>
       <c r="X33" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -3259,11 +3262,11 @@
       </c>
       <c r="Z33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v xml:space="preserve">Battery Holders - </v>
       </c>
       <c r="AA33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Backshells</v>
+        <v>Coin Cell</v>
       </c>
       <c r="AB33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3285,22 +3288,16 @@
     <row r="34" spans="8:31">
       <c r="H34" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Hybrid - Female - Inline</v>
+        <v>Connectors - Battery Holders - Cylindrical</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J34" t="s">
-        <v>66</v>
+        <v>207</v>
       </c>
       <c r="K34" t="s">
-        <v>64</v>
-      </c>
-      <c r="L34" t="s">
-        <v>68</v>
-      </c>
-      <c r="M34" t="s">
-        <v>70</v>
+        <v>209</v>
       </c>
       <c r="P34" s="6" t="b">
         <v>0</v>
@@ -3336,19 +3333,19 @@
       </c>
       <c r="Z34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v xml:space="preserve">Battery Holders - </v>
       </c>
       <c r="AA34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Hybrid - </v>
+        <v>Cylindrical</v>
       </c>
       <c r="AB34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Female - </v>
+        <v/>
       </c>
       <c r="AC34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>Inline</v>
+        <v/>
       </c>
       <c r="AD34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3362,22 +3359,13 @@
     <row r="35" spans="8:31">
       <c r="H35" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Hybrid - Male - Inline</v>
+        <v>Connectors - Card Edge</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J35" t="s">
-        <v>66</v>
-      </c>
-      <c r="K35" t="s">
-        <v>64</v>
-      </c>
-      <c r="L35" t="s">
-        <v>67</v>
-      </c>
-      <c r="M35" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="P35" s="6" t="b">
         <v>0</v>
@@ -3413,19 +3401,19 @@
       </c>
       <c r="Z35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v>Card Edge</v>
       </c>
       <c r="AA35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Hybrid - </v>
+        <v/>
       </c>
       <c r="AB35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Male - </v>
+        <v/>
       </c>
       <c r="AC35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>Inline</v>
+        <v/>
       </c>
       <c r="AD35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3439,40 +3427,31 @@
     <row r="36" spans="8:31">
       <c r="H36" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Female - Inline</v>
+        <v>Connectors - Coaxial</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J36" t="s">
-        <v>66</v>
-      </c>
-      <c r="K36" t="s">
-        <v>63</v>
-      </c>
-      <c r="L36" t="s">
-        <v>68</v>
-      </c>
-      <c r="M36" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="P36" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" t="b">
         <v>0</v>
@@ -3482,7 +3461,7 @@
       </c>
       <c r="X36" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -3490,19 +3469,19 @@
       </c>
       <c r="Z36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v>Coaxial</v>
       </c>
       <c r="AA36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v/>
       </c>
       <c r="AB36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Female - </v>
+        <v/>
       </c>
       <c r="AC36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>Inline</v>
+        <v/>
       </c>
       <c r="AD36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3516,7 +3495,7 @@
     <row r="37" spans="8:31">
       <c r="H37" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Female - PCB Mount</v>
+        <v>Connectors - D-Sub - Backshells</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>34</v>
@@ -3525,13 +3504,7 @@
         <v>66</v>
       </c>
       <c r="K37" t="s">
-        <v>63</v>
-      </c>
-      <c r="L37" t="s">
-        <v>68</v>
-      </c>
-      <c r="M37" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P37" s="6" t="b">
         <v>0</v>
@@ -3571,15 +3544,15 @@
       </c>
       <c r="AA37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v>Backshells</v>
       </c>
       <c r="AB37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Female - </v>
+        <v/>
       </c>
       <c r="AC37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>PCB Mount</v>
+        <v/>
       </c>
       <c r="AD37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3593,7 +3566,7 @@
     <row r="38" spans="8:31">
       <c r="H38" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Male - Inline</v>
+        <v>Connectors - D-Sub - Hybrid - Female - Inline</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>34</v>
@@ -3602,10 +3575,10 @@
         <v>66</v>
       </c>
       <c r="K38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M38" t="s">
         <v>70</v>
@@ -3648,11 +3621,11 @@
       </c>
       <c r="AA38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v xml:space="preserve">Hybrid - </v>
       </c>
       <c r="AB38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Male - </v>
+        <v xml:space="preserve">Female - </v>
       </c>
       <c r="AC38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -3670,7 +3643,7 @@
     <row r="39" spans="8:31">
       <c r="H39" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Male - PCB Mount</v>
+        <v>Connectors - D-Sub - Hybrid - Male - Inline</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>34</v>
@@ -3679,13 +3652,13 @@
         <v>66</v>
       </c>
       <c r="K39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L39" t="s">
         <v>67</v>
       </c>
       <c r="M39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P39" s="6" t="b">
         <v>0</v>
@@ -3725,7 +3698,7 @@
       </c>
       <c r="AA39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v xml:space="preserve">Hybrid - </v>
       </c>
       <c r="AB39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3733,7 +3706,7 @@
       </c>
       <c r="AC39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>PCB Mount</v>
+        <v>Inline</v>
       </c>
       <c r="AD39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3747,13 +3720,22 @@
     <row r="40" spans="8:31">
       <c r="H40" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Flat Flex</v>
+        <v>Connectors - D-Sub - Standard - Female - Inline</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J40" t="s">
-        <v>62</v>
+        <v>66</v>
+      </c>
+      <c r="K40" t="s">
+        <v>63</v>
+      </c>
+      <c r="L40" t="s">
+        <v>68</v>
+      </c>
+      <c r="M40" t="s">
+        <v>70</v>
       </c>
       <c r="P40" s="6" t="b">
         <v>0</v>
@@ -3765,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="b">
         <v>0</v>
@@ -3781,7 +3763,7 @@
       </c>
       <c r="X40" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -3789,19 +3771,19 @@
       </c>
       <c r="Z40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Flat Flex</v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AB40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Female - </v>
       </c>
       <c r="AC40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>Inline</v>
       </c>
       <c r="AD40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3815,13 +3797,22 @@
     <row r="41" spans="8:31">
       <c r="H41" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Jumpers</v>
+        <v>Connectors - D-Sub - Standard - Female - PCB Mount</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J41" t="s">
-        <v>188</v>
+        <v>66</v>
+      </c>
+      <c r="K41" t="s">
+        <v>63</v>
+      </c>
+      <c r="L41" t="s">
+        <v>68</v>
+      </c>
+      <c r="M41" t="s">
+        <v>69</v>
       </c>
       <c r="P41" s="6" t="b">
         <v>0</v>
@@ -3857,19 +3848,19 @@
       </c>
       <c r="Z41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Jumpers</v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AB41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Female - </v>
       </c>
       <c r="AC41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>PCB Mount</v>
       </c>
       <c r="AD41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3883,13 +3874,22 @@
     <row r="42" spans="8:31">
       <c r="H42" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Power Entry Modules</v>
+        <v>Connectors - D-Sub - Standard - Male - Inline</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J42" t="s">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="K42" t="s">
+        <v>63</v>
+      </c>
+      <c r="L42" t="s">
+        <v>67</v>
+      </c>
+      <c r="M42" t="s">
+        <v>70</v>
       </c>
       <c r="P42" s="6" t="b">
         <v>0</v>
@@ -3925,19 +3925,19 @@
       </c>
       <c r="Z42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Power Entry Modules</v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AB42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Male - </v>
       </c>
       <c r="AC42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>Inline</v>
       </c>
       <c r="AD42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3951,13 +3951,22 @@
     <row r="43" spans="8:31">
       <c r="H43" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Screw Connectors</v>
+        <v>Connectors - D-Sub - Standard - Male - PCB Mount</v>
       </c>
       <c r="I43" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J43" t="s">
-        <v>53</v>
+        <v>66</v>
+      </c>
+      <c r="K43" t="s">
+        <v>63</v>
+      </c>
+      <c r="L43" t="s">
+        <v>67</v>
+      </c>
+      <c r="M43" t="s">
+        <v>69</v>
       </c>
       <c r="P43" s="6" t="b">
         <v>0</v>
@@ -3993,19 +4002,19 @@
       </c>
       <c r="Z43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Screw Connectors</v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AB43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Male - </v>
       </c>
       <c r="AC43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>PCB Mount</v>
       </c>
       <c r="AD43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -4019,41 +4028,41 @@
     <row r="44" spans="8:31">
       <c r="H44" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - SD Card Socket</v>
+        <v>Connectors - Flat Flex</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J44" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="P44" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" s="5" t="b">
         <v>1</v>
       </c>
       <c r="T44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U44" t="b">
-        <v>1</v>
-      </c>
-      <c r="V44" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V44" t="b">
+        <v>0</v>
       </c>
       <c r="W44">
         <v>0</v>
       </c>
       <c r="X44" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4061,7 +4070,7 @@
       </c>
       <c r="Z44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>SD Card Socket</v>
+        <v>Flat Flex</v>
       </c>
       <c r="AA44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -4087,44 +4096,41 @@
     <row r="45" spans="8:31">
       <c r="H45" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Terminal Blocks - Wire to Board</v>
+        <v>Connectors - Jumpers</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J45" t="s">
-        <v>61</v>
-      </c>
-      <c r="K45" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="P45" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45" t="b">
-        <v>1</v>
-      </c>
-      <c r="V45" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V45" t="b">
+        <v>0</v>
       </c>
       <c r="W45">
         <v>0</v>
       </c>
       <c r="X45" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4132,11 +4138,11 @@
       </c>
       <c r="Z45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Terminal Blocks - </v>
+        <v>Jumpers</v>
       </c>
       <c r="AA45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Wire to Board</v>
+        <v/>
       </c>
       <c r="AB45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4158,13 +4164,13 @@
     <row r="46" spans="8:31">
       <c r="H46" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Contacts - Banana Plugs</v>
+        <v>Connectors - Power Entry Modules</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="J46" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="P46" s="6" t="b">
         <v>0</v>
@@ -4196,11 +4202,11 @@
       </c>
       <c r="Y46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Contacts - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Banana Plugs</v>
+        <v>Power Entry Modules</v>
       </c>
       <c r="AA46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -4226,13 +4232,13 @@
     <row r="47" spans="8:31">
       <c r="H47" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Contacts - Ferrules</v>
+        <v>Connectors - Screw Connectors</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="J47" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="P47" s="6" t="b">
         <v>0</v>
@@ -4264,11 +4270,11 @@
       </c>
       <c r="Y47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Contacts - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Ferrules</v>
+        <v>Screw Connectors</v>
       </c>
       <c r="AA47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -4294,49 +4300,49 @@
     <row r="48" spans="8:31">
       <c r="H48" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Contacts - Ring Terminals</v>
+        <v>Connectors - SD Card Socket</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="J48" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="P48" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="b">
-        <v>0</v>
-      </c>
-      <c r="V48" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V48" t="s">
+        <v>184</v>
       </c>
       <c r="W48">
         <v>0</v>
       </c>
       <c r="X48" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Contacts - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Ring Terminals</v>
+        <v>SD Card Socket</v>
       </c>
       <c r="AA48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -4362,28 +4368,28 @@
     <row r="49" spans="8:31">
       <c r="H49" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Diodes - Standard</v>
+        <v>Connectors - Terminal Blocks - Wire to Board</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="J49" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="K49" t="s">
-        <v>63</v>
+        <v>216</v>
       </c>
       <c r="P49" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="b">
         <v>1</v>
@@ -4391,27 +4397,27 @@
       <c r="U49" t="b">
         <v>1</v>
       </c>
-      <c r="V49" t="b">
-        <v>0</v>
+      <c r="V49" t="s">
+        <v>184</v>
       </c>
       <c r="W49">
         <v>0</v>
       </c>
       <c r="X49" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Diodes - </v>
+        <v xml:space="preserve">Terminal Blocks - </v>
       </c>
       <c r="AA49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Standard</v>
+        <v>Wire to Board</v>
       </c>
       <c r="AB49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4433,19 +4439,13 @@
     <row r="50" spans="8:31">
       <c r="H50" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - BJT - PNP</v>
+        <v>Contacts - Banana Plugs</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="J50" t="s">
-        <v>195</v>
-      </c>
-      <c r="K50" t="s">
-        <v>92</v>
-      </c>
-      <c r="L50" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="P50" s="6" t="b">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" t="b">
         <v>0</v>
@@ -4473,23 +4473,23 @@
       </c>
       <c r="X50" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">Contacts - </v>
       </c>
       <c r="Z50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v>Banana Plugs</v>
       </c>
       <c r="AA50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">BJT - </v>
+        <v/>
       </c>
       <c r="AB50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>PNP</v>
+        <v/>
       </c>
       <c r="AC50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4507,16 +4507,13 @@
     <row r="51" spans="8:31">
       <c r="H51" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - GaNFET</v>
+        <v>Contacts - Ferrules</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="J51" t="s">
-        <v>195</v>
-      </c>
-      <c r="K51" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="P51" s="6" t="b">
         <v>0</v>
@@ -4531,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="T51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="b">
         <v>0</v>
@@ -4544,19 +4541,19 @@
       </c>
       <c r="X51" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">Contacts - </v>
       </c>
       <c r="Z51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v>Ferrules</v>
       </c>
       <c r="AA51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>GaNFET</v>
+        <v/>
       </c>
       <c r="AB51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4578,16 +4575,13 @@
     <row r="52" spans="8:31">
       <c r="H52" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - JFET</v>
+        <v>Contacts - Ring Terminals</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="J52" t="s">
-        <v>195</v>
-      </c>
-      <c r="K52" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="P52" s="6" t="b">
         <v>0</v>
@@ -4602,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="T52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" t="b">
         <v>0</v>
@@ -4615,19 +4609,19 @@
       </c>
       <c r="X52" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">Contacts - </v>
       </c>
       <c r="Z52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v>Ring Terminals</v>
       </c>
       <c r="AA52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>JFET</v>
+        <v/>
       </c>
       <c r="AB52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4649,28 +4643,28 @@
     <row r="53" spans="8:31">
       <c r="H53" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - MOSFET</v>
+        <v>Discreet - Diodes - Standard</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J53" t="s">
-        <v>195</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="P53" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="b">
         <v>1</v>
@@ -4686,7 +4680,7 @@
       </c>
       <c r="X53" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4694,11 +4688,11 @@
       </c>
       <c r="Z53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v xml:space="preserve">Diodes - </v>
       </c>
       <c r="AA53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>MOSFET</v>
+        <v>Standard</v>
       </c>
       <c r="AB53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4720,7 +4714,7 @@
     <row r="54" spans="8:31">
       <c r="H54" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - SiCFET</v>
+        <v>Discreet - Transistors - BJT - PNP</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>89</v>
@@ -4729,7 +4723,10 @@
         <v>195</v>
       </c>
       <c r="K54" t="s">
-        <v>95</v>
+        <v>92</v>
+      </c>
+      <c r="L54" t="s">
+        <v>202</v>
       </c>
       <c r="P54" s="6" t="b">
         <v>0</v>
@@ -4744,10 +4741,10 @@
         <v>0</v>
       </c>
       <c r="T54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54" t="b">
         <v>0</v>
@@ -4769,11 +4766,11 @@
       </c>
       <c r="AA54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SiCFET</v>
+        <v xml:space="preserve">BJT - </v>
       </c>
       <c r="AB54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>PNP</v>
       </c>
       <c r="AC54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4791,16 +4788,16 @@
     <row r="55" spans="8:31">
       <c r="H55" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - Comparator</v>
+        <v>Discreet - Transistors - GaNFET</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J55" t="s">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="K55" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="P55" s="6" t="b">
         <v>0</v>
@@ -4815,10 +4812,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V55" t="b">
         <v>0</v>
@@ -4832,15 +4829,15 @@
       </c>
       <c r="Y55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Comparator</v>
+        <v>GaNFET</v>
       </c>
       <c r="AB55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4862,16 +4859,16 @@
     <row r="56" spans="8:31">
       <c r="H56" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - DAC</v>
+        <v>Discreet - Transistors - JFET</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J56" t="s">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="K56" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="P56" s="6" t="b">
         <v>0</v>
@@ -4886,10 +4883,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" t="b">
         <v>0</v>
@@ -4903,15 +4900,15 @@
       </c>
       <c r="Y56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DAC</v>
+        <v>JFET</v>
       </c>
       <c r="AB56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4933,31 +4930,31 @@
     <row r="57" spans="8:31">
       <c r="H57" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - FPGA</v>
+        <v>Discreet - Transistors - MOSFET</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J57" t="s">
-        <v>106</v>
+        <v>195</v>
       </c>
       <c r="K57" t="s">
-        <v>108</v>
-      </c>
-      <c r="P57" s="6" t="s">
-        <v>184</v>
+        <v>93</v>
+      </c>
+      <c r="P57" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="Q57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" s="5" t="b">
         <v>1</v>
       </c>
       <c r="T57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U57" t="b">
         <v>1</v>
@@ -4970,19 +4967,19 @@
       </c>
       <c r="X57" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>FPGA</v>
+        <v>MOSFET</v>
       </c>
       <c r="AB57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5004,19 +5001,16 @@
     <row r="58" spans="8:31">
       <c r="H58" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - PolarFire - SOC</v>
+        <v>Discreet - Transistors - SiCFET</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J58" t="s">
-        <v>106</v>
+        <v>195</v>
       </c>
       <c r="K58" t="s">
-        <v>109</v>
-      </c>
-      <c r="L58" t="s">
-        <v>183</v>
+        <v>95</v>
       </c>
       <c r="P58" s="6" t="b">
         <v>0</v>
@@ -5031,10 +5025,10 @@
         <v>0</v>
       </c>
       <c r="T58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V58" t="b">
         <v>0</v>
@@ -5048,19 +5042,19 @@
       </c>
       <c r="Y58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">PolarFire - </v>
+        <v>SiCFET</v>
       </c>
       <c r="AB58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SOC</v>
+        <v/>
       </c>
       <c r="AC58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5078,16 +5072,16 @@
     <row r="59" spans="8:31">
       <c r="H59" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Analog Switch</v>
+        <v>ICs - Analog - Comparator</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J59" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="K59" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="P59" s="6" t="b">
         <v>0</v>
@@ -5123,11 +5117,11 @@
       </c>
       <c r="Z59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Analog Switch</v>
+        <v>Comparator</v>
       </c>
       <c r="AB59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5149,16 +5143,16 @@
     <row r="60" spans="8:31">
       <c r="H60" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Controller</v>
+        <v>ICs - Analog - DAC</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J60" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="K60" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="P60" s="6" t="b">
         <v>0</v>
@@ -5194,11 +5188,11 @@
       </c>
       <c r="Z60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Controller</v>
+        <v>DAC</v>
       </c>
       <c r="AB60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5220,19 +5214,19 @@
     <row r="61" spans="8:31">
       <c r="H61" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Deserializer</v>
+        <v>ICs - Embedded - FPGA</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J61" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="K61" t="s">
-        <v>160</v>
-      </c>
-      <c r="P61" s="6" t="b">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -5241,7 +5235,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="b">
         <v>0</v>
@@ -5257,7 +5251,7 @@
       </c>
       <c r="X61" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -5265,11 +5259,11 @@
       </c>
       <c r="Z61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Embedded - </v>
       </c>
       <c r="AA61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Deserializer</v>
+        <v>FPGA</v>
       </c>
       <c r="AB61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5291,16 +5285,19 @@
     <row r="62" spans="8:31">
       <c r="H62" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Drivers</v>
+        <v>ICs - Embedded - PolarFire - SOC</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J62" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="K62" t="s">
-        <v>120</v>
+        <v>109</v>
+      </c>
+      <c r="L62" t="s">
+        <v>183</v>
       </c>
       <c r="P62" s="6" t="b">
         <v>0</v>
@@ -5336,15 +5333,15 @@
       </c>
       <c r="Z62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Embedded - </v>
       </c>
       <c r="AA62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Drivers</v>
+        <v xml:space="preserve">PolarFire - </v>
       </c>
       <c r="AB62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>SOC</v>
       </c>
       <c r="AC62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5362,7 +5359,7 @@
     <row r="63" spans="8:31">
       <c r="H63" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - IO Expander</v>
+        <v>ICs - Interface  - Analog Switch</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>100</v>
@@ -5371,7 +5368,7 @@
         <v>119</v>
       </c>
       <c r="K63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P63" s="6" t="b">
         <v>0</v>
@@ -5411,7 +5408,7 @@
       </c>
       <c r="AA63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>IO Expander</v>
+        <v>Analog Switch</v>
       </c>
       <c r="AB63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5433,7 +5430,7 @@
     <row r="64" spans="8:31">
       <c r="H64" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Recievers</v>
+        <v>ICs - Interface  - Controller</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>100</v>
@@ -5442,7 +5439,7 @@
         <v>119</v>
       </c>
       <c r="K64" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="P64" s="6" t="b">
         <v>0</v>
@@ -5482,7 +5479,7 @@
       </c>
       <c r="AA64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Recievers</v>
+        <v>Controller</v>
       </c>
       <c r="AB64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5504,7 +5501,7 @@
     <row r="65" spans="8:31">
       <c r="H65" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Serializer</v>
+        <v>ICs - Interface  - Deserializer</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>100</v>
@@ -5513,7 +5510,7 @@
         <v>119</v>
       </c>
       <c r="K65" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P65" s="6" t="b">
         <v>0</v>
@@ -5553,7 +5550,7 @@
       </c>
       <c r="AA65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Serializer</v>
+        <v>Deserializer</v>
       </c>
       <c r="AB65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5575,7 +5572,7 @@
     <row r="66" spans="8:31">
       <c r="H66" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Trancievers</v>
+        <v>ICs - Interface  - Drivers</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>100</v>
@@ -5584,7 +5581,7 @@
         <v>119</v>
       </c>
       <c r="K66" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P66" s="6" t="b">
         <v>0</v>
@@ -5624,7 +5621,7 @@
       </c>
       <c r="AA66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Trancievers</v>
+        <v>Drivers</v>
       </c>
       <c r="AB66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5646,7 +5643,7 @@
     <row r="67" spans="8:31">
       <c r="H67" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - UART</v>
+        <v>ICs - Interface  - IO Expander</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>100</v>
@@ -5655,7 +5652,7 @@
         <v>119</v>
       </c>
       <c r="K67" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="P67" s="6" t="b">
         <v>0</v>
@@ -5695,7 +5692,7 @@
       </c>
       <c r="AA67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>UART</v>
+        <v>IO Expander</v>
       </c>
       <c r="AB67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5717,19 +5714,16 @@
     <row r="68" spans="8:31">
       <c r="H68" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Comparator - Digital</v>
+        <v>ICs - Interface  - Recievers</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K68" t="s">
-        <v>116</v>
-      </c>
-      <c r="L68" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="P68" s="6" t="b">
         <v>0</v>
@@ -5765,15 +5759,15 @@
       </c>
       <c r="Z68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Comparator - </v>
+        <v>Recievers</v>
       </c>
       <c r="AB68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5791,19 +5785,16 @@
     <row r="69" spans="8:31">
       <c r="H69" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Counter - Up</v>
+        <v>ICs - Interface  - Serializer</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J69" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K69" t="s">
-        <v>163</v>
-      </c>
-      <c r="L69" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="P69" s="6" t="b">
         <v>0</v>
@@ -5839,15 +5830,15 @@
       </c>
       <c r="Z69" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA69" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Counter - </v>
+        <v>Serializer</v>
       </c>
       <c r="AB69" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Up</v>
+        <v/>
       </c>
       <c r="AC69" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5865,19 +5856,16 @@
     <row r="70" spans="8:31">
       <c r="H70" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Counter - Up&amp;Down</v>
+        <v>ICs - Interface  - Trancievers</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J70" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K70" t="s">
-        <v>163</v>
-      </c>
-      <c r="L70" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="P70" s="6" t="b">
         <v>0</v>
@@ -5913,15 +5901,15 @@
       </c>
       <c r="Z70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Counter - </v>
+        <v>Trancievers</v>
       </c>
       <c r="AB70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Up&amp;Down</v>
+        <v/>
       </c>
       <c r="AC70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5939,19 +5927,16 @@
     <row r="71" spans="8:31">
       <c r="H71" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Demultiplexer - Digital</v>
+        <v>ICs - Interface  - UART</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J71" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K71" t="s">
-        <v>175</v>
-      </c>
-      <c r="L71" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="P71" s="6" t="b">
         <v>0</v>
@@ -5987,15 +5972,15 @@
       </c>
       <c r="Z71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Demultiplexer - </v>
+        <v>UART</v>
       </c>
       <c r="AB71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6013,7 +5998,7 @@
     <row r="72" spans="8:31">
       <c r="H72" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Flip Flops</v>
+        <v>ICs - Logic - Comparator - Digital</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>100</v>
@@ -6022,7 +6007,10 @@
         <v>118</v>
       </c>
       <c r="K72" t="s">
-        <v>166</v>
+        <v>116</v>
+      </c>
+      <c r="L72" t="s">
+        <v>98</v>
       </c>
       <c r="P72" s="6" t="b">
         <v>0</v>
@@ -6062,11 +6050,11 @@
       </c>
       <c r="AA72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Flip Flops</v>
+        <v xml:space="preserve">Comparator - </v>
       </c>
       <c r="AB72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6084,7 +6072,7 @@
     <row r="73" spans="8:31">
       <c r="H73" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Gates</v>
+        <v>ICs - Logic - Counter - Up</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>100</v>
@@ -6093,7 +6081,10 @@
         <v>118</v>
       </c>
       <c r="K73" t="s">
-        <v>167</v>
+        <v>163</v>
+      </c>
+      <c r="L73" t="s">
+        <v>164</v>
       </c>
       <c r="P73" s="6" t="b">
         <v>0</v>
@@ -6133,11 +6124,11 @@
       </c>
       <c r="AA73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Gates</v>
+        <v xml:space="preserve">Counter - </v>
       </c>
       <c r="AB73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Up</v>
       </c>
       <c r="AC73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6155,7 +6146,7 @@
     <row r="74" spans="8:31">
       <c r="H74" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Latches</v>
+        <v>ICs - Logic - Counter - Up&amp;Down</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>100</v>
@@ -6164,7 +6155,10 @@
         <v>118</v>
       </c>
       <c r="K74" t="s">
-        <v>168</v>
+        <v>163</v>
+      </c>
+      <c r="L74" t="s">
+        <v>165</v>
       </c>
       <c r="P74" s="6" t="b">
         <v>0</v>
@@ -6204,11 +6198,11 @@
       </c>
       <c r="AA74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Latches</v>
+        <v xml:space="preserve">Counter - </v>
       </c>
       <c r="AB74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Up&amp;Down</v>
       </c>
       <c r="AC74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6226,7 +6220,7 @@
     <row r="75" spans="8:31">
       <c r="H75" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Level Shifters</v>
+        <v>ICs - Logic - Demultiplexer - Digital</v>
       </c>
       <c r="I75" s="6" t="s">
         <v>100</v>
@@ -6235,7 +6229,10 @@
         <v>118</v>
       </c>
       <c r="K75" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="L75" t="s">
+        <v>98</v>
       </c>
       <c r="P75" s="6" t="b">
         <v>0</v>
@@ -6247,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T75" t="b">
         <v>0</v>
@@ -6263,7 +6260,7 @@
       </c>
       <c r="X75" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6275,11 +6272,11 @@
       </c>
       <c r="AA75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Level Shifters</v>
+        <v xml:space="preserve">Demultiplexer - </v>
       </c>
       <c r="AB75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6297,7 +6294,7 @@
     <row r="76" spans="8:31">
       <c r="H76" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Multiplexer - Digital</v>
+        <v>ICs - Logic - Flip Flops</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>100</v>
@@ -6306,10 +6303,7 @@
         <v>118</v>
       </c>
       <c r="K76" t="s">
-        <v>174</v>
-      </c>
-      <c r="L76" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="P76" s="6" t="b">
         <v>0</v>
@@ -6349,11 +6343,11 @@
       </c>
       <c r="AA76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Multiplexer - </v>
+        <v>Flip Flops</v>
       </c>
       <c r="AB76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6371,7 +6365,7 @@
     <row r="77" spans="8:31">
       <c r="H77" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Multivibrators</v>
+        <v>ICs - Logic - Gates</v>
       </c>
       <c r="I77" s="6" t="s">
         <v>100</v>
@@ -6380,7 +6374,7 @@
         <v>118</v>
       </c>
       <c r="K77" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P77" s="6" t="b">
         <v>0</v>
@@ -6420,7 +6414,7 @@
       </c>
       <c r="AA77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Multivibrators</v>
+        <v>Gates</v>
       </c>
       <c r="AB77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6442,7 +6436,7 @@
     <row r="78" spans="8:31">
       <c r="H78" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Shift Registers - PISO</v>
+        <v>ICs - Logic - Latches</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>100</v>
@@ -6451,10 +6445,7 @@
         <v>118</v>
       </c>
       <c r="K78" t="s">
-        <v>170</v>
-      </c>
-      <c r="L78" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="P78" s="6" t="b">
         <v>0</v>
@@ -6494,11 +6485,11 @@
       </c>
       <c r="AA78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Shift Registers - </v>
+        <v>Latches</v>
       </c>
       <c r="AB78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>PISO</v>
+        <v/>
       </c>
       <c r="AC78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6516,7 +6507,7 @@
     <row r="79" spans="8:31">
       <c r="H79" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Shift Registers - SIPO</v>
+        <v>ICs - Logic - Level Shifters</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>100</v>
@@ -6525,10 +6516,7 @@
         <v>118</v>
       </c>
       <c r="K79" t="s">
-        <v>170</v>
-      </c>
-      <c r="L79" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="P79" s="6" t="b">
         <v>0</v>
@@ -6540,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="S79" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="b">
         <v>0</v>
@@ -6556,7 +6544,7 @@
       </c>
       <c r="X79" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6568,11 +6556,11 @@
       </c>
       <c r="AA79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Shift Registers - </v>
+        <v>Level Shifters</v>
       </c>
       <c r="AB79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SIPO</v>
+        <v/>
       </c>
       <c r="AC79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6590,7 +6578,7 @@
     <row r="80" spans="8:31">
       <c r="H80" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Switch - Digital</v>
+        <v>ICs - Logic - Multiplexer - Digital</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>100</v>
@@ -6599,7 +6587,7 @@
         <v>118</v>
       </c>
       <c r="K80" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L80" t="s">
         <v>98</v>
@@ -6642,7 +6630,7 @@
       </c>
       <c r="AA80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Switch - </v>
+        <v xml:space="preserve">Multiplexer - </v>
       </c>
       <c r="AB80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6664,7 +6652,7 @@
     <row r="81" spans="8:31">
       <c r="H81" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Translators</v>
+        <v>ICs - Logic - Multivibrators</v>
       </c>
       <c r="I81" s="6" t="s">
         <v>100</v>
@@ -6673,7 +6661,7 @@
         <v>118</v>
       </c>
       <c r="K81" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="P81" s="6" t="b">
         <v>0</v>
@@ -6713,7 +6701,7 @@
       </c>
       <c r="AA81" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Translators</v>
+        <v>Multivibrators</v>
       </c>
       <c r="AB81" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6735,16 +6723,19 @@
     <row r="82" spans="8:31">
       <c r="H82" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - DRAM</v>
+        <v>ICs - Logic - Shift Registers - PISO</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J82" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K82" t="s">
-        <v>113</v>
+        <v>170</v>
+      </c>
+      <c r="L82" t="s">
+        <v>172</v>
       </c>
       <c r="P82" s="6" t="b">
         <v>0</v>
@@ -6780,15 +6771,15 @@
       </c>
       <c r="Z82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DRAM</v>
+        <v xml:space="preserve">Shift Registers - </v>
       </c>
       <c r="AB82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>PISO</v>
       </c>
       <c r="AC82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6806,44 +6797,47 @@
     <row r="83" spans="8:31">
       <c r="H83" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - EEPROM</v>
+        <v>ICs - Logic - Shift Registers - SIPO</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J83" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K83" t="s">
-        <v>111</v>
+        <v>170</v>
+      </c>
+      <c r="L83" t="s">
+        <v>171</v>
       </c>
       <c r="P83" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S83" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U83" t="b">
         <v>1</v>
       </c>
-      <c r="V83" t="s">
-        <v>184</v>
+      <c r="V83" t="b">
+        <v>0</v>
       </c>
       <c r="W83">
         <v>0</v>
       </c>
       <c r="X83" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6851,15 +6845,15 @@
       </c>
       <c r="Z83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>EEPROM</v>
+        <v xml:space="preserve">Shift Registers - </v>
       </c>
       <c r="AB83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>SIPO</v>
       </c>
       <c r="AC83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6877,44 +6871,47 @@
     <row r="84" spans="8:31">
       <c r="H84" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - FLASH</v>
+        <v>ICs - Logic - Switch - Digital</v>
       </c>
       <c r="I84" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J84" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K84" t="s">
-        <v>205</v>
+        <v>173</v>
+      </c>
+      <c r="L84" t="s">
+        <v>98</v>
       </c>
       <c r="P84" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U84" t="b">
         <v>1</v>
       </c>
-      <c r="V84" t="s">
-        <v>184</v>
+      <c r="V84" t="b">
+        <v>0</v>
       </c>
       <c r="W84">
         <v>0</v>
       </c>
       <c r="X84" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6922,15 +6919,15 @@
       </c>
       <c r="Z84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>FLASH</v>
+        <v xml:space="preserve">Switch - </v>
       </c>
       <c r="AB84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6948,16 +6945,16 @@
     <row r="85" spans="8:31">
       <c r="H85" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - SD Card</v>
+        <v>ICs - Logic - Translators</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J85" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K85" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="P85" s="6" t="b">
         <v>0</v>
@@ -6993,11 +6990,11 @@
       </c>
       <c r="Z85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SD Card</v>
+        <v>Translators</v>
       </c>
       <c r="AB85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7019,19 +7016,16 @@
     <row r="86" spans="8:31">
       <c r="H86" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Gate Driver - Isolated</v>
+        <v>ICs - Memory - DRAM</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J86" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="K86" t="s">
-        <v>101</v>
-      </c>
-      <c r="L86" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="P86" s="6" t="b">
         <v>0</v>
@@ -7067,15 +7061,15 @@
       </c>
       <c r="Z86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Gate Driver - </v>
+        <v>DRAM</v>
       </c>
       <c r="AB86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Isolated</v>
+        <v/>
       </c>
       <c r="AC86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -7093,47 +7087,44 @@
     <row r="87" spans="8:31">
       <c r="H87" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Gate Driver - Non Isolated</v>
+        <v>ICs - Memory - EEPROM</v>
       </c>
       <c r="I87" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J87" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="K87" t="s">
-        <v>101</v>
-      </c>
-      <c r="L87" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="P87" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U87" t="b">
         <v>1</v>
       </c>
-      <c r="V87" t="b">
-        <v>0</v>
+      <c r="V87" t="s">
+        <v>184</v>
       </c>
       <c r="W87">
         <v>0</v>
       </c>
       <c r="X87" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -7141,15 +7132,15 @@
       </c>
       <c r="Z87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Gate Driver - </v>
+        <v>EEPROM</v>
       </c>
       <c r="AB87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Non Isolated</v>
+        <v/>
       </c>
       <c r="AC87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -7167,44 +7158,44 @@
     <row r="88" spans="8:31">
       <c r="H88" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Half&amp;H Bridge</v>
+        <v>ICs - Memory - FLASH</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J88" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="K88" t="s">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="P88" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U88" t="b">
         <v>1</v>
       </c>
-      <c r="V88" t="b">
-        <v>0</v>
+      <c r="V88" t="s">
+        <v>184</v>
       </c>
       <c r="W88">
         <v>0</v>
       </c>
       <c r="X88" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y88" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -7212,11 +7203,11 @@
       </c>
       <c r="Z88" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA88" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Half&amp;H Bridge</v>
+        <v>FLASH</v>
       </c>
       <c r="AB88" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7238,16 +7229,16 @@
     <row r="89" spans="8:31">
       <c r="H89" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Supply Sequencing</v>
+        <v>ICs - Memory - SD Card</v>
       </c>
       <c r="I89" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J89" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="K89" t="s">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="P89" s="6" t="b">
         <v>0</v>
@@ -7265,7 +7256,7 @@
         <v>0</v>
       </c>
       <c r="U89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V89" t="b">
         <v>0</v>
@@ -7275,7 +7266,7 @@
       </c>
       <c r="X89" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y89" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -7283,11 +7274,11 @@
       </c>
       <c r="Z89" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA89" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Supply Sequencing</v>
+        <v>SD Card</v>
       </c>
       <c r="AB89" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7309,7 +7300,7 @@
     <row r="90" spans="8:31">
       <c r="H90" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Switching Controler</v>
+        <v>ICs - Power - Gate Driver - Isolated</v>
       </c>
       <c r="I90" s="6" t="s">
         <v>100</v>
@@ -7318,7 +7309,10 @@
         <v>88</v>
       </c>
       <c r="K90" t="s">
-        <v>104</v>
+        <v>101</v>
+      </c>
+      <c r="L90" t="s">
+        <v>84</v>
       </c>
       <c r="P90" s="6" t="b">
         <v>0</v>
@@ -7358,11 +7352,11 @@
       </c>
       <c r="AA90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Switching Controler</v>
+        <v xml:space="preserve">Gate Driver - </v>
       </c>
       <c r="AB90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Isolated</v>
       </c>
       <c r="AC90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -7380,41 +7374,47 @@
     <row r="91" spans="8:31">
       <c r="H91" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - RTCs</v>
+        <v>ICs - Power - Gate Driver - Non Isolated</v>
       </c>
       <c r="I91" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J91" t="s">
-        <v>210</v>
+        <v>88</v>
+      </c>
+      <c r="K91" t="s">
+        <v>101</v>
+      </c>
+      <c r="L91" t="s">
+        <v>102</v>
       </c>
       <c r="P91" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U91" t="b">
         <v>1</v>
       </c>
-      <c r="V91" t="s">
-        <v>184</v>
+      <c r="V91" t="b">
+        <v>0</v>
       </c>
       <c r="W91">
         <v>0</v>
       </c>
       <c r="X91" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -7422,15 +7422,15 @@
       </c>
       <c r="Z91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>RTCs</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Gate Driver - </v>
       </c>
       <c r="AB91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Non Isolated</v>
       </c>
       <c r="AC91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -7448,13 +7448,16 @@
     <row r="92" spans="8:31">
       <c r="H92" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Inductors - Common Mode Choke</v>
+        <v>ICs - Power - Half&amp;H Bridge</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="J92" t="s">
-        <v>80</v>
+        <v>88</v>
+      </c>
+      <c r="K92" t="s">
+        <v>139</v>
       </c>
       <c r="P92" s="6" t="b">
         <v>0</v>
@@ -7472,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="U92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V92" t="b">
         <v>0</v>
@@ -7482,19 +7485,19 @@
       </c>
       <c r="X92" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Inductors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Common Mode Choke</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Half&amp;H Bridge</v>
       </c>
       <c r="AB92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7516,13 +7519,16 @@
     <row r="93" spans="8:31">
       <c r="H93" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Isolators - Analog</v>
+        <v>ICs - Power - Supply Sequencing</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J93" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="K93" t="s">
+        <v>200</v>
       </c>
       <c r="P93" s="6" t="b">
         <v>0</v>
@@ -7540,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="U93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V93" t="b">
         <v>0</v>
@@ -7550,19 +7556,19 @@
       </c>
       <c r="X93" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Isolators - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Analog</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Supply Sequencing</v>
       </c>
       <c r="AB93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7584,13 +7590,16 @@
     <row r="94" spans="8:31">
       <c r="H94" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>LEDs - RGB</v>
+        <v>ICs - Power - Switching Controler</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="J94" t="s">
-        <v>154</v>
+        <v>88</v>
+      </c>
+      <c r="K94" t="s">
+        <v>104</v>
       </c>
       <c r="P94" s="6" t="b">
         <v>0</v>
@@ -7605,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="T94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U94" t="b">
         <v>1</v>
@@ -7618,19 +7627,19 @@
       </c>
       <c r="X94" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y94" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">LEDs - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z94" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>RGB</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA94" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Switching Controler</v>
       </c>
       <c r="AB94" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7652,49 +7661,49 @@
     <row r="95" spans="8:31">
       <c r="H95" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Heat Shrink</v>
+        <v>ICs - RTCs</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="J95" t="s">
-        <v>147</v>
+        <v>210</v>
       </c>
       <c r="P95" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" s="5" t="b">
         <v>1</v>
       </c>
       <c r="T95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U95" t="b">
-        <v>0</v>
-      </c>
-      <c r="V95" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V95" t="s">
+        <v>184</v>
       </c>
       <c r="W95">
         <v>0</v>
       </c>
       <c r="X95" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y95" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z95" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Heat Shrink</v>
+        <v>RTCs</v>
       </c>
       <c r="AA95" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7720,13 +7729,13 @@
     <row r="96" spans="8:31">
       <c r="H96" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Nuts</v>
+        <v>Isolators - Analog</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="J96" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="P96" s="6" t="b">
         <v>0</v>
@@ -7744,7 +7753,7 @@
         <v>0</v>
       </c>
       <c r="U96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V96" t="b">
         <v>0</v>
@@ -7754,15 +7763,15 @@
       </c>
       <c r="X96" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y96" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Isolators - </v>
       </c>
       <c r="Z96" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Nuts</v>
+        <v>Analog</v>
       </c>
       <c r="AA96" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7788,13 +7797,13 @@
     <row r="97" spans="8:31">
       <c r="H97" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Spacers</v>
+        <v>LEDs - RGB</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="J97" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="P97" s="6" t="b">
         <v>0</v>
@@ -7809,10 +7818,10 @@
         <v>0</v>
       </c>
       <c r="T97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V97" t="b">
         <v>0</v>
@@ -7822,15 +7831,15 @@
       </c>
       <c r="X97" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">LEDs - </v>
       </c>
       <c r="Z97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Spacers</v>
+        <v>RGB</v>
       </c>
       <c r="AA97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7856,16 +7865,13 @@
     <row r="98" spans="8:31">
       <c r="H98" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Standoffs  - F_F</v>
+        <v>Mechanical  - Heat Shrink</v>
       </c>
       <c r="I98" s="6" t="s">
         <v>133</v>
       </c>
       <c r="J98" t="s">
-        <v>134</v>
-      </c>
-      <c r="K98" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P98" s="6" t="b">
         <v>0</v>
@@ -7877,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="S98" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" t="b">
         <v>0</v>
@@ -7893,7 +7899,7 @@
       </c>
       <c r="X98" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -7901,11 +7907,11 @@
       </c>
       <c r="Z98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standoffs  - </v>
+        <v>Heat Shrink</v>
       </c>
       <c r="AA98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>F_F</v>
+        <v/>
       </c>
       <c r="AB98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7927,16 +7933,13 @@
     <row r="99" spans="8:31">
       <c r="H99" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Standoffs  - M_F</v>
+        <v>Mechanical  - Nuts</v>
       </c>
       <c r="I99" s="6" t="s">
         <v>133</v>
       </c>
       <c r="J99" t="s">
-        <v>134</v>
-      </c>
-      <c r="K99" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P99" s="6" t="b">
         <v>0</v>
@@ -7972,11 +7975,11 @@
       </c>
       <c r="Z99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standoffs  - </v>
+        <v>Nuts</v>
       </c>
       <c r="AA99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>M_F</v>
+        <v/>
       </c>
       <c r="AB99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7998,13 +8001,13 @@
     <row r="100" spans="8:31">
       <c r="H100" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - PolyFuses</v>
+        <v>Mechanical  - Spacers</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="J100" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="P100" s="6" t="b">
         <v>0</v>
@@ -8016,13 +8019,13 @@
         <v>0</v>
       </c>
       <c r="S100" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V100" t="b">
         <v>0</v>
@@ -8032,15 +8035,15 @@
       </c>
       <c r="X100" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>42.857142857142854</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>PolyFuses</v>
+        <v>Spacers</v>
       </c>
       <c r="AA100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -8066,16 +8069,16 @@
     <row r="101" spans="8:31">
       <c r="H101" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - Chasis Mount - AC-DC</v>
+        <v>Mechanical  - Standoffs  - F_F</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="J101" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="K101" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="P101" s="6" t="b">
         <v>0</v>
@@ -8107,15 +8110,15 @@
       </c>
       <c r="Y101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Chasis Mount - </v>
+        <v xml:space="preserve">Standoffs  - </v>
       </c>
       <c r="AA101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>AC-DC</v>
+        <v>F_F</v>
       </c>
       <c r="AB101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8137,16 +8140,16 @@
     <row r="102" spans="8:31">
       <c r="H102" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - Chasis Mount - DC-DC</v>
+        <v>Mechanical  - Standoffs  - M_F</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="J102" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="K102" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="P102" s="6" t="b">
         <v>0</v>
@@ -8178,15 +8181,15 @@
       </c>
       <c r="Y102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Chasis Mount - </v>
+        <v xml:space="preserve">Standoffs  - </v>
       </c>
       <c r="AA102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DC-DC</v>
+        <v>M_F</v>
       </c>
       <c r="AB102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8208,16 +8211,13 @@
     <row r="103" spans="8:31">
       <c r="H103" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - PCB Mount - AC-DC</v>
+        <v>Protection - PolyFuses</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="J103" t="s">
-        <v>69</v>
-      </c>
-      <c r="K103" t="s">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="P103" s="6" t="b">
         <v>0</v>
@@ -8229,13 +8229,13 @@
         <v>0</v>
       </c>
       <c r="S103" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V103" t="b">
         <v>0</v>
@@ -8244,19 +8244,20 @@
         <v>0</v>
       </c>
       <c r="X103" s="6">
-        <v>5</v>
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>42.857142857142854</v>
       </c>
       <c r="Y103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">PCB Mount - </v>
+        <v>PolyFuses</v>
       </c>
       <c r="AA103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>AC-DC</v>
+        <v/>
       </c>
       <c r="AB103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8278,13 +8279,16 @@
     <row r="104" spans="8:31">
       <c r="H104" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Network</v>
+        <v>PSUs - Chasis Mount - AC-DC</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="J104" t="s">
-        <v>51</v>
+        <v>86</v>
+      </c>
+      <c r="K104" t="s">
+        <v>82</v>
       </c>
       <c r="P104" s="6" t="b">
         <v>0</v>
@@ -8316,15 +8320,15 @@
       </c>
       <c r="Y104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Resistors - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Network</v>
+        <v xml:space="preserve">Chasis Mount - </v>
       </c>
       <c r="AA104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>AC-DC</v>
       </c>
       <c r="AB104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8346,16 +8350,16 @@
     <row r="105" spans="8:31">
       <c r="H105" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Single - Through Hole</v>
+        <v>PSUs - Chasis Mount - DC-DC</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="J105" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="K105" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="P105" s="6" t="b">
         <v>0</v>
@@ -8387,15 +8391,15 @@
       </c>
       <c r="Y105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Resistors - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Single - </v>
+        <v xml:space="preserve">Chasis Mount - </v>
       </c>
       <c r="AA105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Through Hole</v>
+        <v>DC-DC</v>
       </c>
       <c r="AB105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8417,13 +8421,16 @@
     <row r="106" spans="8:31">
       <c r="H106" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Capacitance To Digital</v>
+        <v>PSUs - PCB Mount - AC-DC</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="J106" t="s">
-        <v>212</v>
+        <v>69</v>
+      </c>
+      <c r="K106" t="s">
+        <v>82</v>
       </c>
       <c r="P106" s="6" t="b">
         <v>0</v>
@@ -8450,20 +8457,19 @@
         <v>0</v>
       </c>
       <c r="X106" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Sensors - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Capacitance To Digital</v>
+        <v xml:space="preserve">PCB Mount - </v>
       </c>
       <c r="AA106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>AC-DC</v>
       </c>
       <c r="AB106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8485,13 +8491,13 @@
     <row r="107" spans="8:31">
       <c r="H107" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Humidity</v>
+        <v>Resistors - Network</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>211</v>
+        <v>42</v>
       </c>
       <c r="J107" t="s">
-        <v>215</v>
+        <v>51</v>
       </c>
       <c r="P107" s="6" t="b">
         <v>0</v>
@@ -8523,11 +8529,11 @@
       </c>
       <c r="Y107" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Sensors - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z107" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Humidity</v>
+        <v>Network</v>
       </c>
       <c r="AA107" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -8553,16 +8559,16 @@
     <row r="108" spans="8:31">
       <c r="H108" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Temperature - RTDs</v>
+        <v>Resistors - Single - Through Hole</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>211</v>
+        <v>42</v>
       </c>
       <c r="J108" t="s">
-        <v>213</v>
+        <v>43</v>
       </c>
       <c r="K108" t="s">
-        <v>214</v>
+        <v>52</v>
       </c>
       <c r="P108" s="6" t="b">
         <v>0</v>
@@ -8594,15 +8600,15 @@
       </c>
       <c r="Y108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Sensors - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Temperature - </v>
+        <v xml:space="preserve">Single - </v>
       </c>
       <c r="AA108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>RTDs</v>
+        <v>Through Hole</v>
       </c>
       <c r="AB108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8624,16 +8630,13 @@
     <row r="109" spans="8:31">
       <c r="H109" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Touch Sensor - Capacitive</v>
+        <v>Sensors - Capacitance To Digital</v>
       </c>
       <c r="I109" s="6" t="s">
         <v>211</v>
       </c>
       <c r="J109" t="s">
-        <v>157</v>
-      </c>
-      <c r="K109" t="s">
-        <v>158</v>
+        <v>212</v>
       </c>
       <c r="P109" s="6" t="b">
         <v>0</v>
@@ -8669,11 +8672,11 @@
       </c>
       <c r="Z109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Touch Sensor - </v>
+        <v>Capacitance To Digital</v>
       </c>
       <c r="AA109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Capacitive</v>
+        <v/>
       </c>
       <c r="AB109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8695,16 +8698,13 @@
     <row r="110" spans="8:31">
       <c r="H110" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Transformer - Power - Chasis Mount</v>
+        <v>Sensors - Humidity</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="J110" t="s">
-        <v>88</v>
-      </c>
-      <c r="K110" t="s">
-        <v>86</v>
+        <v>215</v>
       </c>
       <c r="P110" s="6" t="b">
         <v>0</v>
@@ -8736,15 +8736,15 @@
       </c>
       <c r="Y110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Transformer - </v>
+        <v xml:space="preserve">Sensors - </v>
       </c>
       <c r="Z110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v>Humidity</v>
       </c>
       <c r="AA110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Chasis Mount</v>
+        <v/>
       </c>
       <c r="AB110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8766,16 +8766,16 @@
     <row r="111" spans="8:31">
       <c r="H111" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Transformer - Power - PCB Mount</v>
+        <v>Sensors - Temperature - RTDs</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="J111" t="s">
-        <v>88</v>
+        <v>213</v>
       </c>
       <c r="K111" t="s">
-        <v>69</v>
+        <v>214</v>
       </c>
       <c r="P111" s="6" t="b">
         <v>0</v>
@@ -8807,15 +8807,15 @@
       </c>
       <c r="Y111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Transformer - </v>
+        <v xml:space="preserve">Sensors - </v>
       </c>
       <c r="Z111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Temperature - </v>
       </c>
       <c r="AA111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>PCB Mount</v>
+        <v>RTDs</v>
       </c>
       <c r="AB111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8837,13 +8837,16 @@
     <row r="112" spans="8:31">
       <c r="H112" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Voltage References - Misc</v>
+        <v>Sensors - Touch Sensor - Capacitive</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="J112" t="s">
-        <v>187</v>
+        <v>157</v>
+      </c>
+      <c r="K112" t="s">
+        <v>158</v>
       </c>
       <c r="P112" s="6" t="b">
         <v>0</v>
@@ -8875,15 +8878,15 @@
       </c>
       <c r="Y112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Voltage References - </v>
+        <v xml:space="preserve">Sensors - </v>
       </c>
       <c r="Z112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Misc</v>
+        <v xml:space="preserve">Touch Sensor - </v>
       </c>
       <c r="AA112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Capacitive</v>
       </c>
       <c r="AB112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8905,53 +8908,56 @@
     <row r="113" spans="8:31">
       <c r="H113" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Cables - Premade</v>
+        <v>Transformer - Power - Chasis Mount</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="J113" t="s">
-        <v>31</v>
+        <v>88</v>
+      </c>
+      <c r="K113" t="s">
+        <v>86</v>
       </c>
       <c r="P113" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S113" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W113">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X113" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Cables - </v>
+        <v xml:space="preserve">Transformer - </v>
       </c>
       <c r="Z113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Premade</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Chasis Mount</v>
       </c>
       <c r="AB113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8973,53 +8979,56 @@
     <row r="114" spans="8:31">
       <c r="H114" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Capacitors - Unpolarized</v>
+        <v>Transformer - Power - PCB Mount</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="J114" t="s">
-        <v>33</v>
+        <v>88</v>
+      </c>
+      <c r="K114" t="s">
+        <v>69</v>
       </c>
       <c r="P114" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S114" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W114">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X114" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Capacitors - </v>
+        <v xml:space="preserve">Transformer - </v>
       </c>
       <c r="Z114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Unpolarized</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>PCB Mount</v>
       </c>
       <c r="AB114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9041,56 +9050,53 @@
     <row r="115" spans="8:31">
       <c r="H115" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - ICs - Generators &amp; Synthisizers</v>
+        <v>Voltage References - Misc</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="J115" t="s">
-        <v>100</v>
-      </c>
-      <c r="K115" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="P115" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S115" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W115">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X115" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Voltage References - </v>
       </c>
       <c r="Z115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v>Misc</v>
       </c>
       <c r="AA115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Generators &amp; Synthisizers</v>
+        <v/>
       </c>
       <c r="AB115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9112,19 +9118,13 @@
     <row r="116" spans="8:31">
       <c r="H116" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - XO</v>
+        <v>Cables - Premade</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>153</v>
+        <v>30</v>
       </c>
       <c r="J116" t="s">
-        <v>124</v>
-      </c>
-      <c r="K116" t="s">
-        <v>125</v>
-      </c>
-      <c r="L116" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="P116" s="6" t="b">
         <v>1</v>
@@ -9156,19 +9156,19 @@
       </c>
       <c r="Y116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Cables - </v>
       </c>
       <c r="Z116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v>Premade</v>
       </c>
       <c r="AA116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Fixed - </v>
+        <v/>
       </c>
       <c r="AB116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>XO</v>
+        <v/>
       </c>
       <c r="AC116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -9186,13 +9186,13 @@
     <row r="117" spans="8:31">
       <c r="H117" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Barrel Jack</v>
+        <v>Capacitors - Unpolarized</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J117" t="s">
-        <v>196</v>
+        <v>33</v>
       </c>
       <c r="P117" s="6" t="b">
         <v>1</v>
@@ -9224,11 +9224,11 @@
       </c>
       <c r="Y117" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Capacitors - </v>
       </c>
       <c r="Z117" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Barrel Jack</v>
+        <v>Unpolarized</v>
       </c>
       <c r="AA117" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9254,13 +9254,16 @@
     <row r="118" spans="8:31">
       <c r="H118" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - IC socket</v>
+        <v>Clock&amp;Timing - ICs - Generators &amp; Synthisizers</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="J118" t="s">
-        <v>199</v>
+        <v>100</v>
+      </c>
+      <c r="K118" t="s">
+        <v>140</v>
       </c>
       <c r="P118" s="6" t="b">
         <v>1</v>
@@ -9292,15 +9295,15 @@
       </c>
       <c r="Y118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>IC socket</v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="AA118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Generators &amp; Synthisizers</v>
       </c>
       <c r="AB118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9322,13 +9325,19 @@
     <row r="119" spans="8:31">
       <c r="H119" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Mezzanine</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - XO</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="J119" t="s">
-        <v>179</v>
+        <v>124</v>
+      </c>
+      <c r="K119" t="s">
+        <v>125</v>
+      </c>
+      <c r="L119" t="s">
+        <v>126</v>
       </c>
       <c r="P119" s="6" t="b">
         <v>1</v>
@@ -9360,19 +9369,19 @@
       </c>
       <c r="Y119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Mezzanine</v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Fixed - </v>
       </c>
       <c r="AB119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>XO</v>
       </c>
       <c r="AC119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -9390,16 +9399,13 @@
     <row r="120" spans="8:31">
       <c r="H120" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Pads - SMD</v>
+        <v>Connectors - Barrel Jack</v>
       </c>
       <c r="I120" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J120" t="s">
-        <v>47</v>
-      </c>
-      <c r="K120" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="P120" s="6" t="b">
         <v>1</v>
@@ -9435,11 +9441,11 @@
       </c>
       <c r="Z120" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Pads - </v>
+        <v>Barrel Jack</v>
       </c>
       <c r="AA120" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SMD</v>
+        <v/>
       </c>
       <c r="AB120" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9461,16 +9467,13 @@
     <row r="121" spans="8:31">
       <c r="H121" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Pads - Through Hole</v>
+        <v>Connectors - IC socket</v>
       </c>
       <c r="I121" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J121" t="s">
-        <v>47</v>
-      </c>
-      <c r="K121" t="s">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="P121" s="6" t="b">
         <v>1</v>
@@ -9506,11 +9509,11 @@
       </c>
       <c r="Z121" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Pads - </v>
+        <v>IC socket</v>
       </c>
       <c r="AA121" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Through Hole</v>
+        <v/>
       </c>
       <c r="AB121" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9532,13 +9535,13 @@
     <row r="122" spans="8:31">
       <c r="H122" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Programming</v>
+        <v>Connectors - Mezzanine</v>
       </c>
       <c r="I122" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J122" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="P122" s="6" t="b">
         <v>1</v>
@@ -9574,7 +9577,7 @@
       </c>
       <c r="Z122" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Programming</v>
+        <v>Mezzanine</v>
       </c>
       <c r="AA122" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9600,13 +9603,16 @@
     <row r="123" spans="8:31">
       <c r="H123" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Rectangular</v>
+        <v>Connectors - Pads - SMD</v>
       </c>
       <c r="I123" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J123" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="K123" t="s">
+        <v>44</v>
       </c>
       <c r="P123" s="6" t="b">
         <v>1</v>
@@ -9642,11 +9648,11 @@
       </c>
       <c r="Z123" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Rectangular</v>
+        <v xml:space="preserve">Pads - </v>
       </c>
       <c r="AA123" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>SMD</v>
       </c>
       <c r="AB123" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9668,13 +9674,16 @@
     <row r="124" spans="8:31">
       <c r="H124" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - RJ</v>
+        <v>Connectors - Pads - Through Hole</v>
       </c>
       <c r="I124" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J124" t="s">
-        <v>36</v>
+        <v>47</v>
+      </c>
+      <c r="K124" t="s">
+        <v>52</v>
       </c>
       <c r="P124" s="6" t="b">
         <v>1</v>
@@ -9710,11 +9719,11 @@
       </c>
       <c r="Z124" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>RJ</v>
+        <v xml:space="preserve">Pads - </v>
       </c>
       <c r="AA124" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Through Hole</v>
       </c>
       <c r="AB124" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9736,13 +9745,13 @@
     <row r="125" spans="8:31">
       <c r="H125" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - USB</v>
+        <v>Connectors - Programming</v>
       </c>
       <c r="I125" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J125" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P125" s="6" t="b">
         <v>1</v>
@@ -9778,7 +9787,7 @@
       </c>
       <c r="Z125" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>USB</v>
+        <v>Programming</v>
       </c>
       <c r="AA125" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9804,16 +9813,13 @@
     <row r="126" spans="8:31">
       <c r="H126" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Diodes - Schottky</v>
+        <v>Connectors - Rectangular</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="J126" t="s">
-        <v>90</v>
-      </c>
-      <c r="K126" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="P126" s="6" t="b">
         <v>1</v>
@@ -9845,15 +9851,15 @@
       </c>
       <c r="Y126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Diodes - </v>
+        <v>Rectangular</v>
       </c>
       <c r="AA126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Schottky</v>
+        <v/>
       </c>
       <c r="AB126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9875,19 +9881,13 @@
     <row r="127" spans="8:31">
       <c r="H127" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - BJT - NPN</v>
+        <v>Connectors - RJ</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="J127" t="s">
-        <v>195</v>
-      </c>
-      <c r="K127" t="s">
-        <v>92</v>
-      </c>
-      <c r="L127" t="s">
-        <v>201</v>
+        <v>36</v>
       </c>
       <c r="P127" s="6" t="b">
         <v>1</v>
@@ -9919,19 +9919,19 @@
       </c>
       <c r="Y127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v>RJ</v>
       </c>
       <c r="AA127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">BJT - </v>
+        <v/>
       </c>
       <c r="AB127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>NPN</v>
+        <v/>
       </c>
       <c r="AC127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -9949,16 +9949,13 @@
     <row r="128" spans="8:31">
       <c r="H128" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - OP Amp</v>
+        <v>Connectors - USB</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="J128" t="s">
-        <v>99</v>
-      </c>
-      <c r="K128" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="P128" s="6" t="b">
         <v>1</v>
@@ -9990,15 +9987,15 @@
       </c>
       <c r="Y128" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z128" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v>USB</v>
       </c>
       <c r="AA128" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>OP Amp</v>
+        <v/>
       </c>
       <c r="AB128" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10020,16 +10017,16 @@
     <row r="129" spans="8:31">
       <c r="H129" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - MCU</v>
+        <v>Discreet - Diodes - Schottky</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J129" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="K129" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="P129" s="6" t="b">
         <v>1</v>
@@ -10061,15 +10058,15 @@
       </c>
       <c r="Y129" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z129" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Diodes - </v>
       </c>
       <c r="AA129" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>MCU</v>
+        <v>Schottky</v>
       </c>
       <c r="AB129" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10091,19 +10088,19 @@
     <row r="130" spans="8:31">
       <c r="H130" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - MCU - Module</v>
+        <v>Discreet - Transistors - BJT - NPN</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J130" t="s">
-        <v>106</v>
+        <v>195</v>
       </c>
       <c r="K130" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="L130" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="P130" s="6" t="b">
         <v>1</v>
@@ -10135,19 +10132,19 @@
       </c>
       <c r="Y130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">MCU - </v>
+        <v xml:space="preserve">BJT - </v>
       </c>
       <c r="AB130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Module</v>
+        <v>NPN</v>
       </c>
       <c r="AC130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10165,16 +10162,16 @@
     <row r="131" spans="8:31">
       <c r="H131" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Ideal Diodes</v>
+        <v>ICs - Analog - OP Amp</v>
       </c>
       <c r="I131" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J131" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="K131" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="P131" s="6" t="b">
         <v>1</v>
@@ -10210,11 +10207,11 @@
       </c>
       <c r="Z131" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA131" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Ideal Diodes</v>
+        <v>OP Amp</v>
       </c>
       <c r="AB131" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10236,16 +10233,16 @@
     <row r="132" spans="8:31">
       <c r="H132" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Linear Regulation</v>
+        <v>ICs - Embedded - MCU</v>
       </c>
       <c r="I132" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J132" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="K132" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="P132" s="6" t="b">
         <v>1</v>
@@ -10281,11 +10278,11 @@
       </c>
       <c r="Z132" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Embedded - </v>
       </c>
       <c r="AA132" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Linear Regulation</v>
+        <v>MCU</v>
       </c>
       <c r="AB132" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10307,10 +10304,19 @@
     <row r="133" spans="8:31">
       <c r="H133" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Inductors</v>
+        <v>ICs - Embedded - MCU - Module</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>37</v>
+        <v>100</v>
+      </c>
+      <c r="J133" t="s">
+        <v>106</v>
+      </c>
+      <c r="K133" t="s">
+        <v>107</v>
+      </c>
+      <c r="L133" t="s">
+        <v>189</v>
       </c>
       <c r="P133" s="6" t="b">
         <v>1</v>
@@ -10342,19 +10348,19 @@
       </c>
       <c r="Y133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v>Inductors</v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v/>
+        <v xml:space="preserve">Embedded - </v>
       </c>
       <c r="AA133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">MCU - </v>
       </c>
       <c r="AB133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Module</v>
       </c>
       <c r="AC133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10372,13 +10378,16 @@
     <row r="134" spans="8:31">
       <c r="H134" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Inductors - Ferrite Bead</v>
+        <v>ICs - Power - Ideal Diodes</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="J134" t="s">
-        <v>203</v>
+        <v>88</v>
+      </c>
+      <c r="K134" t="s">
+        <v>105</v>
       </c>
       <c r="P134" s="6" t="b">
         <v>1</v>
@@ -10410,15 +10419,15 @@
       </c>
       <c r="Y134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Inductors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Ferrite Bead</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Ideal Diodes</v>
       </c>
       <c r="AB134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10440,19 +10449,16 @@
     <row r="135" spans="8:31">
       <c r="H135" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>LEDs - Standard - Indicator - SMD</v>
+        <v>ICs - Power - Linear Regulation</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="J135" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="K135" t="s">
-        <v>151</v>
-      </c>
-      <c r="L135" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="P135" s="6" t="b">
         <v>1</v>
@@ -10484,19 +10490,19 @@
       </c>
       <c r="Y135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">LEDs - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Indicator - </v>
+        <v>Linear Regulation</v>
       </c>
       <c r="AB135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SMD</v>
+        <v/>
       </c>
       <c r="AC135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10514,19 +10520,10 @@
     <row r="136" spans="8:31">
       <c r="H136" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>LEDs - Standard - Indicator - Through Hole</v>
+        <v>Inductors</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="J136" t="s">
-        <v>63</v>
-      </c>
-      <c r="K136" t="s">
-        <v>151</v>
-      </c>
-      <c r="L136" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="P136" s="6" t="b">
         <v>1</v>
@@ -10558,19 +10555,19 @@
       </c>
       <c r="Y136" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">LEDs - </v>
+        <v>Inductors</v>
       </c>
       <c r="Z136" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v/>
       </c>
       <c r="AA136" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Indicator - </v>
+        <v/>
       </c>
       <c r="AB136" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Through Hole</v>
+        <v/>
       </c>
       <c r="AC136" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10588,13 +10585,13 @@
     <row r="137" spans="8:31">
       <c r="H137" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Feet</v>
+        <v>Inductors - Ferrite Bead</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="J137" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="P137" s="6" t="b">
         <v>1</v>
@@ -10626,11 +10623,11 @@
       </c>
       <c r="Y137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Inductors - </v>
       </c>
       <c r="Z137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Feet</v>
+        <v>Ferrite Bead</v>
       </c>
       <c r="AA137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10656,13 +10653,19 @@
     <row r="138" spans="8:31">
       <c r="H138" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Screws</v>
+        <v>LEDs - Standard - Indicator - SMD</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="J138" t="s">
-        <v>136</v>
+        <v>63</v>
+      </c>
+      <c r="K138" t="s">
+        <v>151</v>
+      </c>
+      <c r="L138" t="s">
+        <v>44</v>
       </c>
       <c r="P138" s="6" t="b">
         <v>1</v>
@@ -10694,19 +10697,19 @@
       </c>
       <c r="Y138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">LEDs - </v>
       </c>
       <c r="Z138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Screws</v>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AA138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Indicator - </v>
       </c>
       <c r="AB138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>SMD</v>
       </c>
       <c r="AC138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10724,13 +10727,19 @@
     <row r="139" spans="8:31">
       <c r="H139" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - Fuses</v>
+        <v>LEDs - Standard - Indicator - Through Hole</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="J139" t="s">
-        <v>39</v>
+        <v>63</v>
+      </c>
+      <c r="K139" t="s">
+        <v>151</v>
+      </c>
+      <c r="L139" t="s">
+        <v>52</v>
       </c>
       <c r="P139" s="6" t="b">
         <v>1</v>
@@ -10762,19 +10771,19 @@
       </c>
       <c r="Y139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">LEDs - </v>
       </c>
       <c r="Z139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Fuses</v>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AA139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Indicator - </v>
       </c>
       <c r="AB139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Through Hole</v>
       </c>
       <c r="AC139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10792,13 +10801,13 @@
     <row r="140" spans="8:31">
       <c r="H140" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - GDT</v>
+        <v>Mechanical  - Feet</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="J140" t="s">
-        <v>40</v>
+        <v>198</v>
       </c>
       <c r="P140" s="6" t="b">
         <v>1</v>
@@ -10830,11 +10839,11 @@
       </c>
       <c r="Y140" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z140" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>GDT</v>
+        <v>Feet</v>
       </c>
       <c r="AA140" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10860,13 +10869,13 @@
     <row r="141" spans="8:31">
       <c r="H141" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - MOVs</v>
+        <v>Mechanical  - Screws</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="J141" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="P141" s="6" t="b">
         <v>1</v>
@@ -10898,11 +10907,11 @@
       </c>
       <c r="Y141" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z141" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>MOVs</v>
+        <v>Screws</v>
       </c>
       <c r="AA141" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10928,13 +10937,13 @@
     <row r="142" spans="8:31">
       <c r="H142" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - TVS Diode</v>
+        <v>Protection - Fuses</v>
       </c>
       <c r="I142" s="6" t="s">
         <v>38</v>
       </c>
       <c r="J142" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="P142" s="6" t="b">
         <v>1</v>
@@ -10970,7 +10979,7 @@
       </c>
       <c r="Z142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>TVS Diode</v>
+        <v>Fuses</v>
       </c>
       <c r="AA142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10996,19 +11005,13 @@
     <row r="143" spans="8:31">
       <c r="H143" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - PCB Mount - DC-DC - Non-Isolated</v>
+        <v>Protection - GDT</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="J143" t="s">
-        <v>69</v>
-      </c>
-      <c r="K143" t="s">
-        <v>83</v>
-      </c>
-      <c r="L143" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="P143" s="6" t="b">
         <v>1</v>
@@ -11040,19 +11043,19 @@
       </c>
       <c r="Y143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">PCB Mount - </v>
+        <v>GDT</v>
       </c>
       <c r="AA143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">DC-DC - </v>
+        <v/>
       </c>
       <c r="AB143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Non-Isolated</v>
+        <v/>
       </c>
       <c r="AC143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -11070,13 +11073,13 @@
     <row r="144" spans="8:31">
       <c r="H144" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - Wall Wart</v>
+        <v>Protection - MOVs</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="J144" t="s">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="P144" s="6" t="b">
         <v>1</v>
@@ -11108,11 +11111,11 @@
       </c>
       <c r="Y144" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z144" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Wall Wart</v>
+        <v>MOVs</v>
       </c>
       <c r="AA144" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11138,13 +11141,13 @@
     <row r="145" spans="8:31">
       <c r="H145" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Isolated Array</v>
+        <v>Protection - TVS Diode</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J145" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="P145" s="6" t="b">
         <v>1</v>
@@ -11176,11 +11179,11 @@
       </c>
       <c r="Y145" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Resistors - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z145" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Isolated Array</v>
+        <v>TVS Diode</v>
       </c>
       <c r="AA145" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11206,16 +11209,19 @@
     <row r="146" spans="8:31">
       <c r="H146" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Single - SMD</v>
+        <v>PSUs - PCB Mount - DC-DC - Non-Isolated</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="J146" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="K146" t="s">
-        <v>44</v>
+        <v>83</v>
+      </c>
+      <c r="L146" t="s">
+        <v>85</v>
       </c>
       <c r="P146" s="6" t="b">
         <v>1</v>
@@ -11247,19 +11253,19 @@
       </c>
       <c r="Y146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Resistors - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Single - </v>
+        <v xml:space="preserve">PCB Mount - </v>
       </c>
       <c r="AA146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SMD</v>
+        <v xml:space="preserve">DC-DC - </v>
       </c>
       <c r="AB146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Non-Isolated</v>
       </c>
       <c r="AC146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -11277,13 +11283,13 @@
     <row r="147" spans="8:31">
       <c r="H147" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Switches - Push</v>
+        <v>PSUs - Wall Wart</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="J147" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="P147" s="6" t="b">
         <v>1</v>
@@ -11315,11 +11321,11 @@
       </c>
       <c r="Y147" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Switches - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z147" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Push</v>
+        <v>Wall Wart</v>
       </c>
       <c r="AA147" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11345,13 +11351,13 @@
     <row r="148" spans="8:31">
       <c r="H148" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Switches - Slide</v>
+        <v>Resistors - Isolated Array</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>181</v>
+        <v>42</v>
       </c>
       <c r="J148" t="s">
-        <v>191</v>
+        <v>50</v>
       </c>
       <c r="P148" s="6" t="b">
         <v>1</v>
@@ -11383,11 +11389,11 @@
       </c>
       <c r="Y148" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Switches - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z148" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Slide</v>
+        <v>Isolated Array</v>
       </c>
       <c r="AA148" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11413,13 +11419,16 @@
     <row r="149" spans="8:31">
       <c r="H149" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Switches - Tactile</v>
+        <v>Resistors - Single - SMD</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>181</v>
+        <v>42</v>
       </c>
       <c r="J149" t="s">
-        <v>182</v>
+        <v>43</v>
+      </c>
+      <c r="K149" t="s">
+        <v>44</v>
       </c>
       <c r="P149" s="6" t="b">
         <v>1</v>
@@ -11451,15 +11460,15 @@
       </c>
       <c r="Y149" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Switches - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z149" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Tactile</v>
+        <v xml:space="preserve">Single - </v>
       </c>
       <c r="AA149" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>SMD</v>
       </c>
       <c r="AB149" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -11481,13 +11490,13 @@
     <row r="150" spans="8:31">
       <c r="H150" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Heat Sinks</v>
+        <v>Switches - Push</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>45</v>
+        <v>181</v>
       </c>
       <c r="J150" t="s">
-        <v>46</v>
+        <v>204</v>
       </c>
       <c r="P150" s="6" t="b">
         <v>1</v>
@@ -11519,11 +11528,11 @@
       </c>
       <c r="Y150" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Thermal - </v>
+        <v xml:space="preserve">Switches - </v>
       </c>
       <c r="Z150" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Heat Sinks</v>
+        <v>Push</v>
       </c>
       <c r="AA150" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11549,13 +11558,13 @@
     <row r="151" spans="8:31">
       <c r="H151" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Pads</v>
+        <v>Switches - Slide</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>45</v>
+        <v>181</v>
       </c>
       <c r="J151" t="s">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="P151" s="6" t="b">
         <v>1</v>
@@ -11587,11 +11596,11 @@
       </c>
       <c r="Y151" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Thermal - </v>
+        <v xml:space="preserve">Switches - </v>
       </c>
       <c r="Z151" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Pads</v>
+        <v>Slide</v>
       </c>
       <c r="AA151" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11617,13 +11626,13 @@
     <row r="152" spans="8:31">
       <c r="H152" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Voltage References - Burried Zener</v>
+        <v>Switches - Tactile</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J152" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="P152" s="6" t="b">
         <v>1</v>
@@ -11655,29 +11664,233 @@
       </c>
       <c r="Y152" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Switches - </v>
+      </c>
+      <c r="Z152" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v>Tactile</v>
+      </c>
+      <c r="AA152" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB152" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC152" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD152" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE152" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="8:31">
+      <c r="H153" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Thermal - Heat Sinks</v>
+      </c>
+      <c r="I153" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J153" t="s">
+        <v>46</v>
+      </c>
+      <c r="P153" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q153" t="b">
+        <v>1</v>
+      </c>
+      <c r="R153" t="b">
+        <v>1</v>
+      </c>
+      <c r="S153" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T153" t="b">
+        <v>1</v>
+      </c>
+      <c r="U153" t="b">
+        <v>1</v>
+      </c>
+      <c r="V153" t="b">
+        <v>1</v>
+      </c>
+      <c r="W153">
+        <v>-1</v>
+      </c>
+      <c r="X153" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>100</v>
+      </c>
+      <c r="Y153" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Thermal - </v>
+      </c>
+      <c r="Z153" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v>Heat Sinks</v>
+      </c>
+      <c r="AA153" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB153" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC153" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD153" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE153" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="8:31">
+      <c r="H154" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Thermal - Pads</v>
+      </c>
+      <c r="I154" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J154" t="s">
+        <v>47</v>
+      </c>
+      <c r="P154" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q154" t="b">
+        <v>1</v>
+      </c>
+      <c r="R154" t="b">
+        <v>1</v>
+      </c>
+      <c r="S154" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T154" t="b">
+        <v>1</v>
+      </c>
+      <c r="U154" t="b">
+        <v>1</v>
+      </c>
+      <c r="V154" t="b">
+        <v>1</v>
+      </c>
+      <c r="W154">
+        <v>-1</v>
+      </c>
+      <c r="X154" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>100</v>
+      </c>
+      <c r="Y154" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Thermal - </v>
+      </c>
+      <c r="Z154" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v>Pads</v>
+      </c>
+      <c r="AA154" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB154" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC154" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD154" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE154" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="8:31">
+      <c r="H155" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Voltage References - Burried Zener</v>
+      </c>
+      <c r="I155" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J155" t="s">
+        <v>186</v>
+      </c>
+      <c r="P155" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q155" t="b">
+        <v>1</v>
+      </c>
+      <c r="R155" t="b">
+        <v>1</v>
+      </c>
+      <c r="S155" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T155" t="b">
+        <v>1</v>
+      </c>
+      <c r="U155" t="b">
+        <v>1</v>
+      </c>
+      <c r="V155" t="b">
+        <v>1</v>
+      </c>
+      <c r="W155">
+        <v>-1</v>
+      </c>
+      <c r="X155" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>100</v>
+      </c>
+      <c r="Y155" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Voltage References - </v>
       </c>
-      <c r="Z152" t="str">
+      <c r="Z155" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Burried Zener</v>
       </c>
-      <c r="AA152" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB152" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC152" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD152" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE152" t="str">
+      <c r="AA155" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB155" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC155" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD155" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE155" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
         <v/>
       </c>
@@ -11700,7 +11913,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H152">
+  <conditionalFormatting sqref="H12:H155">
     <cfRule type="expression" dxfId="4" priority="2">
       <formula>IF($W12 = -1, 1, 0)</formula>
     </cfRule>
@@ -11710,7 +11923,7 @@
       <formula>IF($W12 &gt;= $E$18, 1, 0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P12:V152">
+  <conditionalFormatting sqref="P12:V155">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="TRALSE">
       <formula>NOT(ISERROR(SEARCH("TRALSE",P12)))</formula>
     </cfRule>
@@ -11724,7 +11937,7 @@
       <formula>NOT(ISERROR(SEARCH("TRUE",P12)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W12:W152">
+  <conditionalFormatting sqref="W12:W155">
     <cfRule type="cellIs" priority="77" stopIfTrue="1" operator="equal">
       <formula>-1</formula>
     </cfRule>
@@ -11737,7 +11950,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X12:X152">
+  <conditionalFormatting sqref="X12:X155">
     <cfRule type="expression" priority="9" stopIfTrue="1">
       <formula>IF(COUNTA(P12:W12)&gt;0,0,1)</formula>
     </cfRule>

--- a/To Add v2/00 Things To Add.xlsx
+++ b/To Add v2/00 Things To Add.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Danakil_KiCad_DB\To Add v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9258A3C6-27F6-434B-AAEA-308199999A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BD5C4D-6252-4039-BC13-CC7BA0DFC4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="7725" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="223">
   <si>
     <t>Table Name</t>
   </si>
@@ -621,9 +621,6 @@
     <t>Burried Zener</t>
   </si>
   <si>
-    <t>Misc</t>
-  </si>
-  <si>
     <t>Jumpers</t>
   </si>
   <si>
@@ -724,6 +721,12 @@
   </si>
   <si>
     <t>Tape</t>
+  </si>
+  <si>
+    <t>Zener</t>
+  </si>
+  <si>
+    <t>General Purpose</t>
   </si>
 </sst>
 </file>
@@ -858,7 +861,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -933,6 +936,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1042,10 +1046,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}" name="Table1" displayName="Table1" ref="H11:AE155" totalsRowShown="0">
-  <autoFilter ref="H11:AE155" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H12:AE155">
-    <sortCondition descending="1" ref="W11:W155"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}" name="Table1" displayName="Table1" ref="H11:AE156" totalsRowShown="0">
+  <autoFilter ref="H11:AE156" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H12:AE156">
+    <sortCondition descending="1" ref="W11:W156"/>
   </sortState>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{24CA07BC-B564-425C-A1C9-824F8759E630}" name="Table Name"/>
@@ -1356,7 +1360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AE155"/>
+  <dimension ref="B1:AE156"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="14.08984375" customWidth="1"/>
@@ -1404,7 +1408,7 @@
       </c>
       <c r="E3" s="13">
         <f>COUNTA(H12:H10039)</f>
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I3"/>
       <c r="P3"/>
@@ -1432,7 +1436,7 @@
       </c>
       <c r="E5" s="14">
         <f>COUNTIF(W12:W10040,"&gt;-1")</f>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G5" t="s">
         <v>49</v>
@@ -1440,31 +1444,31 @@
       <c r="I5"/>
       <c r="P5" s="8">
         <f t="shared" ref="P5:V5" si="0">100*COUNTIF(P12:P9999,"=TRUE")/COUNTA(P12:P9999)</f>
-        <v>38.888888888888886</v>
+        <v>40</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="0"/>
-        <v>38.888888888888886</v>
+        <v>39.310344827586206</v>
       </c>
       <c r="R5" s="8">
         <f t="shared" si="0"/>
-        <v>38.888888888888886</v>
+        <v>39.310344827586206</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="0"/>
-        <v>43.055555555555557</v>
+        <v>44.827586206896555</v>
       </c>
       <c r="T5" s="8">
         <f t="shared" si="0"/>
-        <v>46.527777777777779</v>
+        <v>46.896551724137929</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" si="0"/>
-        <v>66.666666666666671</v>
+        <v>66.896551724137936</v>
       </c>
       <c r="V5" s="8">
         <f t="shared" si="0"/>
-        <v>27.777777777777779</v>
+        <v>27.586206896551722</v>
       </c>
     </row>
     <row r="6" spans="2:31">
@@ -1475,13 +1479,13 @@
       </c>
       <c r="E6" s="14">
         <f>COUNTIF(X12:X10038,"&gt;0") -E4</f>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I6"/>
       <c r="P6"/>
       <c r="S6">
         <f>COUNTIF(S12:S9999,"=TRUE")</f>
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="2:31">
@@ -1492,7 +1496,7 @@
       </c>
       <c r="E7" s="15">
         <f>(COUNTIF(P12:V10039,"=TRUE")/COUNTA(P12:V10039))*100</f>
-        <v>42.956349206349202</v>
+        <v>43.546798029556648</v>
       </c>
       <c r="I7"/>
       <c r="P7"/>
@@ -1508,7 +1512,7 @@
       </c>
       <c r="E8" s="13">
         <f>P5</f>
-        <v>38.888888888888886</v>
+        <v>40</v>
       </c>
       <c r="I8"/>
       <c r="P8"/>
@@ -1525,7 +1529,7 @@
       </c>
       <c r="E9" s="14">
         <f>Q5</f>
-        <v>38.888888888888886</v>
+        <v>39.310344827586206</v>
       </c>
       <c r="I9"/>
       <c r="P9"/>
@@ -1550,7 +1554,7 @@
       </c>
       <c r="E10" s="15">
         <f>R5</f>
-        <v>38.888888888888886</v>
+        <v>39.310344827586206</v>
       </c>
       <c r="I10" s="19" t="s">
         <v>8</v>
@@ -1589,11 +1593,11 @@
         <v>13</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E11" s="13">
         <f>S5</f>
-        <v>43.055555555555557</v>
+        <v>44.827586206896555</v>
       </c>
       <c r="H11" t="s">
         <v>0</v>
@@ -1672,24 +1676,24 @@
       <c r="B12" s="18"/>
       <c r="C12" s="25"/>
       <c r="D12" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E12" s="14">
         <f>T5</f>
-        <v>46.527777777777779</v>
+        <v>46.896551724137929</v>
       </c>
       <c r="H12" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Tape</v>
+        <v>Voltage References - General Purpose</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>45</v>
+        <v>185</v>
       </c>
       <c r="J12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P12" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -1698,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
@@ -1714,15 +1718,15 @@
       </c>
       <c r="X12" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Thermal - </v>
+        <v xml:space="preserve">Voltage References - </v>
       </c>
       <c r="Z12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Tape</v>
+        <v>General Purpose</v>
       </c>
       <c r="AA12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -1749,21 +1753,21 @@
       <c r="B13" s="18"/>
       <c r="C13" s="26"/>
       <c r="D13" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E13" s="15">
         <f>U5</f>
-        <v>66.666666666666671</v>
+        <v>66.896551724137936</v>
       </c>
       <c r="H13" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Sensors - Temperature - Digital</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K13" t="s">
         <v>98</v>
@@ -1778,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="b">
         <v>0</v>
@@ -1794,7 +1798,7 @@
       </c>
       <c r="X13" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y13" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -1835,57 +1839,60 @@
       </c>
       <c r="E14" s="13">
         <f>COUNTIF(W12:W9999,"=0")</f>
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H14" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Paste</v>
+        <v>Discreet - Diodes - Zener</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s">
-        <v>219</v>
+        <v>90</v>
+      </c>
+      <c r="K14" t="s">
+        <v>221</v>
       </c>
       <c r="P14" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="5" t="b">
         <v>1</v>
       </c>
       <c r="T14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V14" t="s">
+        <v>184</v>
       </c>
       <c r="W14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Thermal - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Paste</v>
+        <v xml:space="preserve">Diodes - </v>
       </c>
       <c r="AA14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Zener</v>
       </c>
       <c r="AB14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1912,17 +1919,20 @@
       </c>
       <c r="E15" s="14">
         <f>COUNTIF(W12:W9999,"&gt;0")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Glue</v>
+        <v>Transformer - Power - PCB Mount</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s">
-        <v>220</v>
+        <v>88</v>
+      </c>
+      <c r="K15" t="s">
+        <v>69</v>
       </c>
       <c r="P15" s="6" t="b">
         <v>0</v>
@@ -1946,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="W15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
@@ -1954,15 +1964,15 @@
       </c>
       <c r="Y15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Thermal - </v>
+        <v xml:space="preserve">Transformer - </v>
       </c>
       <c r="Z15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Glue</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>PCB Mount</v>
       </c>
       <c r="AB15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1988,57 +1998,60 @@
       </c>
       <c r="E16" s="14" cm="1">
         <f t="array" ref="E16">SUM(IF(W12:W9999 &gt; 0,X12:X9999,0))/COUNTIF(W12:W9999,"&gt;0")</f>
-        <v>3.5714285714285712</v>
+        <v>21.428571428571427</v>
       </c>
       <c r="H16" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Inductors - Common Mode Choke</v>
+        <v>Transformer - Power - Chasis Mount</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="J16" t="s">
-        <v>80</v>
+        <v>88</v>
+      </c>
+      <c r="K16" t="s">
+        <v>86</v>
       </c>
       <c r="P16" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="b">
-        <v>1</v>
-      </c>
-      <c r="V16" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <v>0</v>
       </c>
       <c r="W16">
         <v>0</v>
       </c>
       <c r="X16" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Inductors - </v>
+        <v xml:space="preserve">Transformer - </v>
       </c>
       <c r="Z16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Common Mode Choke</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Chasis Mount</v>
       </c>
       <c r="AB16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2064,67 +2077,61 @@
       </c>
       <c r="E17" s="14" cm="1">
         <f t="array" ref="E17">SUM(IF(W12:W9999 =E18,X12:X9999,0))/SUM(IF(W12:W9997 =E18,1,0))</f>
-        <v>0</v>
+        <v>21.428571428571427</v>
       </c>
       <c r="H17" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - PCB Mount - DC-DC - Isolated</v>
+        <v>Thermal - Tape</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="J17" t="s">
-        <v>69</v>
-      </c>
-      <c r="K17" t="s">
-        <v>83</v>
-      </c>
-      <c r="L17" t="s">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="P17" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="b">
-        <v>1</v>
-      </c>
-      <c r="V17" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
       </c>
       <c r="W17">
         <v>0</v>
       </c>
       <c r="X17" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Thermal - </v>
       </c>
       <c r="Z17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">PCB Mount - </v>
+        <v>Tape</v>
       </c>
       <c r="AA17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">DC-DC - </v>
+        <v/>
       </c>
       <c r="AB17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Isolated</v>
+        <v/>
       </c>
       <c r="AC17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2149,56 +2156,53 @@
       </c>
       <c r="H18" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - ADC</v>
+        <v>Thermal - Paste</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
-      </c>
-      <c r="K18" t="s">
-        <v>114</v>
+        <v>218</v>
       </c>
       <c r="P18" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="5" t="b">
         <v>1</v>
       </c>
       <c r="T18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="b">
-        <v>1</v>
-      </c>
-      <c r="V18" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
       </c>
       <c r="W18">
         <v>0</v>
       </c>
       <c r="X18" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Thermal - </v>
       </c>
       <c r="Z18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v>Paste</v>
       </c>
       <c r="AA18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>ADC</v>
+        <v/>
       </c>
       <c r="AB18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2220,13 +2224,13 @@
     <row r="19" spans="3:31">
       <c r="H19" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Isolators - Optoisolator</v>
+        <v>Thermal - Glue</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="J19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P19" s="6" t="b">
         <v>0</v>
@@ -2258,11 +2262,11 @@
       </c>
       <c r="Y19" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Isolators - </v>
+        <v xml:space="preserve">Thermal - </v>
       </c>
       <c r="Z19" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Optoisolator</v>
+        <v>Glue</v>
       </c>
       <c r="AA19" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -2288,16 +2292,16 @@
     <row r="20" spans="3:31">
       <c r="H20" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Switching Regulator</v>
+        <v>Sensors - Touch Sensor - Capacitive</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J20" t="s">
-        <v>88</v>
+        <v>210</v>
+      </c>
+      <c r="J20" s="30" t="s">
+        <v>157</v>
       </c>
       <c r="K20" t="s">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="P20" s="6" t="b">
         <v>0</v>
@@ -2315,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="b">
         <v>0</v>
@@ -2325,19 +2329,19 @@
       </c>
       <c r="X20" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Sensors - </v>
       </c>
       <c r="Z20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Touch Sensor - </v>
       </c>
       <c r="AA20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Switching Regulator</v>
+        <v>Capacitive</v>
       </c>
       <c r="AB20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2359,63 +2363,60 @@
     <row r="21" spans="3:31">
       <c r="H21" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - Logic_Out</v>
+        <v>Sensors - Temperature - RTDs</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="J21" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="K21" t="s">
-        <v>125</v>
-      </c>
-      <c r="L21" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="P21" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T21" t="b">
-        <v>1</v>
-      </c>
-      <c r="U21" t="b">
-        <v>1</v>
-      </c>
-      <c r="V21" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="T21" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
       </c>
       <c r="W21">
         <v>0</v>
       </c>
       <c r="X21" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Sensors - </v>
       </c>
       <c r="Z21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v xml:space="preserve">Temperature - </v>
       </c>
       <c r="AA21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Fixed - </v>
+        <v>RTDs</v>
       </c>
       <c r="AB21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Logic_Out</v>
+        <v/>
       </c>
       <c r="AC21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2433,49 +2434,49 @@
     <row r="22" spans="3:31">
       <c r="H22" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Test Points</v>
+        <v>Sensors - Humidity</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="J22" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="P22" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="b">
-        <v>1</v>
-      </c>
-      <c r="V22" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
       </c>
       <c r="W22">
         <v>0</v>
       </c>
       <c r="X22" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Sensors - </v>
       </c>
       <c r="Z22" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Test Points</v>
+        <v>Humidity</v>
       </c>
       <c r="AA22" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -2501,56 +2502,53 @@
     <row r="23" spans="3:31">
       <c r="H23" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Standoffs  - SMD</v>
+        <v>Sensors - Capacitance To Digital</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="J23" t="s">
-        <v>134</v>
-      </c>
-      <c r="K23" t="s">
-        <v>44</v>
+        <v>211</v>
       </c>
       <c r="P23" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" t="b">
-        <v>1</v>
-      </c>
-      <c r="V23" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
       </c>
       <c r="W23">
         <v>0</v>
       </c>
       <c r="X23" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Sensors - </v>
       </c>
       <c r="Z23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standoffs  - </v>
+        <v>Capacitance To Digital</v>
       </c>
       <c r="AA23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SMD</v>
+        <v/>
       </c>
       <c r="AB23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2572,53 +2570,56 @@
     <row r="24" spans="3:31">
       <c r="H24" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Isolators - Digital</v>
+        <v>Resistors - Single - Through Hole</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>98</v>
+        <v>43</v>
+      </c>
+      <c r="K24" t="s">
+        <v>52</v>
       </c>
       <c r="P24" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="b">
-        <v>1</v>
-      </c>
-      <c r="V24" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <v>0</v>
       </c>
       <c r="W24">
         <v>0</v>
       </c>
       <c r="X24" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Isolators - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Digital</v>
+        <v xml:space="preserve">Single - </v>
       </c>
       <c r="AA24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Through Hole</v>
       </c>
       <c r="AB24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2640,49 +2641,49 @@
     <row r="25" spans="3:31">
       <c r="H25" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Capacitors - Polarized</v>
+        <v>Resistors - Network</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="J25" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="P25" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V25" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
       </c>
       <c r="W25">
         <v>0</v>
       </c>
       <c r="X25" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Capacitors - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Polarized</v>
+        <v>Network</v>
       </c>
       <c r="AA25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -2708,60 +2709,63 @@
     <row r="26" spans="3:31">
       <c r="H26" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - ICs - DDS</v>
+        <v>PSUs - PCB Mount - DC-DC - Isolated</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="J26" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="K26" t="s">
-        <v>123</v>
+        <v>83</v>
+      </c>
+      <c r="L26" t="s">
+        <v>84</v>
       </c>
       <c r="P26" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="b">
         <v>1</v>
       </c>
-      <c r="V26" t="b">
-        <v>0</v>
+      <c r="V26" t="s">
+        <v>184</v>
       </c>
       <c r="W26">
         <v>0</v>
       </c>
       <c r="X26" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">PCB Mount - </v>
       </c>
       <c r="AA26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DDS</v>
+        <v xml:space="preserve">DC-DC - </v>
       </c>
       <c r="AB26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Isolated</v>
       </c>
       <c r="AC26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2779,19 +2783,16 @@
     <row r="27" spans="3:31">
       <c r="H27" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - Ceramic Resonator</v>
+        <v>PSUs - PCB Mount - AC-DC</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="J27" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="K27" t="s">
-        <v>125</v>
-      </c>
-      <c r="L27" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="P27" s="6" t="b">
         <v>0</v>
@@ -2806,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="b">
         <v>0</v>
@@ -2818,24 +2819,23 @@
         <v>0</v>
       </c>
       <c r="X27" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v xml:space="preserve">PCB Mount - </v>
       </c>
       <c r="AA27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Fixed - </v>
+        <v>AC-DC</v>
       </c>
       <c r="AB27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Ceramic Resonator</v>
+        <v/>
       </c>
       <c r="AC27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2853,19 +2853,16 @@
     <row r="28" spans="3:31">
       <c r="H28" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - TCXO</v>
+        <v>PSUs - Chasis Mount - DC-DC</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="J28" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="K28" t="s">
-        <v>125</v>
-      </c>
-      <c r="L28" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="P28" s="6" t="b">
         <v>0</v>
@@ -2880,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" t="b">
         <v>0</v>
@@ -2893,23 +2890,23 @@
       </c>
       <c r="X28" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v xml:space="preserve">Chasis Mount - </v>
       </c>
       <c r="AA28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Fixed - </v>
+        <v>DC-DC</v>
       </c>
       <c r="AB28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>TCXO</v>
+        <v/>
       </c>
       <c r="AC28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2927,19 +2924,16 @@
     <row r="29" spans="3:31">
       <c r="H29" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - VCOs - VCO</v>
+        <v>PSUs - Chasis Mount - AC-DC</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="J29" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="K29" t="s">
-        <v>129</v>
-      </c>
-      <c r="L29" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="P29" s="6" t="b">
         <v>0</v>
@@ -2954,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="b">
         <v>0</v>
@@ -2967,23 +2961,23 @@
       </c>
       <c r="X29" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v xml:space="preserve">Chasis Mount - </v>
       </c>
       <c r="AA29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">VCOs - </v>
+        <v>AC-DC</v>
       </c>
       <c r="AB29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>VCO</v>
+        <v/>
       </c>
       <c r="AC29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -3001,19 +2995,13 @@
     <row r="30" spans="3:31">
       <c r="H30" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - VCOs - VCTCXO</v>
+        <v>Protection - PolyFuses</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="J30" t="s">
-        <v>124</v>
-      </c>
-      <c r="K30" t="s">
-        <v>129</v>
-      </c>
-      <c r="L30" t="s">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="P30" s="6" t="b">
         <v>0</v>
@@ -3025,13 +3013,13 @@
         <v>0</v>
       </c>
       <c r="S30" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="b">
         <v>1</v>
       </c>
       <c r="U30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" t="b">
         <v>0</v>
@@ -3041,23 +3029,23 @@
       </c>
       <c r="X30" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="Y30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v>PolyFuses</v>
       </c>
       <c r="AA30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">VCOs - </v>
+        <v/>
       </c>
       <c r="AB30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>VCTCXO</v>
+        <v/>
       </c>
       <c r="AC30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -3075,63 +3063,60 @@
     <row r="31" spans="3:31">
       <c r="H31" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - VCOs - VCXO</v>
+        <v>Mechanical  - Standoffs  - SMD</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="J31" t="s">
-        <v>124</v>
+        <v>133</v>
+      </c>
+      <c r="J31" s="30" t="s">
+        <v>134</v>
       </c>
       <c r="K31" t="s">
-        <v>129</v>
-      </c>
-      <c r="L31" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="P31" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="b">
         <v>1</v>
       </c>
       <c r="U31" t="b">
-        <v>0</v>
-      </c>
-      <c r="V31" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V31" t="s">
+        <v>184</v>
       </c>
       <c r="W31">
         <v>0</v>
       </c>
       <c r="X31" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v xml:space="preserve">Standoffs  - </v>
       </c>
       <c r="AA31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">VCOs - </v>
+        <v>SMD</v>
       </c>
       <c r="AB31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>VCXO</v>
+        <v/>
       </c>
       <c r="AC31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -3149,13 +3134,16 @@
     <row r="32" spans="3:31">
       <c r="H32" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Banana Jacks</v>
+        <v>Mechanical  - Standoffs  - M_F</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="J32" t="s">
-        <v>59</v>
+        <v>134</v>
+      </c>
+      <c r="K32" t="s">
+        <v>141</v>
       </c>
       <c r="P32" s="6" t="b">
         <v>0</v>
@@ -3187,15 +3175,15 @@
       </c>
       <c r="Y32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Banana Jacks</v>
+        <v xml:space="preserve">Standoffs  - </v>
       </c>
       <c r="AA32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>M_F</v>
       </c>
       <c r="AB32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3217,56 +3205,56 @@
     <row r="33" spans="8:31">
       <c r="H33" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Battery Holders - Coin Cell</v>
+        <v>Mechanical  - Standoffs  - F_F</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="J33" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="K33" t="s">
-        <v>208</v>
+        <v>142</v>
       </c>
       <c r="P33" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="b">
-        <v>1</v>
-      </c>
-      <c r="V33" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
       </c>
       <c r="W33">
         <v>0</v>
       </c>
       <c r="X33" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Battery Holders - </v>
+        <v xml:space="preserve">Standoffs  - </v>
       </c>
       <c r="AA33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Coin Cell</v>
+        <v>F_F</v>
       </c>
       <c r="AB33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3288,16 +3276,13 @@
     <row r="34" spans="8:31">
       <c r="H34" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Battery Holders - Cylindrical</v>
+        <v>Mechanical  - Spacers</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="J34" t="s">
-        <v>207</v>
-      </c>
-      <c r="K34" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="P34" s="6" t="b">
         <v>0</v>
@@ -3329,15 +3314,15 @@
       </c>
       <c r="Y34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Battery Holders - </v>
+        <v>Spacers</v>
       </c>
       <c r="AA34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Cylindrical</v>
+        <v/>
       </c>
       <c r="AB34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3359,13 +3344,13 @@
     <row r="35" spans="8:31">
       <c r="H35" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Card Edge</v>
+        <v>Mechanical  - Nuts</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="J35" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="P35" s="6" t="b">
         <v>0</v>
@@ -3397,11 +3382,11 @@
       </c>
       <c r="Y35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Card Edge</v>
+        <v>Nuts</v>
       </c>
       <c r="AA35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3427,31 +3412,31 @@
     <row r="36" spans="8:31">
       <c r="H36" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Coaxial</v>
+        <v>Mechanical  - Heat Shrink</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="J36" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="P36" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" s="5" t="b">
         <v>1</v>
       </c>
       <c r="T36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="b">
         <v>0</v>
@@ -3461,15 +3446,15 @@
       </c>
       <c r="X36" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Coaxial</v>
+        <v>Heat Shrink</v>
       </c>
       <c r="AA36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3495,16 +3480,13 @@
     <row r="37" spans="8:31">
       <c r="H37" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Backshells</v>
+        <v>LEDs - RGB</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="J37" t="s">
-        <v>66</v>
-      </c>
-      <c r="K37" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="P37" s="6" t="b">
         <v>0</v>
@@ -3519,10 +3501,10 @@
         <v>0</v>
       </c>
       <c r="T37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" t="b">
         <v>0</v>
@@ -3532,19 +3514,19 @@
       </c>
       <c r="X37" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">LEDs - </v>
       </c>
       <c r="Z37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v>RGB</v>
       </c>
       <c r="AA37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Backshells</v>
+        <v/>
       </c>
       <c r="AB37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3566,22 +3548,13 @@
     <row r="38" spans="8:31">
       <c r="H38" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Hybrid - Female - Inline</v>
+        <v>Isolators - Optoisolator</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="J38" t="s">
-        <v>66</v>
-      </c>
-      <c r="K38" t="s">
-        <v>64</v>
-      </c>
-      <c r="L38" t="s">
-        <v>68</v>
-      </c>
-      <c r="M38" t="s">
-        <v>70</v>
+        <v>217</v>
       </c>
       <c r="P38" s="6" t="b">
         <v>0</v>
@@ -3613,23 +3586,23 @@
       </c>
       <c r="Y38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Isolators - </v>
       </c>
       <c r="Z38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v>Optoisolator</v>
       </c>
       <c r="AA38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Hybrid - </v>
+        <v/>
       </c>
       <c r="AB38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Female - </v>
+        <v/>
       </c>
       <c r="AC38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>Inline</v>
+        <v/>
       </c>
       <c r="AD38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3643,70 +3616,61 @@
     <row r="39" spans="8:31">
       <c r="H39" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Hybrid - Male - Inline</v>
+        <v>Isolators - Digital</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J39" t="s">
-        <v>66</v>
-      </c>
-      <c r="K39" t="s">
-        <v>64</v>
-      </c>
-      <c r="L39" t="s">
-        <v>67</v>
-      </c>
-      <c r="M39" t="s">
-        <v>70</v>
+        <v>97</v>
+      </c>
+      <c r="J39" s="30" t="s">
+        <v>98</v>
       </c>
       <c r="P39" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T39" t="b">
-        <v>0</v>
-      </c>
-      <c r="U39" t="b">
-        <v>0</v>
-      </c>
-      <c r="V39" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T39" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U39" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V39" t="s">
+        <v>184</v>
       </c>
       <c r="W39">
         <v>0</v>
       </c>
       <c r="X39" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Isolators - </v>
       </c>
       <c r="Z39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v>Digital</v>
       </c>
       <c r="AA39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Hybrid - </v>
+        <v/>
       </c>
       <c r="AB39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Male - </v>
+        <v/>
       </c>
       <c r="AC39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>Inline</v>
+        <v/>
       </c>
       <c r="AD39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3720,22 +3684,13 @@
     <row r="40" spans="8:31">
       <c r="H40" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Female - Inline</v>
+        <v>Isolators - Analog</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="J40" t="s">
-        <v>66</v>
-      </c>
-      <c r="K40" t="s">
-        <v>63</v>
-      </c>
-      <c r="L40" t="s">
-        <v>68</v>
-      </c>
-      <c r="M40" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="P40" s="6" t="b">
         <v>0</v>
@@ -3753,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" t="b">
         <v>0</v>
@@ -3763,27 +3718,27 @@
       </c>
       <c r="X40" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Isolators - </v>
       </c>
       <c r="Z40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v>Analog</v>
       </c>
       <c r="AA40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v/>
       </c>
       <c r="AB40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Female - </v>
+        <v/>
       </c>
       <c r="AC40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>Inline</v>
+        <v/>
       </c>
       <c r="AD40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3797,70 +3752,61 @@
     <row r="41" spans="8:31">
       <c r="H41" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Female - PCB Mount</v>
+        <v>Inductors - Common Mode Choke</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J41" t="s">
-        <v>66</v>
-      </c>
-      <c r="K41" t="s">
-        <v>63</v>
-      </c>
-      <c r="L41" t="s">
-        <v>68</v>
-      </c>
-      <c r="M41" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="P41" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U41" t="b">
-        <v>0</v>
-      </c>
-      <c r="V41" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V41" t="s">
+        <v>184</v>
       </c>
       <c r="W41">
         <v>0</v>
       </c>
       <c r="X41" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Inductors - </v>
       </c>
       <c r="Z41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v>Common Mode Choke</v>
       </c>
       <c r="AA41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v/>
       </c>
       <c r="AB41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Female - </v>
+        <v/>
       </c>
       <c r="AC41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>PCB Mount</v>
+        <v/>
       </c>
       <c r="AD41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3874,70 +3820,61 @@
     <row r="42" spans="8:31">
       <c r="H42" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Male - Inline</v>
+        <v>ICs - RTCs</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="J42" t="s">
-        <v>66</v>
-      </c>
-      <c r="K42" t="s">
-        <v>63</v>
-      </c>
-      <c r="L42" t="s">
-        <v>67</v>
-      </c>
-      <c r="M42" t="s">
-        <v>70</v>
+        <v>209</v>
       </c>
       <c r="P42" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" t="b">
-        <v>0</v>
-      </c>
-      <c r="V42" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V42" t="s">
+        <v>184</v>
       </c>
       <c r="W42">
         <v>0</v>
       </c>
       <c r="X42" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v>RTCs</v>
       </c>
       <c r="AA42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v/>
       </c>
       <c r="AB42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Male - </v>
+        <v/>
       </c>
       <c r="AC42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>Inline</v>
+        <v/>
       </c>
       <c r="AD42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -3951,22 +3888,16 @@
     <row r="43" spans="8:31">
       <c r="H43" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Male - PCB Mount</v>
+        <v>ICs - Power - Switching Regulator</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="J43" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s">
-        <v>63</v>
-      </c>
-      <c r="L43" t="s">
-        <v>67</v>
-      </c>
-      <c r="M43" t="s">
-        <v>69</v>
+        <v>216</v>
       </c>
       <c r="P43" s="6" t="b">
         <v>0</v>
@@ -3984,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" t="b">
         <v>0</v>
@@ -3994,27 +3925,27 @@
       </c>
       <c r="X43" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v>Switching Regulator</v>
       </c>
       <c r="AB43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Male - </v>
+        <v/>
       </c>
       <c r="AC43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>PCB Mount</v>
+        <v/>
       </c>
       <c r="AD43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -4028,13 +3959,16 @@
     <row r="44" spans="8:31">
       <c r="H44" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Flat Flex</v>
+        <v>ICs - Power - Switching Controler</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="J44" t="s">
-        <v>62</v>
+        <v>88</v>
+      </c>
+      <c r="K44" t="s">
+        <v>104</v>
       </c>
       <c r="P44" s="6" t="b">
         <v>0</v>
@@ -4046,13 +3980,13 @@
         <v>0</v>
       </c>
       <c r="S44" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" t="b">
         <v>0</v>
       </c>
       <c r="U44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" t="b">
         <v>0</v>
@@ -4066,15 +4000,15 @@
       </c>
       <c r="Y44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Flat Flex</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Switching Controler</v>
       </c>
       <c r="AB44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4096,13 +4030,16 @@
     <row r="45" spans="8:31">
       <c r="H45" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Jumpers</v>
+        <v>ICs - Power - Supply Sequencing</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="J45" t="s">
-        <v>188</v>
+        <v>88</v>
+      </c>
+      <c r="K45" t="s">
+        <v>199</v>
       </c>
       <c r="P45" s="6" t="b">
         <v>0</v>
@@ -4134,15 +4071,15 @@
       </c>
       <c r="Y45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Jumpers</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Supply Sequencing</v>
       </c>
       <c r="AB45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4164,13 +4101,16 @@
     <row r="46" spans="8:31">
       <c r="H46" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Power Entry Modules</v>
+        <v>ICs - Power - Half&amp;H Bridge</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="J46" t="s">
-        <v>60</v>
+        <v>88</v>
+      </c>
+      <c r="K46" t="s">
+        <v>139</v>
       </c>
       <c r="P46" s="6" t="b">
         <v>0</v>
@@ -4188,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" t="b">
         <v>0</v>
@@ -4198,19 +4138,19 @@
       </c>
       <c r="X46" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Power Entry Modules</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Half&amp;H Bridge</v>
       </c>
       <c r="AB46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4232,13 +4172,19 @@
     <row r="47" spans="8:31">
       <c r="H47" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Screw Connectors</v>
+        <v>ICs - Power - Gate Driver - Non Isolated</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="J47" t="s">
-        <v>53</v>
+        <v>88</v>
+      </c>
+      <c r="K47" t="s">
+        <v>101</v>
+      </c>
+      <c r="L47" t="s">
+        <v>102</v>
       </c>
       <c r="P47" s="6" t="b">
         <v>0</v>
@@ -4256,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="U47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" t="b">
         <v>0</v>
@@ -4266,23 +4212,23 @@
       </c>
       <c r="X47" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Screw Connectors</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Gate Driver - </v>
       </c>
       <c r="AB47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Non Isolated</v>
       </c>
       <c r="AC47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4300,57 +4246,63 @@
     <row r="48" spans="8:31">
       <c r="H48" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - SD Card Socket</v>
+        <v>ICs - Power - Gate Driver - Isolated</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="J48" t="s">
-        <v>56</v>
+        <v>88</v>
+      </c>
+      <c r="K48" t="s">
+        <v>101</v>
+      </c>
+      <c r="L48" t="s">
+        <v>84</v>
       </c>
       <c r="P48" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" t="b">
         <v>1</v>
       </c>
-      <c r="V48" t="s">
-        <v>184</v>
+      <c r="V48" t="b">
+        <v>0</v>
       </c>
       <c r="W48">
         <v>0</v>
       </c>
       <c r="X48" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>SD Card Socket</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Gate Driver - </v>
       </c>
       <c r="AB48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Isolated</v>
       </c>
       <c r="AC48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4368,56 +4320,56 @@
     <row r="49" spans="8:31">
       <c r="H49" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Terminal Blocks - Wire to Board</v>
+        <v>ICs - Memory - SD Card</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="J49" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="K49" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="P49" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49" t="b">
         <v>1</v>
       </c>
-      <c r="V49" t="s">
-        <v>184</v>
+      <c r="V49" t="b">
+        <v>0</v>
       </c>
       <c r="W49">
         <v>0</v>
       </c>
       <c r="X49" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Terminal Blocks - </v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Wire to Board</v>
+        <v>SD Card</v>
       </c>
       <c r="AB49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4439,53 +4391,56 @@
     <row r="50" spans="8:31">
       <c r="H50" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Contacts - Banana Plugs</v>
+        <v>ICs - Memory - FLASH</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J50" t="s">
-        <v>78</v>
+        <v>110</v>
+      </c>
+      <c r="K50" t="s">
+        <v>204</v>
       </c>
       <c r="P50" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="b">
-        <v>0</v>
-      </c>
-      <c r="V50" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>184</v>
       </c>
       <c r="W50">
         <v>0</v>
       </c>
       <c r="X50" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Contacts - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Banana Plugs</v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>FLASH</v>
       </c>
       <c r="AB50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4507,53 +4462,56 @@
     <row r="51" spans="8:31">
       <c r="H51" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Contacts - Ferrules</v>
+        <v>ICs - Memory - EEPROM</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J51" t="s">
-        <v>76</v>
+        <v>110</v>
+      </c>
+      <c r="K51" t="s">
+        <v>111</v>
       </c>
       <c r="P51" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U51" t="b">
-        <v>0</v>
-      </c>
-      <c r="V51" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V51" t="s">
+        <v>184</v>
       </c>
       <c r="W51">
         <v>0</v>
       </c>
       <c r="X51" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Contacts - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Ferrules</v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>EEPROM</v>
       </c>
       <c r="AB51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4575,13 +4533,16 @@
     <row r="52" spans="8:31">
       <c r="H52" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Contacts - Ring Terminals</v>
+        <v>ICs - Memory - DRAM</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J52" t="s">
-        <v>77</v>
+        <v>110</v>
+      </c>
+      <c r="K52" t="s">
+        <v>113</v>
       </c>
       <c r="P52" s="6" t="b">
         <v>0</v>
@@ -4599,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="U52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" t="b">
         <v>0</v>
@@ -4609,19 +4570,19 @@
       </c>
       <c r="X52" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Contacts - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Ring Terminals</v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>DRAM</v>
       </c>
       <c r="AB52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4643,16 +4604,16 @@
     <row r="53" spans="8:31">
       <c r="H53" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Diodes - Standard</v>
+        <v>ICs - Logic - Translators</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J53" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="K53" t="s">
-        <v>63</v>
+        <v>176</v>
       </c>
       <c r="P53" s="6" t="b">
         <v>0</v>
@@ -4667,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U53" t="b">
         <v>1</v>
@@ -4680,19 +4641,19 @@
       </c>
       <c r="X53" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Diodes - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Standard</v>
+        <v>Translators</v>
       </c>
       <c r="AB53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4714,19 +4675,19 @@
     <row r="54" spans="8:31">
       <c r="H54" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - BJT - PNP</v>
+        <v>ICs - Logic - Switch - Digital</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J54" t="s">
-        <v>195</v>
+        <v>118</v>
       </c>
       <c r="K54" t="s">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="L54" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="P54" s="6" t="b">
         <v>0</v>
@@ -4758,19 +4719,19 @@
       </c>
       <c r="Y54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">BJT - </v>
+        <v xml:space="preserve">Switch - </v>
       </c>
       <c r="AB54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>PNP</v>
+        <v>Digital</v>
       </c>
       <c r="AC54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4788,16 +4749,19 @@
     <row r="55" spans="8:31">
       <c r="H55" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - GaNFET</v>
+        <v>ICs - Logic - Shift Registers - SIPO</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J55" t="s">
-        <v>195</v>
+        <v>118</v>
       </c>
       <c r="K55" t="s">
-        <v>94</v>
+        <v>170</v>
+      </c>
+      <c r="L55" t="s">
+        <v>171</v>
       </c>
       <c r="P55" s="6" t="b">
         <v>0</v>
@@ -4812,10 +4776,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" t="b">
         <v>0</v>
@@ -4829,19 +4793,19 @@
       </c>
       <c r="Y55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>GaNFET</v>
+        <v xml:space="preserve">Shift Registers - </v>
       </c>
       <c r="AB55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>SIPO</v>
       </c>
       <c r="AC55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4859,16 +4823,19 @@
     <row r="56" spans="8:31">
       <c r="H56" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - JFET</v>
+        <v>ICs - Logic - Shift Registers - PISO</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J56" t="s">
-        <v>195</v>
+        <v>118</v>
       </c>
       <c r="K56" t="s">
-        <v>96</v>
+        <v>170</v>
+      </c>
+      <c r="L56" t="s">
+        <v>172</v>
       </c>
       <c r="P56" s="6" t="b">
         <v>0</v>
@@ -4883,10 +4850,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" t="b">
         <v>0</v>
@@ -4900,19 +4867,19 @@
       </c>
       <c r="Y56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>JFET</v>
+        <v xml:space="preserve">Shift Registers - </v>
       </c>
       <c r="AB56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>PISO</v>
       </c>
       <c r="AC56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4930,31 +4897,31 @@
     <row r="57" spans="8:31">
       <c r="H57" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - MOSFET</v>
+        <v>ICs - Logic - Multivibrators</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J57" t="s">
-        <v>195</v>
+        <v>118</v>
       </c>
       <c r="K57" t="s">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="P57" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U57" t="b">
         <v>1</v>
@@ -4967,19 +4934,19 @@
       </c>
       <c r="X57" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>MOSFET</v>
+        <v>Multivibrators</v>
       </c>
       <c r="AB57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5001,16 +4968,19 @@
     <row r="58" spans="8:31">
       <c r="H58" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - SiCFET</v>
+        <v>ICs - Logic - Multiplexer - Digital</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J58" t="s">
-        <v>195</v>
+        <v>118</v>
       </c>
       <c r="K58" t="s">
-        <v>95</v>
+        <v>174</v>
+      </c>
+      <c r="L58" t="s">
+        <v>98</v>
       </c>
       <c r="P58" s="6" t="b">
         <v>0</v>
@@ -5025,10 +4995,10 @@
         <v>0</v>
       </c>
       <c r="T58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" t="b">
         <v>0</v>
@@ -5042,19 +5012,19 @@
       </c>
       <c r="Y58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SiCFET</v>
+        <v xml:space="preserve">Multiplexer - </v>
       </c>
       <c r="AB58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5072,16 +5042,16 @@
     <row r="59" spans="8:31">
       <c r="H59" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - Comparator</v>
+        <v>ICs - Logic - Level Shifters</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J59" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="K59" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="P59" s="6" t="b">
         <v>0</v>
@@ -5093,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" t="b">
         <v>0</v>
@@ -5109,7 +5079,7 @@
       </c>
       <c r="X59" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -5117,11 +5087,11 @@
       </c>
       <c r="Z59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Comparator</v>
+        <v>Level Shifters</v>
       </c>
       <c r="AB59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5143,16 +5113,16 @@
     <row r="60" spans="8:31">
       <c r="H60" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - DAC</v>
+        <v>ICs - Logic - Latches</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J60" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="K60" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="P60" s="6" t="b">
         <v>0</v>
@@ -5188,11 +5158,11 @@
       </c>
       <c r="Z60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DAC</v>
+        <v>Latches</v>
       </c>
       <c r="AB60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5214,19 +5184,19 @@
     <row r="61" spans="8:31">
       <c r="H61" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - FPGA</v>
+        <v>ICs - Logic - Gates</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J61" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K61" t="s">
-        <v>108</v>
-      </c>
-      <c r="P61" s="6" t="s">
-        <v>184</v>
+        <v>167</v>
+      </c>
+      <c r="P61" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -5235,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" t="b">
         <v>0</v>
@@ -5251,7 +5221,7 @@
       </c>
       <c r="X61" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -5259,11 +5229,11 @@
       </c>
       <c r="Z61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>FPGA</v>
+        <v>Gates</v>
       </c>
       <c r="AB61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5285,19 +5255,16 @@
     <row r="62" spans="8:31">
       <c r="H62" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - PolarFire - SOC</v>
+        <v>ICs - Logic - Flip Flops</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J62" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K62" t="s">
-        <v>109</v>
-      </c>
-      <c r="L62" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="P62" s="6" t="b">
         <v>0</v>
@@ -5333,15 +5300,15 @@
       </c>
       <c r="Z62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">PolarFire - </v>
+        <v>Flip Flops</v>
       </c>
       <c r="AB62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SOC</v>
+        <v/>
       </c>
       <c r="AC62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5359,16 +5326,19 @@
     <row r="63" spans="8:31">
       <c r="H63" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Analog Switch</v>
+        <v>ICs - Logic - Demultiplexer - Digital</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J63" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K63" t="s">
-        <v>156</v>
+        <v>175</v>
+      </c>
+      <c r="L63" t="s">
+        <v>98</v>
       </c>
       <c r="P63" s="6" t="b">
         <v>0</v>
@@ -5404,15 +5374,15 @@
       </c>
       <c r="Z63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Analog Switch</v>
+        <v xml:space="preserve">Demultiplexer - </v>
       </c>
       <c r="AB63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5430,16 +5400,19 @@
     <row r="64" spans="8:31">
       <c r="H64" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Controller</v>
+        <v>ICs - Logic - Counter - Up&amp;Down</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K64" t="s">
-        <v>161</v>
+        <v>163</v>
+      </c>
+      <c r="L64" t="s">
+        <v>165</v>
       </c>
       <c r="P64" s="6" t="b">
         <v>0</v>
@@ -5475,15 +5448,15 @@
       </c>
       <c r="Z64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Controller</v>
+        <v xml:space="preserve">Counter - </v>
       </c>
       <c r="AB64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Up&amp;Down</v>
       </c>
       <c r="AC64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5501,16 +5474,19 @@
     <row r="65" spans="8:31">
       <c r="H65" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Deserializer</v>
+        <v>ICs - Logic - Counter - Up</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J65" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K65" t="s">
-        <v>160</v>
+        <v>163</v>
+      </c>
+      <c r="L65" t="s">
+        <v>164</v>
       </c>
       <c r="P65" s="6" t="b">
         <v>0</v>
@@ -5546,15 +5522,15 @@
       </c>
       <c r="Z65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Deserializer</v>
+        <v xml:space="preserve">Counter - </v>
       </c>
       <c r="AB65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Up</v>
       </c>
       <c r="AC65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5572,16 +5548,19 @@
     <row r="66" spans="8:31">
       <c r="H66" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Drivers</v>
+        <v>ICs - Logic - Comparator - Digital</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J66" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K66" t="s">
-        <v>120</v>
+        <v>116</v>
+      </c>
+      <c r="L66" t="s">
+        <v>98</v>
       </c>
       <c r="P66" s="6" t="b">
         <v>0</v>
@@ -5617,15 +5596,15 @@
       </c>
       <c r="Z66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Drivers</v>
+        <v xml:space="preserve">Comparator - </v>
       </c>
       <c r="AB66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5643,7 +5622,7 @@
     <row r="67" spans="8:31">
       <c r="H67" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - IO Expander</v>
+        <v>ICs - Interface  - UART</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>100</v>
@@ -5652,7 +5631,7 @@
         <v>119</v>
       </c>
       <c r="K67" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="P67" s="6" t="b">
         <v>0</v>
@@ -5692,7 +5671,7 @@
       </c>
       <c r="AA67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>IO Expander</v>
+        <v>UART</v>
       </c>
       <c r="AB67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5714,7 +5693,7 @@
     <row r="68" spans="8:31">
       <c r="H68" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Recievers</v>
+        <v>ICs - Interface  - Trancievers</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>100</v>
@@ -5723,7 +5702,7 @@
         <v>119</v>
       </c>
       <c r="K68" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P68" s="6" t="b">
         <v>0</v>
@@ -5763,7 +5742,7 @@
       </c>
       <c r="AA68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Recievers</v>
+        <v>Trancievers</v>
       </c>
       <c r="AB68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5856,7 +5835,7 @@
     <row r="70" spans="8:31">
       <c r="H70" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Trancievers</v>
+        <v>ICs - Interface  - Recievers</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>100</v>
@@ -5865,7 +5844,7 @@
         <v>119</v>
       </c>
       <c r="K70" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P70" s="6" t="b">
         <v>0</v>
@@ -5905,7 +5884,7 @@
       </c>
       <c r="AA70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Trancievers</v>
+        <v>Recievers</v>
       </c>
       <c r="AB70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5927,7 +5906,7 @@
     <row r="71" spans="8:31">
       <c r="H71" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - UART</v>
+        <v>ICs - Interface  - IO Expander</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>100</v>
@@ -5936,7 +5915,7 @@
         <v>119</v>
       </c>
       <c r="K71" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="P71" s="6" t="b">
         <v>0</v>
@@ -5976,7 +5955,7 @@
       </c>
       <c r="AA71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>UART</v>
+        <v>IO Expander</v>
       </c>
       <c r="AB71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5998,19 +5977,16 @@
     <row r="72" spans="8:31">
       <c r="H72" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Comparator - Digital</v>
+        <v>ICs - Interface  - Drivers</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J72" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K72" t="s">
-        <v>116</v>
-      </c>
-      <c r="L72" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="P72" s="6" t="b">
         <v>0</v>
@@ -6046,15 +6022,15 @@
       </c>
       <c r="Z72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Comparator - </v>
+        <v>Drivers</v>
       </c>
       <c r="AB72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6072,19 +6048,16 @@
     <row r="73" spans="8:31">
       <c r="H73" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Counter - Up</v>
+        <v>ICs - Interface  - Deserializer</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K73" t="s">
-        <v>163</v>
-      </c>
-      <c r="L73" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="P73" s="6" t="b">
         <v>0</v>
@@ -6120,15 +6093,15 @@
       </c>
       <c r="Z73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Counter - </v>
+        <v>Deserializer</v>
       </c>
       <c r="AB73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Up</v>
+        <v/>
       </c>
       <c r="AC73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6146,19 +6119,16 @@
     <row r="74" spans="8:31">
       <c r="H74" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Counter - Up&amp;Down</v>
+        <v>ICs - Interface  - Controller</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J74" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K74" t="s">
-        <v>163</v>
-      </c>
-      <c r="L74" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P74" s="6" t="b">
         <v>0</v>
@@ -6194,15 +6164,15 @@
       </c>
       <c r="Z74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Counter - </v>
+        <v>Controller</v>
       </c>
       <c r="AB74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Up&amp;Down</v>
+        <v/>
       </c>
       <c r="AC74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6220,19 +6190,16 @@
     <row r="75" spans="8:31">
       <c r="H75" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Demultiplexer - Digital</v>
+        <v>ICs - Interface  - Analog Switch</v>
       </c>
       <c r="I75" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J75" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K75" t="s">
-        <v>175</v>
-      </c>
-      <c r="L75" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="P75" s="6" t="b">
         <v>0</v>
@@ -6268,15 +6235,15 @@
       </c>
       <c r="Z75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Demultiplexer - </v>
+        <v>Analog Switch</v>
       </c>
       <c r="AB75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6294,16 +6261,19 @@
     <row r="76" spans="8:31">
       <c r="H76" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Flip Flops</v>
+        <v>ICs - Embedded - PolarFire - SOC</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J76" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="K76" t="s">
-        <v>166</v>
+        <v>109</v>
+      </c>
+      <c r="L76" t="s">
+        <v>183</v>
       </c>
       <c r="P76" s="6" t="b">
         <v>0</v>
@@ -6339,15 +6309,15 @@
       </c>
       <c r="Z76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Embedded - </v>
       </c>
       <c r="AA76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Flip Flops</v>
+        <v xml:space="preserve">PolarFire - </v>
       </c>
       <c r="AB76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>SOC</v>
       </c>
       <c r="AC76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6365,19 +6335,19 @@
     <row r="77" spans="8:31">
       <c r="H77" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Gates</v>
+        <v>ICs - Embedded - FPGA</v>
       </c>
       <c r="I77" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J77" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="K77" t="s">
-        <v>167</v>
-      </c>
-      <c r="P77" s="6" t="b">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="P77" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="Q77" t="b">
         <v>0</v>
@@ -6386,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" t="b">
         <v>0</v>
@@ -6402,7 +6372,7 @@
       </c>
       <c r="X77" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6410,11 +6380,11 @@
       </c>
       <c r="Z77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Embedded - </v>
       </c>
       <c r="AA77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Gates</v>
+        <v>FPGA</v>
       </c>
       <c r="AB77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6436,16 +6406,16 @@
     <row r="78" spans="8:31">
       <c r="H78" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Latches</v>
+        <v>ICs - Analog - DAC</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J78" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="K78" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="P78" s="6" t="b">
         <v>0</v>
@@ -6481,11 +6451,11 @@
       </c>
       <c r="Z78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Latches</v>
+        <v>DAC</v>
       </c>
       <c r="AB78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6507,16 +6477,16 @@
     <row r="79" spans="8:31">
       <c r="H79" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Level Shifters</v>
+        <v>ICs - Analog - Comparator</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J79" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="K79" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="P79" s="6" t="b">
         <v>0</v>
@@ -6528,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="S79" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T79" t="b">
         <v>0</v>
@@ -6544,7 +6514,7 @@
       </c>
       <c r="X79" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6552,11 +6522,11 @@
       </c>
       <c r="Z79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Level Shifters</v>
+        <v>Comparator</v>
       </c>
       <c r="AB79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6578,47 +6548,44 @@
     <row r="80" spans="8:31">
       <c r="H80" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Multiplexer - Digital</v>
+        <v>ICs - Analog - ADC</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J80" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="K80" t="s">
-        <v>174</v>
-      </c>
-      <c r="L80" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="P80" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U80" t="b">
         <v>1</v>
       </c>
-      <c r="V80" t="b">
-        <v>0</v>
+      <c r="V80" t="s">
+        <v>184</v>
       </c>
       <c r="W80">
         <v>0</v>
       </c>
       <c r="X80" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6626,15 +6593,15 @@
       </c>
       <c r="Z80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Multiplexer - </v>
+        <v>ADC</v>
       </c>
       <c r="AB80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6652,16 +6619,16 @@
     <row r="81" spans="8:31">
       <c r="H81" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Multivibrators</v>
+        <v>Discreet - Transistors - SiCFET</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J81" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="K81" t="s">
-        <v>169</v>
+        <v>95</v>
       </c>
       <c r="P81" s="6" t="b">
         <v>0</v>
@@ -6676,10 +6643,10 @@
         <v>0</v>
       </c>
       <c r="T81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V81" t="b">
         <v>0</v>
@@ -6693,15 +6660,15 @@
       </c>
       <c r="Y81" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z81" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA81" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Multivibrators</v>
+        <v>SiCFET</v>
       </c>
       <c r="AB81" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6723,34 +6690,31 @@
     <row r="82" spans="8:31">
       <c r="H82" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Shift Registers - PISO</v>
+        <v>Discreet - Transistors - MOSFET</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J82" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="K82" t="s">
-        <v>170</v>
-      </c>
-      <c r="L82" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="P82" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U82" t="b">
         <v>1</v>
@@ -6763,23 +6727,23 @@
       </c>
       <c r="X82" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Shift Registers - </v>
+        <v>MOSFET</v>
       </c>
       <c r="AB82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>PISO</v>
+        <v/>
       </c>
       <c r="AC82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6797,19 +6761,16 @@
     <row r="83" spans="8:31">
       <c r="H83" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Shift Registers - SIPO</v>
+        <v>Discreet - Transistors - JFET</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J83" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="K83" t="s">
-        <v>170</v>
-      </c>
-      <c r="L83" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="P83" s="6" t="b">
         <v>0</v>
@@ -6824,10 +6785,10 @@
         <v>0</v>
       </c>
       <c r="T83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V83" t="b">
         <v>0</v>
@@ -6841,19 +6802,19 @@
       </c>
       <c r="Y83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Shift Registers - </v>
+        <v>JFET</v>
       </c>
       <c r="AB83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SIPO</v>
+        <v/>
       </c>
       <c r="AC83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6871,19 +6832,16 @@
     <row r="84" spans="8:31">
       <c r="H84" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Switch - Digital</v>
+        <v>Discreet - Transistors - GaNFET</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J84" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="K84" t="s">
-        <v>173</v>
-      </c>
-      <c r="L84" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="P84" s="6" t="b">
         <v>0</v>
@@ -6898,10 +6856,10 @@
         <v>0</v>
       </c>
       <c r="T84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V84" t="b">
         <v>0</v>
@@ -6915,19 +6873,19 @@
       </c>
       <c r="Y84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Switch - </v>
+        <v>GaNFET</v>
       </c>
       <c r="AB84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6945,16 +6903,19 @@
     <row r="85" spans="8:31">
       <c r="H85" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Translators</v>
+        <v>Discreet - Transistors - BJT - PNP</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J85" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="K85" t="s">
-        <v>176</v>
+        <v>92</v>
+      </c>
+      <c r="L85" t="s">
+        <v>201</v>
       </c>
       <c r="P85" s="6" t="b">
         <v>0</v>
@@ -6986,19 +6947,19 @@
       </c>
       <c r="Y85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Translators</v>
+        <v xml:space="preserve">BJT - </v>
       </c>
       <c r="AB85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>PNP</v>
       </c>
       <c r="AC85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -7016,16 +6977,16 @@
     <row r="86" spans="8:31">
       <c r="H86" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - DRAM</v>
+        <v>Discreet - Diodes - Standard</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="J86" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K86" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="P86" s="6" t="b">
         <v>0</v>
@@ -7040,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="T86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U86" t="b">
         <v>1</v>
@@ -7053,19 +7014,19 @@
       </c>
       <c r="X86" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v xml:space="preserve">Diodes - </v>
       </c>
       <c r="AA86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DRAM</v>
+        <v>Standard</v>
       </c>
       <c r="AB86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7087,56 +7048,53 @@
     <row r="87" spans="8:31">
       <c r="H87" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - EEPROM</v>
+        <v>Contacts - Ring Terminals</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J87" t="s">
-        <v>110</v>
-      </c>
-      <c r="K87" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="P87" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U87" t="b">
-        <v>1</v>
-      </c>
-      <c r="V87" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V87" t="b">
+        <v>0</v>
       </c>
       <c r="W87">
         <v>0</v>
       </c>
       <c r="X87" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Contacts - </v>
       </c>
       <c r="Z87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v>Ring Terminals</v>
       </c>
       <c r="AA87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>EEPROM</v>
+        <v/>
       </c>
       <c r="AB87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7158,56 +7116,53 @@
     <row r="88" spans="8:31">
       <c r="H88" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - FLASH</v>
+        <v>Contacts - Ferrules</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J88" t="s">
-        <v>110</v>
-      </c>
-      <c r="K88" t="s">
-        <v>205</v>
+        <v>76</v>
       </c>
       <c r="P88" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U88" t="b">
-        <v>1</v>
-      </c>
-      <c r="V88" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V88" t="b">
+        <v>0</v>
       </c>
       <c r="W88">
         <v>0</v>
       </c>
       <c r="X88" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Contacts - </v>
       </c>
       <c r="Z88" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v>Ferrules</v>
       </c>
       <c r="AA88" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>FLASH</v>
+        <v/>
       </c>
       <c r="AB88" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7229,16 +7184,13 @@
     <row r="89" spans="8:31">
       <c r="H89" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - SD Card</v>
+        <v>Contacts - Banana Plugs</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J89" t="s">
-        <v>110</v>
-      </c>
-      <c r="K89" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="P89" s="6" t="b">
         <v>0</v>
@@ -7256,7 +7208,7 @@
         <v>0</v>
       </c>
       <c r="U89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V89" t="b">
         <v>0</v>
@@ -7266,19 +7218,19 @@
       </c>
       <c r="X89" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Contacts - </v>
       </c>
       <c r="Z89" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v>Banana Plugs</v>
       </c>
       <c r="AA89" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SD Card</v>
+        <v/>
       </c>
       <c r="AB89" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7300,63 +7252,57 @@
     <row r="90" spans="8:31">
       <c r="H90" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Gate Driver - Isolated</v>
+        <v>Connectors - Test Points</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="J90" t="s">
-        <v>88</v>
-      </c>
-      <c r="K90" t="s">
-        <v>101</v>
-      </c>
-      <c r="L90" t="s">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="P90" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U90" t="b">
         <v>1</v>
       </c>
-      <c r="V90" t="b">
-        <v>0</v>
+      <c r="V90" t="s">
+        <v>184</v>
       </c>
       <c r="W90">
         <v>0</v>
       </c>
       <c r="X90" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v>Test Points</v>
       </c>
       <c r="AA90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Gate Driver - </v>
+        <v/>
       </c>
       <c r="AB90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Isolated</v>
+        <v/>
       </c>
       <c r="AC90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -7374,63 +7320,60 @@
     <row r="91" spans="8:31">
       <c r="H91" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Gate Driver - Non Isolated</v>
+        <v>Connectors - Terminal Blocks - Wire to Board</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="J91" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="K91" t="s">
-        <v>101</v>
-      </c>
-      <c r="L91" t="s">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="P91" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U91" t="b">
         <v>1</v>
       </c>
-      <c r="V91" t="b">
-        <v>0</v>
+      <c r="V91" t="s">
+        <v>184</v>
       </c>
       <c r="W91">
         <v>0</v>
       </c>
       <c r="X91" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Terminal Blocks - </v>
       </c>
       <c r="AA91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Gate Driver - </v>
+        <v>Wire to Board</v>
       </c>
       <c r="AB91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Non Isolated</v>
+        <v/>
       </c>
       <c r="AC91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -7448,56 +7391,53 @@
     <row r="92" spans="8:31">
       <c r="H92" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Half&amp;H Bridge</v>
+        <v>Connectors - SD Card Socket</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="J92" t="s">
-        <v>88</v>
-      </c>
-      <c r="K92" t="s">
-        <v>139</v>
+        <v>56</v>
       </c>
       <c r="P92" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S92" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U92" t="b">
         <v>1</v>
       </c>
-      <c r="V92" t="b">
-        <v>0</v>
+      <c r="V92" t="s">
+        <v>184</v>
       </c>
       <c r="W92">
         <v>0</v>
       </c>
       <c r="X92" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v>SD Card Socket</v>
       </c>
       <c r="AA92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Half&amp;H Bridge</v>
+        <v/>
       </c>
       <c r="AB92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7519,16 +7459,13 @@
     <row r="93" spans="8:31">
       <c r="H93" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Supply Sequencing</v>
+        <v>Connectors - Screw Connectors</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="J93" t="s">
-        <v>88</v>
-      </c>
-      <c r="K93" t="s">
-        <v>200</v>
+        <v>53</v>
       </c>
       <c r="P93" s="6" t="b">
         <v>0</v>
@@ -7560,15 +7497,15 @@
       </c>
       <c r="Y93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v>Screw Connectors</v>
       </c>
       <c r="AA93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Supply Sequencing</v>
+        <v/>
       </c>
       <c r="AB93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7590,16 +7527,13 @@
     <row r="94" spans="8:31">
       <c r="H94" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Switching Controler</v>
+        <v>Connectors - Power Entry Modules</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="J94" t="s">
-        <v>88</v>
-      </c>
-      <c r="K94" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="P94" s="6" t="b">
         <v>0</v>
@@ -7617,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="U94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V94" t="b">
         <v>0</v>
@@ -7627,19 +7561,19 @@
       </c>
       <c r="X94" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z94" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v>Power Entry Modules</v>
       </c>
       <c r="AA94" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Switching Controler</v>
+        <v/>
       </c>
       <c r="AB94" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7661,49 +7595,49 @@
     <row r="95" spans="8:31">
       <c r="H95" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - RTCs</v>
+        <v>Connectors - Jumpers</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="J95" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="P95" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U95" t="b">
-        <v>1</v>
-      </c>
-      <c r="V95" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V95" t="b">
+        <v>0</v>
       </c>
       <c r="W95">
         <v>0</v>
       </c>
       <c r="X95" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z95" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>RTCs</v>
+        <v>Jumpers</v>
       </c>
       <c r="AA95" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7729,13 +7663,13 @@
     <row r="96" spans="8:31">
       <c r="H96" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Isolators - Analog</v>
+        <v>Connectors - Flat Flex</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="J96" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="P96" s="6" t="b">
         <v>0</v>
@@ -7747,13 +7681,13 @@
         <v>0</v>
       </c>
       <c r="S96" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T96" t="b">
         <v>0</v>
       </c>
       <c r="U96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V96" t="b">
         <v>0</v>
@@ -7767,11 +7701,11 @@
       </c>
       <c r="Y96" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Isolators - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z96" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Analog</v>
+        <v>Flat Flex</v>
       </c>
       <c r="AA96" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7797,13 +7731,22 @@
     <row r="97" spans="8:31">
       <c r="H97" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>LEDs - RGB</v>
+        <v>Connectors - D-Sub - Standard - Male - PCB Mount</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="J97" t="s">
-        <v>154</v>
+        <v>66</v>
+      </c>
+      <c r="K97" t="s">
+        <v>63</v>
+      </c>
+      <c r="L97" t="s">
+        <v>67</v>
+      </c>
+      <c r="M97" t="s">
+        <v>69</v>
       </c>
       <c r="P97" s="6" t="b">
         <v>0</v>
@@ -7818,10 +7761,10 @@
         <v>0</v>
       </c>
       <c r="T97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V97" t="b">
         <v>0</v>
@@ -7831,27 +7774,27 @@
       </c>
       <c r="X97" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">LEDs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>RGB</v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AB97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Male - </v>
       </c>
       <c r="AC97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>PCB Mount</v>
       </c>
       <c r="AD97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -7865,33 +7808,42 @@
     <row r="98" spans="8:31">
       <c r="H98" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Heat Shrink</v>
+        <v>Connectors - D-Sub - Standard - Male - Inline</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="J98" t="s">
-        <v>147</v>
+        <v>66</v>
+      </c>
+      <c r="K98" t="s">
+        <v>63</v>
+      </c>
+      <c r="L98" t="s">
+        <v>67</v>
+      </c>
+      <c r="M98" t="s">
+        <v>70</v>
       </c>
       <c r="P98" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q98" t="b">
-        <v>0</v>
-      </c>
-      <c r="R98" t="b">
+      <c r="Q98" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R98" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S98" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T98" t="b">
-        <v>0</v>
-      </c>
-      <c r="U98" t="b">
-        <v>0</v>
-      </c>
-      <c r="V98" t="b">
+        <v>0</v>
+      </c>
+      <c r="T98" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U98" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V98" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W98">
@@ -7899,27 +7851,27 @@
       </c>
       <c r="X98" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Heat Shrink</v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AB98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Male - </v>
       </c>
       <c r="AC98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>Inline</v>
       </c>
       <c r="AD98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -7933,33 +7885,42 @@
     <row r="99" spans="8:31">
       <c r="H99" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Nuts</v>
+        <v>Connectors - D-Sub - Standard - Female - PCB Mount</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="J99" t="s">
-        <v>137</v>
+        <v>66</v>
+      </c>
+      <c r="K99" t="s">
+        <v>63</v>
+      </c>
+      <c r="L99" t="s">
+        <v>68</v>
+      </c>
+      <c r="M99" t="s">
+        <v>69</v>
       </c>
       <c r="P99" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q99" t="b">
-        <v>0</v>
-      </c>
-      <c r="R99" t="b">
+      <c r="Q99" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R99" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S99" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T99" t="b">
-        <v>0</v>
-      </c>
-      <c r="U99" t="b">
-        <v>0</v>
-      </c>
-      <c r="V99" t="b">
+      <c r="T99" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U99" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V99" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W99">
@@ -7971,23 +7932,23 @@
       </c>
       <c r="Y99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Nuts</v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AB99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Female - </v>
       </c>
       <c r="AC99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>PCB Mount</v>
       </c>
       <c r="AD99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -8001,33 +7962,42 @@
     <row r="100" spans="8:31">
       <c r="H100" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Spacers</v>
+        <v>Connectors - D-Sub - Standard - Female - Inline</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="J100" t="s">
-        <v>135</v>
+        <v>66</v>
+      </c>
+      <c r="K100" t="s">
+        <v>63</v>
+      </c>
+      <c r="L100" t="s">
+        <v>68</v>
+      </c>
+      <c r="M100" t="s">
+        <v>70</v>
       </c>
       <c r="P100" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q100" t="b">
-        <v>0</v>
-      </c>
-      <c r="R100" t="b">
+      <c r="Q100" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R100" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S100" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T100" t="b">
-        <v>0</v>
-      </c>
-      <c r="U100" t="b">
-        <v>0</v>
-      </c>
-      <c r="V100" t="b">
+      <c r="T100" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U100" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V100" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W100">
@@ -8039,23 +8009,23 @@
       </c>
       <c r="Y100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Spacers</v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AB100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Female - </v>
       </c>
       <c r="AC100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>Inline</v>
       </c>
       <c r="AD100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -8069,36 +8039,42 @@
     <row r="101" spans="8:31">
       <c r="H101" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Standoffs  - F_F</v>
+        <v>Connectors - D-Sub - Hybrid - Male - Inline</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="J101" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="K101" t="s">
-        <v>142</v>
+        <v>64</v>
+      </c>
+      <c r="L101" t="s">
+        <v>67</v>
+      </c>
+      <c r="M101" t="s">
+        <v>70</v>
       </c>
       <c r="P101" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q101" t="b">
-        <v>0</v>
-      </c>
-      <c r="R101" t="b">
+      <c r="Q101" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R101" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S101" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T101" t="b">
-        <v>0</v>
-      </c>
-      <c r="U101" t="b">
-        <v>0</v>
-      </c>
-      <c r="V101" t="b">
+      <c r="T101" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U101" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V101" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W101">
@@ -8110,23 +8086,23 @@
       </c>
       <c r="Y101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standoffs  - </v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>F_F</v>
+        <v xml:space="preserve">Hybrid - </v>
       </c>
       <c r="AB101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Male - </v>
       </c>
       <c r="AC101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>Inline</v>
       </c>
       <c r="AD101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -8140,36 +8116,42 @@
     <row r="102" spans="8:31">
       <c r="H102" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Standoffs  - M_F</v>
+        <v>Connectors - D-Sub - Hybrid - Female - Inline</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="J102" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="K102" t="s">
-        <v>141</v>
+        <v>64</v>
+      </c>
+      <c r="L102" t="s">
+        <v>68</v>
+      </c>
+      <c r="M102" t="s">
+        <v>70</v>
       </c>
       <c r="P102" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q102" t="b">
-        <v>0</v>
-      </c>
-      <c r="R102" t="b">
+      <c r="Q102" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R102" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S102" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T102" t="b">
-        <v>0</v>
-      </c>
-      <c r="U102" t="b">
-        <v>0</v>
-      </c>
-      <c r="V102" t="b">
+      <c r="T102" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U102" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V102" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W102">
@@ -8181,23 +8163,23 @@
       </c>
       <c r="Y102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standoffs  - </v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>M_F</v>
+        <v xml:space="preserve">Hybrid - </v>
       </c>
       <c r="AB102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Female - </v>
       </c>
       <c r="AC102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>Inline</v>
       </c>
       <c r="AD102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -8211,33 +8193,36 @@
     <row r="103" spans="8:31">
       <c r="H103" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - PolyFuses</v>
+        <v>Connectors - D-Sub - Backshells</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J103" t="s">
-        <v>180</v>
+        <v>66</v>
+      </c>
+      <c r="K103" t="s">
+        <v>65</v>
       </c>
       <c r="P103" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q103" t="b">
-        <v>0</v>
-      </c>
-      <c r="R103" t="b">
+      <c r="Q103" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R103" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S103" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T103" t="b">
-        <v>1</v>
-      </c>
-      <c r="U103" t="b">
-        <v>1</v>
-      </c>
-      <c r="V103" t="b">
+        <v>0</v>
+      </c>
+      <c r="T103" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U103" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V103" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W103">
@@ -8245,19 +8230,19 @@
       </c>
       <c r="X103" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>42.857142857142854</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>PolyFuses</v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Backshells</v>
       </c>
       <c r="AB103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8279,36 +8264,33 @@
     <row r="104" spans="8:31">
       <c r="H104" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - Chasis Mount - AC-DC</v>
+        <v>Connectors - Coaxial</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="J104" t="s">
-        <v>86</v>
-      </c>
-      <c r="K104" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="P104" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="b">
-        <v>0</v>
-      </c>
-      <c r="R104" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q104" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R104" s="30" t="b">
+        <v>1</v>
       </c>
       <c r="S104" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T104" t="b">
-        <v>0</v>
-      </c>
-      <c r="U104" t="b">
-        <v>0</v>
-      </c>
-      <c r="V104" t="b">
+        <v>1</v>
+      </c>
+      <c r="T104" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U104" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V104" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W104">
@@ -8316,19 +8298,19 @@
       </c>
       <c r="X104" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Chasis Mount - </v>
+        <v>Coaxial</v>
       </c>
       <c r="AA104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>AC-DC</v>
+        <v/>
       </c>
       <c r="AB104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8350,36 +8332,33 @@
     <row r="105" spans="8:31">
       <c r="H105" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - Chasis Mount - DC-DC</v>
+        <v>Connectors - Card Edge</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="J105" t="s">
-        <v>86</v>
-      </c>
-      <c r="K105" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="P105" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q105" t="b">
-        <v>0</v>
-      </c>
-      <c r="R105" t="b">
+      <c r="Q105" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R105" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S105" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T105" t="b">
-        <v>0</v>
-      </c>
-      <c r="U105" t="b">
-        <v>0</v>
-      </c>
-      <c r="V105" t="b">
+      <c r="T105" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U105" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V105" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W105">
@@ -8391,15 +8370,15 @@
       </c>
       <c r="Y105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Chasis Mount - </v>
+        <v>Card Edge</v>
       </c>
       <c r="AA105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DC-DC</v>
+        <v/>
       </c>
       <c r="AB105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8421,55 +8400,56 @@
     <row r="106" spans="8:31">
       <c r="H106" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - PCB Mount - AC-DC</v>
+        <v>Connectors - Battery Holders - Cylindrical</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="J106" t="s">
-        <v>69</v>
+        <v>206</v>
       </c>
       <c r="K106" t="s">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="P106" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q106" t="b">
-        <v>0</v>
-      </c>
-      <c r="R106" t="b">
+      <c r="Q106" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R106" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S106" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T106" t="b">
-        <v>0</v>
-      </c>
-      <c r="U106" t="b">
-        <v>0</v>
-      </c>
-      <c r="V106" t="b">
+      <c r="T106" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U106" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V106" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W106">
         <v>0</v>
       </c>
       <c r="X106" s="6">
-        <v>5</v>
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
       </c>
       <c r="Y106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">PCB Mount - </v>
+        <v xml:space="preserve">Battery Holders - </v>
       </c>
       <c r="AA106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>AC-DC</v>
+        <v>Cylindrical</v>
       </c>
       <c r="AB106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8491,53 +8471,56 @@
     <row r="107" spans="8:31">
       <c r="H107" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Network</v>
+        <v>Connectors - Battery Holders - Coin Cell</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J107" t="s">
-        <v>51</v>
+        <v>206</v>
+      </c>
+      <c r="K107" t="s">
+        <v>207</v>
       </c>
       <c r="P107" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="b">
-        <v>0</v>
-      </c>
-      <c r="R107" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q107" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R107" s="30" t="b">
+        <v>1</v>
       </c>
       <c r="S107" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T107" t="b">
-        <v>0</v>
-      </c>
-      <c r="U107" t="b">
-        <v>0</v>
-      </c>
-      <c r="V107" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T107" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U107" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V107" s="30" t="s">
+        <v>184</v>
       </c>
       <c r="W107">
         <v>0</v>
       </c>
       <c r="X107" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y107" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Resistors - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z107" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Network</v>
+        <v xml:space="preserve">Battery Holders - </v>
       </c>
       <c r="AA107" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Coin Cell</v>
       </c>
       <c r="AB107" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8559,36 +8542,33 @@
     <row r="108" spans="8:31">
       <c r="H108" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Single - Through Hole</v>
+        <v>Connectors - Banana Jacks</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J108" t="s">
-        <v>43</v>
-      </c>
-      <c r="K108" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="P108" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q108" t="b">
-        <v>0</v>
-      </c>
-      <c r="R108" t="b">
+      <c r="Q108" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R108" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S108" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T108" t="b">
-        <v>0</v>
-      </c>
-      <c r="U108" t="b">
-        <v>0</v>
-      </c>
-      <c r="V108" t="b">
+      <c r="T108" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U108" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V108" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W108">
@@ -8600,15 +8580,15 @@
       </c>
       <c r="Y108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Resistors - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Single - </v>
+        <v>Banana Jacks</v>
       </c>
       <c r="AA108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Through Hole</v>
+        <v/>
       </c>
       <c r="AB108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8630,33 +8610,39 @@
     <row r="109" spans="8:31">
       <c r="H109" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Capacitance To Digital</v>
+        <v>Clock&amp;Timing - Oscillators  - VCOs - VCXO</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="J109" t="s">
-        <v>212</v>
+        <v>124</v>
+      </c>
+      <c r="K109" t="s">
+        <v>129</v>
+      </c>
+      <c r="L109" t="s">
+        <v>131</v>
       </c>
       <c r="P109" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q109" t="b">
-        <v>0</v>
-      </c>
-      <c r="R109" t="b">
+      <c r="Q109" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R109" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S109" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T109" t="b">
-        <v>0</v>
-      </c>
-      <c r="U109" t="b">
-        <v>0</v>
-      </c>
-      <c r="V109" t="b">
+      <c r="T109" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U109" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V109" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W109">
@@ -8664,23 +8650,23 @@
       </c>
       <c r="X109" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Sensors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Capacitance To Digital</v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">VCOs - </v>
       </c>
       <c r="AB109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>VCXO</v>
       </c>
       <c r="AC109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8698,33 +8684,39 @@
     <row r="110" spans="8:31">
       <c r="H110" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Humidity</v>
+        <v>Clock&amp;Timing - Oscillators  - VCOs - VCTCXO</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="J110" t="s">
-        <v>215</v>
+        <v>124</v>
+      </c>
+      <c r="K110" t="s">
+        <v>129</v>
+      </c>
+      <c r="L110" t="s">
+        <v>132</v>
       </c>
       <c r="P110" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q110" t="b">
-        <v>0</v>
-      </c>
-      <c r="R110" t="b">
+      <c r="Q110" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R110" s="30" t="b">
         <v>0</v>
       </c>
       <c r="S110" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T110" t="b">
-        <v>0</v>
-      </c>
-      <c r="U110" t="b">
-        <v>0</v>
-      </c>
-      <c r="V110" t="b">
+      <c r="T110" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U110" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V110" s="30" t="b">
         <v>0</v>
       </c>
       <c r="W110">
@@ -8732,23 +8724,23 @@
       </c>
       <c r="X110" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Sensors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Humidity</v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">VCOs - </v>
       </c>
       <c r="AB110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>VCTCXO</v>
       </c>
       <c r="AC110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8766,16 +8758,19 @@
     <row r="111" spans="8:31">
       <c r="H111" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Temperature - RTDs</v>
+        <v>Clock&amp;Timing - Oscillators  - VCOs - VCO</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="J111" t="s">
-        <v>213</v>
+        <v>124</v>
       </c>
       <c r="K111" t="s">
-        <v>214</v>
+        <v>129</v>
+      </c>
+      <c r="L111" t="s">
+        <v>130</v>
       </c>
       <c r="P111" s="6" t="b">
         <v>0</v>
@@ -8790,7 +8785,7 @@
         <v>0</v>
       </c>
       <c r="T111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U111" t="b">
         <v>0</v>
@@ -8803,23 +8798,23 @@
       </c>
       <c r="X111" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Sensors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Temperature - </v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>RTDs</v>
+        <v xml:space="preserve">VCOs - </v>
       </c>
       <c r="AB111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>VCO</v>
       </c>
       <c r="AC111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8837,16 +8832,19 @@
     <row r="112" spans="8:31">
       <c r="H112" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Touch Sensor - Capacitive</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - TCXO</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="J112" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="K112" t="s">
-        <v>158</v>
+        <v>125</v>
+      </c>
+      <c r="L112" t="s">
+        <v>127</v>
       </c>
       <c r="P112" s="6" t="b">
         <v>0</v>
@@ -8861,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="T112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U112" t="b">
         <v>0</v>
@@ -8874,23 +8872,23 @@
       </c>
       <c r="X112" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Sensors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Touch Sensor - </v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Capacitive</v>
+        <v xml:space="preserve">Fixed - </v>
       </c>
       <c r="AB112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>TCXO</v>
       </c>
       <c r="AC112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8908,60 +8906,63 @@
     <row r="113" spans="8:31">
       <c r="H113" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Transformer - Power - Chasis Mount</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - Logic_Out</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="J113" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="K113" t="s">
-        <v>86</v>
+        <v>125</v>
+      </c>
+      <c r="L113" t="s">
+        <v>205</v>
       </c>
       <c r="P113" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S113" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U113" t="b">
-        <v>0</v>
-      </c>
-      <c r="V113" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V113" t="s">
+        <v>184</v>
       </c>
       <c r="W113">
         <v>0</v>
       </c>
       <c r="X113" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Transformer - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Chasis Mount</v>
+        <v xml:space="preserve">Fixed - </v>
       </c>
       <c r="AB113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Logic_Out</v>
       </c>
       <c r="AC113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8979,16 +8980,19 @@
     <row r="114" spans="8:31">
       <c r="H114" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Transformer - Power - PCB Mount</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - Ceramic Resonator</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="J114" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="K114" t="s">
-        <v>69</v>
+        <v>125</v>
+      </c>
+      <c r="L114" t="s">
+        <v>128</v>
       </c>
       <c r="P114" s="6" t="b">
         <v>0</v>
@@ -9003,7 +9007,7 @@
         <v>0</v>
       </c>
       <c r="T114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U114" t="b">
         <v>0</v>
@@ -9016,23 +9020,23 @@
       </c>
       <c r="X114" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Transformer - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>PCB Mount</v>
+        <v xml:space="preserve">Fixed - </v>
       </c>
       <c r="AB114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Ceramic Resonator</v>
       </c>
       <c r="AC114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -9050,13 +9054,16 @@
     <row r="115" spans="8:31">
       <c r="H115" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Voltage References - Misc</v>
+        <v>Clock&amp;Timing - ICs - DDS</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="J115" t="s">
-        <v>187</v>
+        <v>100</v>
+      </c>
+      <c r="K115" t="s">
+        <v>123</v>
       </c>
       <c r="P115" s="6" t="b">
         <v>0</v>
@@ -9074,7 +9081,7 @@
         <v>0</v>
       </c>
       <c r="U115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V115" t="b">
         <v>0</v>
@@ -9084,19 +9091,19 @@
       </c>
       <c r="X115" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Voltage References - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Misc</v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="AA115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>DDS</v>
       </c>
       <c r="AB115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9118,13 +9125,13 @@
     <row r="116" spans="8:31">
       <c r="H116" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Cables - Premade</v>
+        <v>Capacitors - Polarized</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J116" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="P116" s="6" t="b">
         <v>1</v>
@@ -9138,29 +9145,29 @@
       <c r="S116" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T116" t="b">
-        <v>1</v>
-      </c>
-      <c r="U116" t="b">
-        <v>1</v>
-      </c>
-      <c r="V116" t="b">
-        <v>1</v>
+      <c r="T116" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U116" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V116" t="s">
+        <v>184</v>
       </c>
       <c r="W116">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X116" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>100</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Cables - </v>
+        <v xml:space="preserve">Capacitors - </v>
       </c>
       <c r="Z116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Premade</v>
+        <v>Polarized</v>
       </c>
       <c r="AA116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9186,13 +9193,13 @@
     <row r="117" spans="8:31">
       <c r="H117" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Capacitors - Unpolarized</v>
+        <v>Voltage References - Burried Zener</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="J117" t="s">
-        <v>33</v>
+        <v>186</v>
       </c>
       <c r="P117" s="6" t="b">
         <v>1</v>
@@ -9224,11 +9231,11 @@
       </c>
       <c r="Y117" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Capacitors - </v>
+        <v xml:space="preserve">Voltage References - </v>
       </c>
       <c r="Z117" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Unpolarized</v>
+        <v>Burried Zener</v>
       </c>
       <c r="AA117" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9254,16 +9261,13 @@
     <row r="118" spans="8:31">
       <c r="H118" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - ICs - Generators &amp; Synthisizers</v>
+        <v>Thermal - Pads</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="J118" t="s">
-        <v>100</v>
-      </c>
-      <c r="K118" t="s">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="P118" s="6" t="b">
         <v>1</v>
@@ -9295,15 +9299,15 @@
       </c>
       <c r="Y118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Thermal - </v>
       </c>
       <c r="Z118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v>Pads</v>
       </c>
       <c r="AA118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Generators &amp; Synthisizers</v>
+        <v/>
       </c>
       <c r="AB118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9325,19 +9329,13 @@
     <row r="119" spans="8:31">
       <c r="H119" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - XO</v>
+        <v>Thermal - Heat Sinks</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="J119" t="s">
-        <v>124</v>
-      </c>
-      <c r="K119" t="s">
-        <v>125</v>
-      </c>
-      <c r="L119" t="s">
-        <v>126</v>
+        <v>46</v>
       </c>
       <c r="P119" s="6" t="b">
         <v>1</v>
@@ -9369,19 +9367,19 @@
       </c>
       <c r="Y119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Thermal - </v>
       </c>
       <c r="Z119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v>Heat Sinks</v>
       </c>
       <c r="AA119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Fixed - </v>
+        <v/>
       </c>
       <c r="AB119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>XO</v>
+        <v/>
       </c>
       <c r="AC119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -9399,13 +9397,13 @@
     <row r="120" spans="8:31">
       <c r="H120" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Barrel Jack</v>
+        <v>Switches - Tactile</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="J120" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="P120" s="6" t="b">
         <v>1</v>
@@ -9437,11 +9435,11 @@
       </c>
       <c r="Y120" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Switches - </v>
       </c>
       <c r="Z120" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Barrel Jack</v>
+        <v>Tactile</v>
       </c>
       <c r="AA120" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9467,13 +9465,13 @@
     <row r="121" spans="8:31">
       <c r="H121" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - IC socket</v>
+        <v>Switches - Slide</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="J121" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="P121" s="6" t="b">
         <v>1</v>
@@ -9505,11 +9503,11 @@
       </c>
       <c r="Y121" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Switches - </v>
       </c>
       <c r="Z121" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>IC socket</v>
+        <v>Slide</v>
       </c>
       <c r="AA121" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9535,13 +9533,13 @@
     <row r="122" spans="8:31">
       <c r="H122" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Mezzanine</v>
+        <v>Switches - Push</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="J122" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="P122" s="6" t="b">
         <v>1</v>
@@ -9573,11 +9571,11 @@
       </c>
       <c r="Y122" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Switches - </v>
       </c>
       <c r="Z122" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Mezzanine</v>
+        <v>Push</v>
       </c>
       <c r="AA122" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9603,13 +9601,13 @@
     <row r="123" spans="8:31">
       <c r="H123" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Pads - SMD</v>
+        <v>Resistors - Single - SMD</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J123" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K123" t="s">
         <v>44</v>
@@ -9644,11 +9642,11 @@
       </c>
       <c r="Y123" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z123" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Pads - </v>
+        <v xml:space="preserve">Single - </v>
       </c>
       <c r="AA123" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9674,16 +9672,13 @@
     <row r="124" spans="8:31">
       <c r="H124" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Pads - Through Hole</v>
+        <v>Resistors - Isolated Array</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J124" t="s">
-        <v>47</v>
-      </c>
-      <c r="K124" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P124" s="6" t="b">
         <v>1</v>
@@ -9715,15 +9710,15 @@
       </c>
       <c r="Y124" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z124" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Pads - </v>
+        <v>Isolated Array</v>
       </c>
       <c r="AA124" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Through Hole</v>
+        <v/>
       </c>
       <c r="AB124" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9745,13 +9740,13 @@
     <row r="125" spans="8:31">
       <c r="H125" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Programming</v>
+        <v>PSUs - Wall Wart</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="J125" t="s">
-        <v>55</v>
+        <v>196</v>
       </c>
       <c r="P125" s="6" t="b">
         <v>1</v>
@@ -9783,11 +9778,11 @@
       </c>
       <c r="Y125" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z125" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Programming</v>
+        <v>Wall Wart</v>
       </c>
       <c r="AA125" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9813,33 +9808,39 @@
     <row r="126" spans="8:31">
       <c r="H126" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Rectangular</v>
+        <v>PSUs - PCB Mount - DC-DC - Non-Isolated</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="J126" t="s">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="K126" t="s">
+        <v>83</v>
+      </c>
+      <c r="L126" t="s">
+        <v>85</v>
       </c>
       <c r="P126" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q126" t="b">
-        <v>1</v>
-      </c>
-      <c r="R126" t="b">
+      <c r="Q126" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R126" s="30" t="b">
         <v>1</v>
       </c>
       <c r="S126" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T126" t="b">
-        <v>1</v>
-      </c>
-      <c r="U126" t="b">
-        <v>1</v>
-      </c>
-      <c r="V126" t="b">
+      <c r="T126" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U126" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V126" s="30" t="b">
         <v>1</v>
       </c>
       <c r="W126">
@@ -9851,19 +9852,19 @@
       </c>
       <c r="Y126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Rectangular</v>
+        <v xml:space="preserve">PCB Mount - </v>
       </c>
       <c r="AA126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">DC-DC - </v>
       </c>
       <c r="AB126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Non-Isolated</v>
       </c>
       <c r="AC126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -9881,33 +9882,33 @@
     <row r="127" spans="8:31">
       <c r="H127" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - RJ</v>
+        <v>Protection - TVS Diode</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J127" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="P127" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q127" t="b">
-        <v>1</v>
-      </c>
-      <c r="R127" t="b">
+      <c r="Q127" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R127" s="30" t="b">
         <v>1</v>
       </c>
       <c r="S127" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T127" t="b">
-        <v>1</v>
-      </c>
-      <c r="U127" t="b">
-        <v>1</v>
-      </c>
-      <c r="V127" t="b">
+      <c r="T127" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U127" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V127" s="30" t="b">
         <v>1</v>
       </c>
       <c r="W127">
@@ -9919,11 +9920,11 @@
       </c>
       <c r="Y127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>RJ</v>
+        <v>TVS Diode</v>
       </c>
       <c r="AA127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9949,33 +9950,33 @@
     <row r="128" spans="8:31">
       <c r="H128" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - USB</v>
+        <v>Protection - MOVs</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J128" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="P128" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q128" t="b">
-        <v>1</v>
-      </c>
-      <c r="R128" t="b">
+      <c r="Q128" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R128" s="30" t="b">
         <v>1</v>
       </c>
       <c r="S128" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T128" t="b">
-        <v>1</v>
-      </c>
-      <c r="U128" t="b">
-        <v>1</v>
-      </c>
-      <c r="V128" t="b">
+      <c r="T128" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U128" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V128" s="30" t="b">
         <v>1</v>
       </c>
       <c r="W128">
@@ -9987,11 +9988,11 @@
       </c>
       <c r="Y128" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z128" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>USB</v>
+        <v>MOVs</v>
       </c>
       <c r="AA128" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10017,36 +10018,33 @@
     <row r="129" spans="8:31">
       <c r="H129" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Diodes - Schottky</v>
+        <v>Protection - GDT</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="J129" t="s">
-        <v>90</v>
-      </c>
-      <c r="K129" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="P129" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q129" t="b">
-        <v>1</v>
-      </c>
-      <c r="R129" t="b">
+      <c r="Q129" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R129" s="30" t="b">
         <v>1</v>
       </c>
       <c r="S129" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T129" t="b">
-        <v>1</v>
-      </c>
-      <c r="U129" t="b">
-        <v>1</v>
-      </c>
-      <c r="V129" t="b">
+      <c r="T129" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U129" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V129" s="30" t="b">
         <v>1</v>
       </c>
       <c r="W129">
@@ -10058,15 +10056,15 @@
       </c>
       <c r="Y129" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z129" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Diodes - </v>
+        <v>GDT</v>
       </c>
       <c r="AA129" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Schottky</v>
+        <v/>
       </c>
       <c r="AB129" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10088,39 +10086,33 @@
     <row r="130" spans="8:31">
       <c r="H130" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - BJT - NPN</v>
+        <v>Protection - Fuses</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="J130" t="s">
-        <v>195</v>
-      </c>
-      <c r="K130" t="s">
-        <v>92</v>
-      </c>
-      <c r="L130" t="s">
-        <v>201</v>
+        <v>39</v>
       </c>
       <c r="P130" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q130" t="b">
-        <v>1</v>
-      </c>
-      <c r="R130" t="b">
+      <c r="Q130" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R130" s="30" t="b">
         <v>1</v>
       </c>
       <c r="S130" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T130" t="b">
-        <v>1</v>
-      </c>
-      <c r="U130" t="b">
-        <v>1</v>
-      </c>
-      <c r="V130" t="b">
+      <c r="T130" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U130" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V130" s="30" t="b">
         <v>1</v>
       </c>
       <c r="W130">
@@ -10132,19 +10124,19 @@
       </c>
       <c r="Y130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v>Fuses</v>
       </c>
       <c r="AA130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">BJT - </v>
+        <v/>
       </c>
       <c r="AB130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>NPN</v>
+        <v/>
       </c>
       <c r="AC130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10162,36 +10154,33 @@
     <row r="131" spans="8:31">
       <c r="H131" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - OP Amp</v>
+        <v>Mechanical  - Screws</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="J131" t="s">
-        <v>99</v>
-      </c>
-      <c r="K131" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="P131" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q131" t="b">
-        <v>1</v>
-      </c>
-      <c r="R131" t="b">
+      <c r="Q131" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R131" s="30" t="b">
         <v>1</v>
       </c>
       <c r="S131" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T131" t="b">
-        <v>1</v>
-      </c>
-      <c r="U131" t="b">
-        <v>1</v>
-      </c>
-      <c r="V131" t="b">
+      <c r="T131" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U131" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V131" s="30" t="b">
         <v>1</v>
       </c>
       <c r="W131">
@@ -10203,15 +10192,15 @@
       </c>
       <c r="Y131" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z131" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v>Screws</v>
       </c>
       <c r="AA131" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>OP Amp</v>
+        <v/>
       </c>
       <c r="AB131" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10233,36 +10222,33 @@
     <row r="132" spans="8:31">
       <c r="H132" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - MCU</v>
+        <v>Mechanical  - Feet</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="J132" t="s">
-        <v>106</v>
-      </c>
-      <c r="K132" t="s">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="P132" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q132" t="b">
-        <v>1</v>
-      </c>
-      <c r="R132" t="b">
+      <c r="Q132" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R132" s="30" t="b">
         <v>1</v>
       </c>
       <c r="S132" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T132" t="b">
-        <v>1</v>
-      </c>
-      <c r="U132" t="b">
-        <v>1</v>
-      </c>
-      <c r="V132" t="b">
+      <c r="T132" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U132" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V132" s="30" t="b">
         <v>1</v>
       </c>
       <c r="W132">
@@ -10274,15 +10260,15 @@
       </c>
       <c r="Y132" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z132" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v>Feet</v>
       </c>
       <c r="AA132" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>MCU</v>
+        <v/>
       </c>
       <c r="AB132" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10304,19 +10290,19 @@
     <row r="133" spans="8:31">
       <c r="H133" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - MCU - Module</v>
+        <v>LEDs - Standard - Indicator - Through Hole</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="J133" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="K133" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L133" t="s">
-        <v>189</v>
+        <v>52</v>
       </c>
       <c r="P133" s="6" t="b">
         <v>1</v>
@@ -10348,19 +10334,19 @@
       </c>
       <c r="Y133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">LEDs - </v>
       </c>
       <c r="Z133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AA133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">MCU - </v>
+        <v xml:space="preserve">Indicator - </v>
       </c>
       <c r="AB133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Module</v>
+        <v>Through Hole</v>
       </c>
       <c r="AC133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10378,16 +10364,19 @@
     <row r="134" spans="8:31">
       <c r="H134" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Ideal Diodes</v>
+        <v>LEDs - Standard - Indicator - SMD</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="J134" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="K134" t="s">
-        <v>105</v>
+        <v>151</v>
+      </c>
+      <c r="L134" t="s">
+        <v>44</v>
       </c>
       <c r="P134" s="6" t="b">
         <v>1</v>
@@ -10419,19 +10408,19 @@
       </c>
       <c r="Y134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">LEDs - </v>
       </c>
       <c r="Z134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AA134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Ideal Diodes</v>
+        <v xml:space="preserve">Indicator - </v>
       </c>
       <c r="AB134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>SMD</v>
       </c>
       <c r="AC134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10449,16 +10438,13 @@
     <row r="135" spans="8:31">
       <c r="H135" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Linear Regulation</v>
+        <v>Inductors - Ferrite Bead</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="J135" t="s">
-        <v>88</v>
-      </c>
-      <c r="K135" t="s">
-        <v>103</v>
+        <v>202</v>
       </c>
       <c r="P135" s="6" t="b">
         <v>1</v>
@@ -10490,15 +10476,15 @@
       </c>
       <c r="Y135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Inductors - </v>
       </c>
       <c r="Z135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v>Ferrite Bead</v>
       </c>
       <c r="AA135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Linear Regulation</v>
+        <v/>
       </c>
       <c r="AB135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10585,13 +10571,16 @@
     <row r="137" spans="8:31">
       <c r="H137" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Inductors - Ferrite Bead</v>
+        <v>ICs - Power - Linear Regulation</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="J137" t="s">
-        <v>203</v>
+        <v>88</v>
+      </c>
+      <c r="K137" t="s">
+        <v>103</v>
       </c>
       <c r="P137" s="6" t="b">
         <v>1</v>
@@ -10623,15 +10612,15 @@
       </c>
       <c r="Y137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Inductors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Ferrite Bead</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Linear Regulation</v>
       </c>
       <c r="AB137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10653,19 +10642,16 @@
     <row r="138" spans="8:31">
       <c r="H138" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>LEDs - Standard - Indicator - SMD</v>
+        <v>ICs - Power - Ideal Diodes</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="J138" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="K138" t="s">
-        <v>151</v>
-      </c>
-      <c r="L138" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="P138" s="6" t="b">
         <v>1</v>
@@ -10697,19 +10683,19 @@
       </c>
       <c r="Y138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">LEDs - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Indicator - </v>
+        <v>Ideal Diodes</v>
       </c>
       <c r="AB138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SMD</v>
+        <v/>
       </c>
       <c r="AC138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10727,19 +10713,19 @@
     <row r="139" spans="8:31">
       <c r="H139" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>LEDs - Standard - Indicator - Through Hole</v>
+        <v>ICs - Embedded - MCU - Module</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="J139" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="K139" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L139" t="s">
-        <v>52</v>
+        <v>188</v>
       </c>
       <c r="P139" s="6" t="b">
         <v>1</v>
@@ -10771,19 +10757,19 @@
       </c>
       <c r="Y139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">LEDs - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v xml:space="preserve">Embedded - </v>
       </c>
       <c r="AA139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Indicator - </v>
+        <v xml:space="preserve">MCU - </v>
       </c>
       <c r="AB139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Through Hole</v>
+        <v>Module</v>
       </c>
       <c r="AC139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10801,13 +10787,16 @@
     <row r="140" spans="8:31">
       <c r="H140" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Feet</v>
+        <v>ICs - Embedded - MCU</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="J140" t="s">
-        <v>198</v>
+        <v>106</v>
+      </c>
+      <c r="K140" t="s">
+        <v>107</v>
       </c>
       <c r="P140" s="6" t="b">
         <v>1</v>
@@ -10839,15 +10828,15 @@
       </c>
       <c r="Y140" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z140" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Feet</v>
+        <v xml:space="preserve">Embedded - </v>
       </c>
       <c r="AA140" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>MCU</v>
       </c>
       <c r="AB140" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10869,13 +10858,16 @@
     <row r="141" spans="8:31">
       <c r="H141" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Screws</v>
+        <v>ICs - Analog - OP Amp</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="J141" t="s">
-        <v>136</v>
+        <v>99</v>
+      </c>
+      <c r="K141" t="s">
+        <v>117</v>
       </c>
       <c r="P141" s="6" t="b">
         <v>1</v>
@@ -10907,15 +10899,15 @@
       </c>
       <c r="Y141" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z141" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Screws</v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA141" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>OP Amp</v>
       </c>
       <c r="AB141" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10937,13 +10929,19 @@
     <row r="142" spans="8:31">
       <c r="H142" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - Fuses</v>
+        <v>Discreet - Transistors - BJT - NPN</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="J142" t="s">
-        <v>39</v>
+        <v>194</v>
+      </c>
+      <c r="K142" t="s">
+        <v>92</v>
+      </c>
+      <c r="L142" t="s">
+        <v>200</v>
       </c>
       <c r="P142" s="6" t="b">
         <v>1</v>
@@ -10975,19 +10973,19 @@
       </c>
       <c r="Y142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Fuses</v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">BJT - </v>
       </c>
       <c r="AB142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>NPN</v>
       </c>
       <c r="AC142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -11005,13 +11003,16 @@
     <row r="143" spans="8:31">
       <c r="H143" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - GDT</v>
+        <v>Discreet - Diodes - Schottky</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="J143" t="s">
-        <v>40</v>
+        <v>90</v>
+      </c>
+      <c r="K143" t="s">
+        <v>91</v>
       </c>
       <c r="P143" s="6" t="b">
         <v>1</v>
@@ -11043,15 +11044,15 @@
       </c>
       <c r="Y143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>GDT</v>
+        <v xml:space="preserve">Diodes - </v>
       </c>
       <c r="AA143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Schottky</v>
       </c>
       <c r="AB143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -11073,13 +11074,13 @@
     <row r="144" spans="8:31">
       <c r="H144" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - MOVs</v>
+        <v>Connectors - USB</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J144" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="P144" s="6" t="b">
         <v>1</v>
@@ -11111,11 +11112,11 @@
       </c>
       <c r="Y144" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z144" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>MOVs</v>
+        <v>USB</v>
       </c>
       <c r="AA144" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11141,13 +11142,13 @@
     <row r="145" spans="8:31">
       <c r="H145" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - TVS Diode</v>
+        <v>Connectors - RJ</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J145" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="P145" s="6" t="b">
         <v>1</v>
@@ -11179,11 +11180,11 @@
       </c>
       <c r="Y145" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z145" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>TVS Diode</v>
+        <v>RJ</v>
       </c>
       <c r="AA145" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11209,19 +11210,13 @@
     <row r="146" spans="8:31">
       <c r="H146" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - PCB Mount - DC-DC - Non-Isolated</v>
+        <v>Connectors - Rectangular</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="J146" t="s">
-        <v>69</v>
-      </c>
-      <c r="K146" t="s">
-        <v>83</v>
-      </c>
-      <c r="L146" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="P146" s="6" t="b">
         <v>1</v>
@@ -11253,19 +11248,19 @@
       </c>
       <c r="Y146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">PCB Mount - </v>
+        <v>Rectangular</v>
       </c>
       <c r="AA146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">DC-DC - </v>
+        <v/>
       </c>
       <c r="AB146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Non-Isolated</v>
+        <v/>
       </c>
       <c r="AC146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -11283,13 +11278,13 @@
     <row r="147" spans="8:31">
       <c r="H147" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - Wall Wart</v>
+        <v>Connectors - Programming</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="J147" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="P147" s="6" t="b">
         <v>1</v>
@@ -11321,11 +11316,11 @@
       </c>
       <c r="Y147" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z147" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Wall Wart</v>
+        <v>Programming</v>
       </c>
       <c r="AA147" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11351,13 +11346,16 @@
     <row r="148" spans="8:31">
       <c r="H148" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Isolated Array</v>
+        <v>Connectors - Pads - Through Hole</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J148" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="K148" t="s">
+        <v>52</v>
       </c>
       <c r="P148" s="6" t="b">
         <v>1</v>
@@ -11389,15 +11387,15 @@
       </c>
       <c r="Y148" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Resistors - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z148" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Isolated Array</v>
+        <v xml:space="preserve">Pads - </v>
       </c>
       <c r="AA148" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Through Hole</v>
       </c>
       <c r="AB148" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -11419,13 +11417,13 @@
     <row r="149" spans="8:31">
       <c r="H149" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Single - SMD</v>
+        <v>Connectors - Pads - SMD</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J149" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K149" t="s">
         <v>44</v>
@@ -11460,11 +11458,11 @@
       </c>
       <c r="Y149" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Resistors - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z149" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Single - </v>
+        <v xml:space="preserve">Pads - </v>
       </c>
       <c r="AA149" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11490,13 +11488,13 @@
     <row r="150" spans="8:31">
       <c r="H150" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Switches - Push</v>
+        <v>Connectors - Mezzanine</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>181</v>
+        <v>34</v>
       </c>
       <c r="J150" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="P150" s="6" t="b">
         <v>1</v>
@@ -11528,11 +11526,11 @@
       </c>
       <c r="Y150" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Switches - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z150" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Push</v>
+        <v>Mezzanine</v>
       </c>
       <c r="AA150" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11558,13 +11556,13 @@
     <row r="151" spans="8:31">
       <c r="H151" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Switches - Slide</v>
+        <v>Connectors - IC socket</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>181</v>
+        <v>34</v>
       </c>
       <c r="J151" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="P151" s="6" t="b">
         <v>1</v>
@@ -11596,11 +11594,11 @@
       </c>
       <c r="Y151" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Switches - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z151" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Slide</v>
+        <v>IC socket</v>
       </c>
       <c r="AA151" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11626,33 +11624,33 @@
     <row r="152" spans="8:31">
       <c r="H152" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Switches - Tactile</v>
+        <v>Connectors - Barrel Jack</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>181</v>
+        <v>34</v>
       </c>
       <c r="J152" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="P152" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q152" t="b">
-        <v>1</v>
-      </c>
-      <c r="R152" t="b">
+      <c r="Q152" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R152" s="30" t="b">
         <v>1</v>
       </c>
       <c r="S152" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T152" t="b">
-        <v>1</v>
-      </c>
-      <c r="U152" t="b">
-        <v>1</v>
-      </c>
-      <c r="V152" t="b">
+      <c r="T152" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U152" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V152" s="30" t="b">
         <v>1</v>
       </c>
       <c r="W152">
@@ -11664,11 +11662,11 @@
       </c>
       <c r="Y152" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Switches - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z152" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Tactile</v>
+        <v>Barrel Jack</v>
       </c>
       <c r="AA152" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11694,13 +11692,19 @@
     <row r="153" spans="8:31">
       <c r="H153" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Heat Sinks</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - XO</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="J153" t="s">
-        <v>46</v>
+        <v>124</v>
+      </c>
+      <c r="K153" t="s">
+        <v>125</v>
+      </c>
+      <c r="L153" t="s">
+        <v>126</v>
       </c>
       <c r="P153" s="6" t="b">
         <v>1</v>
@@ -11732,19 +11736,19 @@
       </c>
       <c r="Y153" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Thermal - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z153" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Heat Sinks</v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA153" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Fixed - </v>
       </c>
       <c r="AB153" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>XO</v>
       </c>
       <c r="AC153" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -11762,13 +11766,16 @@
     <row r="154" spans="8:31">
       <c r="H154" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Pads</v>
+        <v>Clock&amp;Timing - ICs - Generators &amp; Synthisizers</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="J154" t="s">
-        <v>47</v>
+        <v>100</v>
+      </c>
+      <c r="K154" t="s">
+        <v>140</v>
       </c>
       <c r="P154" s="6" t="b">
         <v>1</v>
@@ -11800,15 +11807,15 @@
       </c>
       <c r="Y154" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Thermal - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z154" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Pads</v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="AA154" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Generators &amp; Synthisizers</v>
       </c>
       <c r="AB154" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -11830,13 +11837,13 @@
     <row r="155" spans="8:31">
       <c r="H155" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Voltage References - Burried Zener</v>
+        <v>Capacitors - Unpolarized</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="J155" t="s">
-        <v>186</v>
+        <v>33</v>
       </c>
       <c r="P155" s="6" t="b">
         <v>1</v>
@@ -11868,11 +11875,11 @@
       </c>
       <c r="Y155" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Voltage References - </v>
+        <v xml:space="preserve">Capacitors - </v>
       </c>
       <c r="Z155" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Burried Zener</v>
+        <v>Unpolarized</v>
       </c>
       <c r="AA155" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11891,6 +11898,74 @@
         <v/>
       </c>
       <c r="AE155" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="8:31">
+      <c r="H156" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Cables - Premade</v>
+      </c>
+      <c r="I156" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J156" t="s">
+        <v>31</v>
+      </c>
+      <c r="P156" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q156" t="b">
+        <v>1</v>
+      </c>
+      <c r="R156" t="b">
+        <v>1</v>
+      </c>
+      <c r="S156" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T156" t="b">
+        <v>1</v>
+      </c>
+      <c r="U156" t="b">
+        <v>1</v>
+      </c>
+      <c r="V156" t="b">
+        <v>1</v>
+      </c>
+      <c r="W156">
+        <v>-1</v>
+      </c>
+      <c r="X156" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>100</v>
+      </c>
+      <c r="Y156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Cables - </v>
+      </c>
+      <c r="Z156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v>Premade</v>
+      </c>
+      <c r="AA156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE156" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
         <v/>
       </c>
@@ -11913,7 +11988,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H155">
+  <conditionalFormatting sqref="H12:H156">
     <cfRule type="expression" dxfId="4" priority="2">
       <formula>IF($W12 = -1, 1, 0)</formula>
     </cfRule>
@@ -11923,7 +11998,7 @@
       <formula>IF($W12 &gt;= $E$18, 1, 0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P12:V155">
+  <conditionalFormatting sqref="P12:V156">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="TRALSE">
       <formula>NOT(ISERROR(SEARCH("TRALSE",P12)))</formula>
     </cfRule>
@@ -11937,7 +12012,7 @@
       <formula>NOT(ISERROR(SEARCH("TRUE",P12)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W12:W155">
+  <conditionalFormatting sqref="W12:W156">
     <cfRule type="cellIs" priority="77" stopIfTrue="1" operator="equal">
       <formula>-1</formula>
     </cfRule>
@@ -11950,7 +12025,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X12:X155">
+  <conditionalFormatting sqref="X12:X156">
     <cfRule type="expression" priority="9" stopIfTrue="1">
       <formula>IF(COUNTA(P12:W12)&gt;0,0,1)</formula>
     </cfRule>

--- a/To Add v2/00 Things To Add.xlsx
+++ b/To Add v2/00 Things To Add.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Danakil_KiCad_DB\To Add v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BD5C4D-6252-4039-BC13-CC7BA0DFC4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DB5800-6D8A-4F05-851F-AE58A0DE31D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="7725" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="224">
   <si>
     <t>Table Name</t>
   </si>
@@ -727,6 +727,9 @@
   </si>
   <si>
     <t>General Purpose</t>
+  </si>
+  <si>
+    <t>Shunts</t>
   </si>
 </sst>
 </file>
@@ -861,7 +864,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -936,7 +939,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1046,10 +1048,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}" name="Table1" displayName="Table1" ref="H11:AE156" totalsRowShown="0">
-  <autoFilter ref="H11:AE156" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H12:AE156">
-    <sortCondition descending="1" ref="W11:W156"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}" name="Table1" displayName="Table1" ref="H11:AE157" totalsRowShown="0">
+  <autoFilter ref="H11:AE157" xr:uid="{DD6E292C-4D1E-49EA-9A61-3C83B907CF9E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H12:AE157">
+    <sortCondition descending="1" ref="W11:W157"/>
   </sortState>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{24CA07BC-B564-425C-A1C9-824F8759E630}" name="Table Name"/>
@@ -1360,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AE156"/>
+  <dimension ref="B1:AE157"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="14.08984375" customWidth="1"/>
@@ -1408,7 +1410,7 @@
       </c>
       <c r="E3" s="13">
         <f>COUNTA(H12:H10039)</f>
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I3"/>
       <c r="P3"/>
@@ -1436,7 +1438,7 @@
       </c>
       <c r="E5" s="14">
         <f>COUNTIF(W12:W10040,"&gt;-1")</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G5" t="s">
         <v>49</v>
@@ -1444,31 +1446,31 @@
       <c r="I5"/>
       <c r="P5" s="8">
         <f t="shared" ref="P5:V5" si="0">100*COUNTIF(P12:P9999,"=TRUE")/COUNTA(P12:P9999)</f>
-        <v>40</v>
+        <v>40.410958904109592</v>
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="0"/>
-        <v>39.310344827586206</v>
+        <v>39.726027397260275</v>
       </c>
       <c r="R5" s="8">
         <f t="shared" si="0"/>
-        <v>39.310344827586206</v>
+        <v>39.726027397260275</v>
       </c>
       <c r="S5" s="8">
         <f t="shared" si="0"/>
-        <v>44.827586206896555</v>
+        <v>44.520547945205479</v>
       </c>
       <c r="T5" s="8">
         <f t="shared" si="0"/>
-        <v>46.896551724137929</v>
+        <v>47.260273972602739</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" si="0"/>
-        <v>66.896551724137936</v>
+        <v>67.123287671232873</v>
       </c>
       <c r="V5" s="8">
         <f t="shared" si="0"/>
-        <v>27.586206896551722</v>
+        <v>27.397260273972602</v>
       </c>
     </row>
     <row r="6" spans="2:31">
@@ -1479,7 +1481,7 @@
       </c>
       <c r="E6" s="14">
         <f>COUNTIF(X12:X10038,"&gt;0") -E4</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I6"/>
       <c r="P6"/>
@@ -1496,7 +1498,7 @@
       </c>
       <c r="E7" s="15">
         <f>(COUNTIF(P12:V10039,"=TRUE")/COUNTA(P12:V10039))*100</f>
-        <v>43.546798029556648</v>
+        <v>43.737769080234834</v>
       </c>
       <c r="I7"/>
       <c r="P7"/>
@@ -1512,7 +1514,7 @@
       </c>
       <c r="E8" s="13">
         <f>P5</f>
-        <v>40</v>
+        <v>40.410958904109592</v>
       </c>
       <c r="I8"/>
       <c r="P8"/>
@@ -1529,7 +1531,7 @@
       </c>
       <c r="E9" s="14">
         <f>Q5</f>
-        <v>39.310344827586206</v>
+        <v>39.726027397260275</v>
       </c>
       <c r="I9"/>
       <c r="P9"/>
@@ -1554,7 +1556,7 @@
       </c>
       <c r="E10" s="15">
         <f>R5</f>
-        <v>39.310344827586206</v>
+        <v>39.726027397260275</v>
       </c>
       <c r="I10" s="19" t="s">
         <v>8</v>
@@ -1597,7 +1599,7 @@
       </c>
       <c r="E11" s="13">
         <f>S5</f>
-        <v>44.827586206896555</v>
+        <v>44.520547945205479</v>
       </c>
       <c r="H11" t="s">
         <v>0</v>
@@ -1680,17 +1682,20 @@
       </c>
       <c r="E12" s="14">
         <f>T5</f>
-        <v>46.896551724137929</v>
+        <v>47.260273972602739</v>
       </c>
       <c r="H12" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Voltage References - General Purpose</v>
+        <v>Resistors - Single - Shunts</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="J12" t="s">
-        <v>222</v>
+        <v>43</v>
+      </c>
+      <c r="K12" t="s">
+        <v>223</v>
       </c>
       <c r="P12" s="6" t="b">
         <v>1</v>
@@ -1702,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
@@ -1718,19 +1723,19 @@
       </c>
       <c r="X12" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Voltage References - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>General Purpose</v>
+        <v xml:space="preserve">Single - </v>
       </c>
       <c r="AA12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Shunts</v>
       </c>
       <c r="AB12" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1757,7 +1762,7 @@
       </c>
       <c r="E13" s="15">
         <f>U5</f>
-        <v>66.896551724137936</v>
+        <v>67.123287671232873</v>
       </c>
       <c r="H13" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
@@ -1794,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="W13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X13" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
@@ -1839,20 +1844,17 @@
       </c>
       <c r="E14" s="13">
         <f>COUNTIF(W12:W9999,"=0")</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H14" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Diodes - Zener</v>
+        <v>Voltage References - General Purpose</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="J14" t="s">
-        <v>90</v>
-      </c>
-      <c r="K14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P14" s="6" t="b">
         <v>1</v>
@@ -1872,8 +1874,8 @@
       <c r="U14" t="b">
         <v>1</v>
       </c>
-      <c r="V14" t="s">
-        <v>184</v>
+      <c r="V14" t="b">
+        <v>0</v>
       </c>
       <c r="W14">
         <v>0</v>
@@ -1884,15 +1886,15 @@
       </c>
       <c r="Y14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">Voltage References - </v>
       </c>
       <c r="Z14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Diodes - </v>
+        <v>General Purpose</v>
       </c>
       <c r="AA14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Zener</v>
+        <v/>
       </c>
       <c r="AB14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1923,56 +1925,56 @@
       </c>
       <c r="H15" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Transformer - Power - PCB Mount</v>
+        <v>Discreet - Diodes - Zener</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s">
-        <v>69</v>
+        <v>221</v>
       </c>
       <c r="P15" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="b">
-        <v>0</v>
-      </c>
-      <c r="V15" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V15" t="s">
+        <v>184</v>
       </c>
       <c r="W15">
         <v>0</v>
       </c>
       <c r="X15" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Transformer - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Diodes - </v>
       </c>
       <c r="AA15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>PCB Mount</v>
+        <v>Zener</v>
       </c>
       <c r="AB15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1998,11 +2000,11 @@
       </c>
       <c r="E16" s="14" cm="1">
         <f t="array" ref="E16">SUM(IF(W12:W9999 &gt; 0,X12:X9999,0))/COUNTIF(W12:W9999,"&gt;0")</f>
-        <v>21.428571428571427</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="H16" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Transformer - Power - Chasis Mount</v>
+        <v>Transformer - Power - PCB Mount</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>87</v>
@@ -2011,7 +2013,7 @@
         <v>88</v>
       </c>
       <c r="K16" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="P16" s="6" t="b">
         <v>0</v>
@@ -2051,7 +2053,7 @@
       </c>
       <c r="AA16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Chasis Mount</v>
+        <v>PCB Mount</v>
       </c>
       <c r="AB16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2077,17 +2079,20 @@
       </c>
       <c r="E17" s="14" cm="1">
         <f t="array" ref="E17">SUM(IF(W12:W9999 =E18,X12:X9999,0))/SUM(IF(W12:W9997 =E18,1,0))</f>
-        <v>21.428571428571427</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="H17" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Tape</v>
+        <v>Transformer - Power - Chasis Mount</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s">
-        <v>220</v>
+        <v>88</v>
+      </c>
+      <c r="K17" t="s">
+        <v>86</v>
       </c>
       <c r="P17" s="6" t="b">
         <v>0</v>
@@ -2119,15 +2124,15 @@
       </c>
       <c r="Y17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Thermal - </v>
+        <v xml:space="preserve">Transformer - </v>
       </c>
       <c r="Z17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Tape</v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Chasis Mount</v>
       </c>
       <c r="AB17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2156,13 +2161,13 @@
       </c>
       <c r="H18" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Paste</v>
+        <v>Thermal - Tape</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J18" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P18" s="6" t="b">
         <v>0</v>
@@ -2174,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
@@ -2190,7 +2195,7 @@
       </c>
       <c r="X18" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -2198,7 +2203,7 @@
       </c>
       <c r="Z18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Paste</v>
+        <v>Tape</v>
       </c>
       <c r="AA18" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -2224,13 +2229,13 @@
     <row r="19" spans="3:31">
       <c r="H19" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Glue</v>
+        <v>Thermal - Paste</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P19" s="6" t="b">
         <v>0</v>
@@ -2242,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
@@ -2258,7 +2263,7 @@
       </c>
       <c r="X19" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y19" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -2266,7 +2271,7 @@
       </c>
       <c r="Z19" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Glue</v>
+        <v>Paste</v>
       </c>
       <c r="AA19" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -2292,16 +2297,13 @@
     <row r="20" spans="3:31">
       <c r="H20" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Touch Sensor - Capacitive</v>
+        <v>Thermal - Glue</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J20" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="K20" t="s">
-        <v>158</v>
+        <v>45</v>
+      </c>
+      <c r="J20" t="s">
+        <v>219</v>
       </c>
       <c r="P20" s="6" t="b">
         <v>0</v>
@@ -2333,15 +2335,15 @@
       </c>
       <c r="Y20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Sensors - </v>
+        <v xml:space="preserve">Thermal - </v>
       </c>
       <c r="Z20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Touch Sensor - </v>
+        <v>Glue</v>
       </c>
       <c r="AA20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Capacitive</v>
+        <v/>
       </c>
       <c r="AB20" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2363,16 +2365,16 @@
     <row r="21" spans="3:31">
       <c r="H21" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Temperature - RTDs</v>
+        <v>Sensors - Touch Sensor - Capacitive</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>210</v>
       </c>
       <c r="J21" t="s">
-        <v>212</v>
+        <v>157</v>
       </c>
       <c r="K21" t="s">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="P21" s="6" t="b">
         <v>0</v>
@@ -2386,10 +2388,10 @@
       <c r="S21" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T21" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U21" s="30" t="b">
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" t="b">
         <v>0</v>
       </c>
       <c r="V21" t="b">
@@ -2408,11 +2410,11 @@
       </c>
       <c r="Z21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Temperature - </v>
+        <v xml:space="preserve">Touch Sensor - </v>
       </c>
       <c r="AA21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>RTDs</v>
+        <v>Capacitive</v>
       </c>
       <c r="AB21" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2434,13 +2436,16 @@
     <row r="22" spans="3:31">
       <c r="H22" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Humidity</v>
+        <v>Sensors - Temperature - RTDs</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>210</v>
       </c>
       <c r="J22" t="s">
-        <v>214</v>
+        <v>212</v>
+      </c>
+      <c r="K22" t="s">
+        <v>213</v>
       </c>
       <c r="P22" s="6" t="b">
         <v>0</v>
@@ -2476,11 +2481,11 @@
       </c>
       <c r="Z22" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Humidity</v>
+        <v xml:space="preserve">Temperature - </v>
       </c>
       <c r="AA22" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>RTDs</v>
       </c>
       <c r="AB22" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2502,13 +2507,13 @@
     <row r="23" spans="3:31">
       <c r="H23" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Capacitance To Digital</v>
+        <v>Sensors - Humidity</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>210</v>
       </c>
       <c r="J23" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P23" s="6" t="b">
         <v>0</v>
@@ -2544,7 +2549,7 @@
       </c>
       <c r="Z23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Capacitance To Digital</v>
+        <v>Humidity</v>
       </c>
       <c r="AA23" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -2570,16 +2575,13 @@
     <row r="24" spans="3:31">
       <c r="H24" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Single - Through Hole</v>
+        <v>Sensors - Capacitance To Digital</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K24" t="s">
-        <v>52</v>
+        <v>211</v>
       </c>
       <c r="P24" s="6" t="b">
         <v>0</v>
@@ -2611,15 +2613,15 @@
       </c>
       <c r="Y24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Resistors - </v>
+        <v xml:space="preserve">Sensors - </v>
       </c>
       <c r="Z24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Single - </v>
+        <v>Capacitance To Digital</v>
       </c>
       <c r="AA24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Through Hole</v>
+        <v/>
       </c>
       <c r="AB24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2641,13 +2643,16 @@
     <row r="25" spans="3:31">
       <c r="H25" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Network</v>
+        <v>Resistors - Single - Through Hole</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J25" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="K25" t="s">
+        <v>52</v>
       </c>
       <c r="P25" s="6" t="b">
         <v>0</v>
@@ -2683,11 +2688,11 @@
       </c>
       <c r="Z25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Network</v>
+        <v xml:space="preserve">Single - </v>
       </c>
       <c r="AA25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Through Hole</v>
       </c>
       <c r="AB25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2709,63 +2714,57 @@
     <row r="26" spans="3:31">
       <c r="H26" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - PCB Mount - DC-DC - Isolated</v>
+        <v>Resistors - Network</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="J26" t="s">
-        <v>69</v>
-      </c>
-      <c r="K26" t="s">
-        <v>83</v>
-      </c>
-      <c r="L26" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="P26" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" t="b">
-        <v>1</v>
-      </c>
-      <c r="V26" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
       </c>
       <c r="W26">
         <v>0</v>
       </c>
       <c r="X26" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">PCB Mount - </v>
+        <v>Network</v>
       </c>
       <c r="AA26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">DC-DC - </v>
+        <v/>
       </c>
       <c r="AB26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Isolated</v>
+        <v/>
       </c>
       <c r="AC26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2783,7 +2782,7 @@
     <row r="27" spans="3:31">
       <c r="H27" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - PCB Mount - AC-DC</v>
+        <v>PSUs - PCB Mount - DC-DC - Isolated</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>81</v>
@@ -2792,34 +2791,38 @@
         <v>69</v>
       </c>
       <c r="K27" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="L27" t="s">
+        <v>84</v>
       </c>
       <c r="P27" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="b">
-        <v>0</v>
-      </c>
-      <c r="V27" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V27" t="s">
+        <v>184</v>
       </c>
       <c r="W27">
         <v>0</v>
       </c>
       <c r="X27" s="6">
-        <v>5</v>
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -2831,11 +2834,11 @@
       </c>
       <c r="AA27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>AC-DC</v>
+        <v xml:space="preserve">DC-DC - </v>
       </c>
       <c r="AB27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Isolated</v>
       </c>
       <c r="AC27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -2853,16 +2856,16 @@
     <row r="28" spans="3:31">
       <c r="H28" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - Chasis Mount - DC-DC</v>
+        <v>PSUs - PCB Mount - AC-DC</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J28" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="K28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P28" s="6" t="b">
         <v>0</v>
@@ -2889,8 +2892,7 @@
         <v>0</v>
       </c>
       <c r="X28" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -2898,11 +2900,11 @@
       </c>
       <c r="Z28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Chasis Mount - </v>
+        <v xml:space="preserve">PCB Mount - </v>
       </c>
       <c r="AA28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DC-DC</v>
+        <v>AC-DC</v>
       </c>
       <c r="AB28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2924,7 +2926,7 @@
     <row r="29" spans="3:31">
       <c r="H29" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - Chasis Mount - AC-DC</v>
+        <v>PSUs - Chasis Mount - DC-DC</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>81</v>
@@ -2933,7 +2935,7 @@
         <v>86</v>
       </c>
       <c r="K29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P29" s="6" t="b">
         <v>0</v>
@@ -2973,7 +2975,7 @@
       </c>
       <c r="AA29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>AC-DC</v>
+        <v>DC-DC</v>
       </c>
       <c r="AB29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2995,13 +2997,16 @@
     <row r="30" spans="3:31">
       <c r="H30" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - PolyFuses</v>
+        <v>PSUs - Chasis Mount - AC-DC</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="J30" t="s">
-        <v>180</v>
+        <v>86</v>
+      </c>
+      <c r="K30" t="s">
+        <v>82</v>
       </c>
       <c r="P30" s="6" t="b">
         <v>0</v>
@@ -3013,13 +3018,13 @@
         <v>0</v>
       </c>
       <c r="S30" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="b">
         <v>0</v>
@@ -3029,19 +3034,19 @@
       </c>
       <c r="X30" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>42.857142857142854</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>PolyFuses</v>
+        <v xml:space="preserve">Chasis Mount - </v>
       </c>
       <c r="AA30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>AC-DC</v>
       </c>
       <c r="AB30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3063,25 +3068,22 @@
     <row r="31" spans="3:31">
       <c r="H31" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Standoffs  - SMD</v>
+        <v>Protection - PolyFuses</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J31" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K31" t="s">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="J31" t="s">
+        <v>180</v>
       </c>
       <c r="P31" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="5" t="b">
         <v>1</v>
@@ -3092,27 +3094,27 @@
       <c r="U31" t="b">
         <v>1</v>
       </c>
-      <c r="V31" t="s">
-        <v>184</v>
+      <c r="V31" t="b">
+        <v>0</v>
       </c>
       <c r="W31">
         <v>0</v>
       </c>
       <c r="X31" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="Y31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standoffs  - </v>
+        <v>PolyFuses</v>
       </c>
       <c r="AA31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SMD</v>
+        <v/>
       </c>
       <c r="AB31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3134,7 +3136,7 @@
     <row r="32" spans="3:31">
       <c r="H32" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Standoffs  - M_F</v>
+        <v>Mechanical  - Standoffs  - SMD</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>133</v>
@@ -3143,35 +3145,35 @@
         <v>134</v>
       </c>
       <c r="K32" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="P32" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="b">
-        <v>0</v>
-      </c>
-      <c r="V32" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V32" t="s">
+        <v>184</v>
       </c>
       <c r="W32">
         <v>0</v>
       </c>
       <c r="X32" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -3183,7 +3185,7 @@
       </c>
       <c r="AA32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>M_F</v>
+        <v>SMD</v>
       </c>
       <c r="AB32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3205,7 +3207,7 @@
     <row r="33" spans="8:31">
       <c r="H33" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Standoffs  - F_F</v>
+        <v>Mechanical  - Standoffs  - M_F</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>133</v>
@@ -3214,7 +3216,7 @@
         <v>134</v>
       </c>
       <c r="K33" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P33" s="6" t="b">
         <v>0</v>
@@ -3254,7 +3256,7 @@
       </c>
       <c r="AA33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>F_F</v>
+        <v>M_F</v>
       </c>
       <c r="AB33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3276,13 +3278,16 @@
     <row r="34" spans="8:31">
       <c r="H34" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Spacers</v>
+        <v>Mechanical  - Standoffs  - F_F</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>133</v>
       </c>
       <c r="J34" t="s">
-        <v>135</v>
+        <v>134</v>
+      </c>
+      <c r="K34" t="s">
+        <v>142</v>
       </c>
       <c r="P34" s="6" t="b">
         <v>0</v>
@@ -3318,11 +3323,11 @@
       </c>
       <c r="Z34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Spacers</v>
+        <v xml:space="preserve">Standoffs  - </v>
       </c>
       <c r="AA34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>F_F</v>
       </c>
       <c r="AB34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3344,13 +3349,13 @@
     <row r="35" spans="8:31">
       <c r="H35" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Nuts</v>
+        <v>Mechanical  - Spacers</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>133</v>
       </c>
       <c r="J35" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P35" s="6" t="b">
         <v>0</v>
@@ -3386,7 +3391,7 @@
       </c>
       <c r="Z35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Nuts</v>
+        <v>Spacers</v>
       </c>
       <c r="AA35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3412,13 +3417,13 @@
     <row r="36" spans="8:31">
       <c r="H36" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Heat Shrink</v>
+        <v>Mechanical  - Nuts</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>133</v>
       </c>
       <c r="J36" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="b">
         <v>0</v>
@@ -3430,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="b">
         <v>0</v>
@@ -3446,7 +3451,7 @@
       </c>
       <c r="X36" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -3454,7 +3459,7 @@
       </c>
       <c r="Z36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Heat Shrink</v>
+        <v>Nuts</v>
       </c>
       <c r="AA36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3480,13 +3485,13 @@
     <row r="37" spans="8:31">
       <c r="H37" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>LEDs - RGB</v>
+        <v>Mechanical  - Heat Shrink</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="J37" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="P37" s="6" t="b">
         <v>0</v>
@@ -3498,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="S37" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" t="b">
         <v>0</v>
@@ -3514,15 +3519,15 @@
       </c>
       <c r="X37" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">LEDs - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>RGB</v>
+        <v>Heat Shrink</v>
       </c>
       <c r="AA37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3548,13 +3553,13 @@
     <row r="38" spans="8:31">
       <c r="H38" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Isolators - Optoisolator</v>
+        <v>LEDs - RGB</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="J38" t="s">
-        <v>217</v>
+        <v>154</v>
       </c>
       <c r="P38" s="6" t="b">
         <v>0</v>
@@ -3569,10 +3574,10 @@
         <v>0</v>
       </c>
       <c r="T38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" t="b">
         <v>0</v>
@@ -3582,15 +3587,15 @@
       </c>
       <c r="X38" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Isolators - </v>
+        <v xml:space="preserve">LEDs - </v>
       </c>
       <c r="Z38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Optoisolator</v>
+        <v>RGB</v>
       </c>
       <c r="AA38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3616,41 +3621,41 @@
     <row r="39" spans="8:31">
       <c r="H39" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Isolators - Digital</v>
+        <v>Isolators - Optoisolator</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J39" s="30" t="s">
-        <v>98</v>
+      <c r="J39" t="s">
+        <v>217</v>
       </c>
       <c r="P39" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T39" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U39" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V39" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="T39" t="b">
+        <v>0</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+      <c r="V39" t="b">
+        <v>0</v>
       </c>
       <c r="W39">
         <v>0</v>
       </c>
       <c r="X39" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -3658,7 +3663,7 @@
       </c>
       <c r="Z39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Digital</v>
+        <v>Optoisolator</v>
       </c>
       <c r="AA39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3684,41 +3689,41 @@
     <row r="40" spans="8:31">
       <c r="H40" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Isolators - Analog</v>
+        <v>Isolators - Digital</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>97</v>
       </c>
       <c r="J40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P40" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40" t="b">
         <v>1</v>
       </c>
-      <c r="V40" t="b">
-        <v>0</v>
+      <c r="V40" t="s">
+        <v>184</v>
       </c>
       <c r="W40">
         <v>0</v>
       </c>
       <c r="X40" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -3726,7 +3731,7 @@
       </c>
       <c r="Z40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Analog</v>
+        <v>Digital</v>
       </c>
       <c r="AA40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3752,49 +3757,49 @@
     <row r="41" spans="8:31">
       <c r="H41" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Inductors - Common Mode Choke</v>
+        <v>Isolators - Analog</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="J41" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="P41" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U41" t="b">
         <v>1</v>
       </c>
-      <c r="V41" t="s">
-        <v>184</v>
+      <c r="V41" t="b">
+        <v>0</v>
       </c>
       <c r="W41">
         <v>0</v>
       </c>
       <c r="X41" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Inductors - </v>
+        <v xml:space="preserve">Isolators - </v>
       </c>
       <c r="Z41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Common Mode Choke</v>
+        <v>Analog</v>
       </c>
       <c r="AA41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3820,13 +3825,13 @@
     <row r="42" spans="8:31">
       <c r="H42" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - RTCs</v>
+        <v>Inductors - Common Mode Choke</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="J42" t="s">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="P42" s="6" t="b">
         <v>1</v>
@@ -3858,11 +3863,11 @@
       </c>
       <c r="Y42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Inductors - </v>
       </c>
       <c r="Z42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>RTCs</v>
+        <v>Common Mode Choke</v>
       </c>
       <c r="AA42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -3888,44 +3893,41 @@
     <row r="43" spans="8:31">
       <c r="H43" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Switching Regulator</v>
+        <v>ICs - RTCs</v>
       </c>
       <c r="I43" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J43" t="s">
-        <v>88</v>
-      </c>
-      <c r="K43" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="P43" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="b">
         <v>1</v>
       </c>
-      <c r="V43" t="b">
-        <v>0</v>
+      <c r="V43" t="s">
+        <v>184</v>
       </c>
       <c r="W43">
         <v>0</v>
       </c>
       <c r="X43" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -3933,11 +3935,11 @@
       </c>
       <c r="Z43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v>RTCs</v>
       </c>
       <c r="AA43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Switching Regulator</v>
+        <v/>
       </c>
       <c r="AB43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -3959,7 +3961,7 @@
     <row r="44" spans="8:31">
       <c r="H44" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Switching Controler</v>
+        <v>ICs - Power - Switching Regulator</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>100</v>
@@ -3968,7 +3970,7 @@
         <v>88</v>
       </c>
       <c r="K44" t="s">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="P44" s="6" t="b">
         <v>0</v>
@@ -4008,7 +4010,7 @@
       </c>
       <c r="AA44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Switching Controler</v>
+        <v>Switching Regulator</v>
       </c>
       <c r="AB44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4030,7 +4032,7 @@
     <row r="45" spans="8:31">
       <c r="H45" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Supply Sequencing</v>
+        <v>ICs - Power - Switching Controler</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>100</v>
@@ -4039,7 +4041,7 @@
         <v>88</v>
       </c>
       <c r="K45" t="s">
-        <v>199</v>
+        <v>104</v>
       </c>
       <c r="P45" s="6" t="b">
         <v>0</v>
@@ -4057,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" t="b">
         <v>0</v>
@@ -4067,7 +4069,7 @@
       </c>
       <c r="X45" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4079,7 +4081,7 @@
       </c>
       <c r="AA45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Supply Sequencing</v>
+        <v>Switching Controler</v>
       </c>
       <c r="AB45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4101,7 +4103,7 @@
     <row r="46" spans="8:31">
       <c r="H46" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Half&amp;H Bridge</v>
+        <v>ICs - Power - Supply Sequencing</v>
       </c>
       <c r="I46" s="6" t="s">
         <v>100</v>
@@ -4110,7 +4112,7 @@
         <v>88</v>
       </c>
       <c r="K46" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="P46" s="6" t="b">
         <v>0</v>
@@ -4128,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" t="b">
         <v>0</v>
@@ -4138,7 +4140,7 @@
       </c>
       <c r="X46" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4150,7 +4152,7 @@
       </c>
       <c r="AA46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Half&amp;H Bridge</v>
+        <v>Supply Sequencing</v>
       </c>
       <c r="AB46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4172,7 +4174,7 @@
     <row r="47" spans="8:31">
       <c r="H47" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Gate Driver - Non Isolated</v>
+        <v>ICs - Power - Half&amp;H Bridge</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>100</v>
@@ -4181,10 +4183,7 @@
         <v>88</v>
       </c>
       <c r="K47" t="s">
-        <v>101</v>
-      </c>
-      <c r="L47" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="P47" s="6" t="b">
         <v>0</v>
@@ -4224,11 +4223,11 @@
       </c>
       <c r="AA47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Gate Driver - </v>
+        <v>Half&amp;H Bridge</v>
       </c>
       <c r="AB47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Non Isolated</v>
+        <v/>
       </c>
       <c r="AC47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4246,7 +4245,7 @@
     <row r="48" spans="8:31">
       <c r="H48" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Gate Driver - Isolated</v>
+        <v>ICs - Power - Gate Driver - Non Isolated</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>100</v>
@@ -4258,7 +4257,7 @@
         <v>101</v>
       </c>
       <c r="L48" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="P48" s="6" t="b">
         <v>0</v>
@@ -4302,7 +4301,7 @@
       </c>
       <c r="AB48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Isolated</v>
+        <v>Non Isolated</v>
       </c>
       <c r="AC48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4320,16 +4319,19 @@
     <row r="49" spans="8:31">
       <c r="H49" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - SD Card</v>
+        <v>ICs - Power - Gate Driver - Isolated</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J49" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s">
-        <v>112</v>
+        <v>101</v>
+      </c>
+      <c r="L49" t="s">
+        <v>84</v>
       </c>
       <c r="P49" s="6" t="b">
         <v>0</v>
@@ -4365,15 +4367,15 @@
       </c>
       <c r="Z49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SD Card</v>
+        <v xml:space="preserve">Gate Driver - </v>
       </c>
       <c r="AB49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Isolated</v>
       </c>
       <c r="AC49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4391,7 +4393,7 @@
     <row r="50" spans="8:31">
       <c r="H50" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - FLASH</v>
+        <v>ICs - Memory - SD Card</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>100</v>
@@ -4400,35 +4402,35 @@
         <v>110</v>
       </c>
       <c r="K50" t="s">
-        <v>204</v>
+        <v>112</v>
       </c>
       <c r="P50" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U50" t="b">
         <v>1</v>
       </c>
-      <c r="V50" t="s">
-        <v>184</v>
+      <c r="V50" t="b">
+        <v>0</v>
       </c>
       <c r="W50">
         <v>0</v>
       </c>
       <c r="X50" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4440,7 +4442,7 @@
       </c>
       <c r="AA50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>FLASH</v>
+        <v>SD Card</v>
       </c>
       <c r="AB50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4462,7 +4464,7 @@
     <row r="51" spans="8:31">
       <c r="H51" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - EEPROM</v>
+        <v>ICs - Memory - FLASH</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>100</v>
@@ -4471,7 +4473,7 @@
         <v>110</v>
       </c>
       <c r="K51" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="P51" s="6" t="b">
         <v>1</v>
@@ -4511,7 +4513,7 @@
       </c>
       <c r="AA51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>EEPROM</v>
+        <v>FLASH</v>
       </c>
       <c r="AB51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4533,7 +4535,7 @@
     <row r="52" spans="8:31">
       <c r="H52" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - DRAM</v>
+        <v>ICs - Memory - EEPROM</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>100</v>
@@ -4542,35 +4544,35 @@
         <v>110</v>
       </c>
       <c r="K52" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P52" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U52" t="b">
         <v>1</v>
       </c>
-      <c r="V52" t="b">
-        <v>0</v>
+      <c r="V52" t="s">
+        <v>184</v>
       </c>
       <c r="W52">
         <v>0</v>
       </c>
       <c r="X52" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4582,7 +4584,7 @@
       </c>
       <c r="AA52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DRAM</v>
+        <v>EEPROM</v>
       </c>
       <c r="AB52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4604,16 +4606,16 @@
     <row r="53" spans="8:31">
       <c r="H53" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Translators</v>
+        <v>ICs - Memory - DRAM</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J53" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="K53" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="P53" s="6" t="b">
         <v>0</v>
@@ -4649,11 +4651,11 @@
       </c>
       <c r="Z53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Translators</v>
+        <v>DRAM</v>
       </c>
       <c r="AB53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4675,7 +4677,7 @@
     <row r="54" spans="8:31">
       <c r="H54" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Switch - Digital</v>
+        <v>ICs - Logic - Translators</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>100</v>
@@ -4684,10 +4686,7 @@
         <v>118</v>
       </c>
       <c r="K54" t="s">
-        <v>173</v>
-      </c>
-      <c r="L54" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="P54" s="6" t="b">
         <v>0</v>
@@ -4727,11 +4726,11 @@
       </c>
       <c r="AA54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Switch - </v>
+        <v>Translators</v>
       </c>
       <c r="AB54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4749,7 +4748,7 @@
     <row r="55" spans="8:31">
       <c r="H55" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Shift Registers - SIPO</v>
+        <v>ICs - Logic - Switch - Digital</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>100</v>
@@ -4758,10 +4757,10 @@
         <v>118</v>
       </c>
       <c r="K55" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L55" t="s">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="P55" s="6" t="b">
         <v>0</v>
@@ -4801,11 +4800,11 @@
       </c>
       <c r="AA55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Shift Registers - </v>
+        <v xml:space="preserve">Switch - </v>
       </c>
       <c r="AB55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SIPO</v>
+        <v>Digital</v>
       </c>
       <c r="AC55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4823,7 +4822,7 @@
     <row r="56" spans="8:31">
       <c r="H56" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Shift Registers - PISO</v>
+        <v>ICs - Logic - Shift Registers - SIPO</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>100</v>
@@ -4835,7 +4834,7 @@
         <v>170</v>
       </c>
       <c r="L56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P56" s="6" t="b">
         <v>0</v>
@@ -4879,7 +4878,7 @@
       </c>
       <c r="AB56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>PISO</v>
+        <v>SIPO</v>
       </c>
       <c r="AC56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4897,7 +4896,7 @@
     <row r="57" spans="8:31">
       <c r="H57" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Multivibrators</v>
+        <v>ICs - Logic - Shift Registers - PISO</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>100</v>
@@ -4906,7 +4905,10 @@
         <v>118</v>
       </c>
       <c r="K57" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="L57" t="s">
+        <v>172</v>
       </c>
       <c r="P57" s="6" t="b">
         <v>0</v>
@@ -4946,11 +4948,11 @@
       </c>
       <c r="AA57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Multivibrators</v>
+        <v xml:space="preserve">Shift Registers - </v>
       </c>
       <c r="AB57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>PISO</v>
       </c>
       <c r="AC57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4968,7 +4970,7 @@
     <row r="58" spans="8:31">
       <c r="H58" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Multiplexer - Digital</v>
+        <v>ICs - Logic - Multivibrators</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>100</v>
@@ -4977,10 +4979,7 @@
         <v>118</v>
       </c>
       <c r="K58" t="s">
-        <v>174</v>
-      </c>
-      <c r="L58" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="P58" s="6" t="b">
         <v>0</v>
@@ -5020,11 +5019,11 @@
       </c>
       <c r="AA58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Multiplexer - </v>
+        <v>Multivibrators</v>
       </c>
       <c r="AB58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5042,7 +5041,7 @@
     <row r="59" spans="8:31">
       <c r="H59" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Level Shifters</v>
+        <v>ICs - Logic - Multiplexer - Digital</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>100</v>
@@ -5051,7 +5050,10 @@
         <v>118</v>
       </c>
       <c r="K59" t="s">
-        <v>177</v>
+        <v>174</v>
+      </c>
+      <c r="L59" t="s">
+        <v>98</v>
       </c>
       <c r="P59" s="6" t="b">
         <v>0</v>
@@ -5063,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" t="b">
         <v>0</v>
@@ -5079,7 +5081,7 @@
       </c>
       <c r="X59" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -5091,11 +5093,11 @@
       </c>
       <c r="AA59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Level Shifters</v>
+        <v xml:space="preserve">Multiplexer - </v>
       </c>
       <c r="AB59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5113,7 +5115,7 @@
     <row r="60" spans="8:31">
       <c r="H60" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Latches</v>
+        <v>ICs - Logic - Level Shifters</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>100</v>
@@ -5122,7 +5124,7 @@
         <v>118</v>
       </c>
       <c r="K60" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="P60" s="6" t="b">
         <v>0</v>
@@ -5134,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="S60" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" t="b">
         <v>0</v>
@@ -5150,7 +5152,7 @@
       </c>
       <c r="X60" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -5162,7 +5164,7 @@
       </c>
       <c r="AA60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Latches</v>
+        <v>Level Shifters</v>
       </c>
       <c r="AB60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5184,7 +5186,7 @@
     <row r="61" spans="8:31">
       <c r="H61" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Gates</v>
+        <v>ICs - Logic - Latches</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>100</v>
@@ -5193,7 +5195,7 @@
         <v>118</v>
       </c>
       <c r="K61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P61" s="6" t="b">
         <v>0</v>
@@ -5233,7 +5235,7 @@
       </c>
       <c r="AA61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Gates</v>
+        <v>Latches</v>
       </c>
       <c r="AB61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5255,7 +5257,7 @@
     <row r="62" spans="8:31">
       <c r="H62" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Flip Flops</v>
+        <v>ICs - Logic - Gates</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>100</v>
@@ -5264,7 +5266,7 @@
         <v>118</v>
       </c>
       <c r="K62" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P62" s="6" t="b">
         <v>0</v>
@@ -5304,7 +5306,7 @@
       </c>
       <c r="AA62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Flip Flops</v>
+        <v>Gates</v>
       </c>
       <c r="AB62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5326,7 +5328,7 @@
     <row r="63" spans="8:31">
       <c r="H63" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Demultiplexer - Digital</v>
+        <v>ICs - Logic - Flip Flops</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>100</v>
@@ -5335,10 +5337,7 @@
         <v>118</v>
       </c>
       <c r="K63" t="s">
-        <v>175</v>
-      </c>
-      <c r="L63" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="P63" s="6" t="b">
         <v>0</v>
@@ -5378,11 +5377,11 @@
       </c>
       <c r="AA63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Demultiplexer - </v>
+        <v>Flip Flops</v>
       </c>
       <c r="AB63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5400,7 +5399,7 @@
     <row r="64" spans="8:31">
       <c r="H64" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Counter - Up&amp;Down</v>
+        <v>ICs - Logic - Demultiplexer - Digital</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>100</v>
@@ -5409,10 +5408,10 @@
         <v>118</v>
       </c>
       <c r="K64" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="L64" t="s">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="P64" s="6" t="b">
         <v>0</v>
@@ -5452,11 +5451,11 @@
       </c>
       <c r="AA64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Counter - </v>
+        <v xml:space="preserve">Demultiplexer - </v>
       </c>
       <c r="AB64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Up&amp;Down</v>
+        <v>Digital</v>
       </c>
       <c r="AC64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5474,7 +5473,7 @@
     <row r="65" spans="8:31">
       <c r="H65" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Counter - Up</v>
+        <v>ICs - Logic - Counter - Up&amp;Down</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>100</v>
@@ -5486,7 +5485,7 @@
         <v>163</v>
       </c>
       <c r="L65" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P65" s="6" t="b">
         <v>0</v>
@@ -5530,7 +5529,7 @@
       </c>
       <c r="AB65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Up</v>
+        <v>Up&amp;Down</v>
       </c>
       <c r="AC65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5548,7 +5547,7 @@
     <row r="66" spans="8:31">
       <c r="H66" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Comparator - Digital</v>
+        <v>ICs - Logic - Counter - Up</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>100</v>
@@ -5557,10 +5556,10 @@
         <v>118</v>
       </c>
       <c r="K66" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="L66" t="s">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="P66" s="6" t="b">
         <v>0</v>
@@ -5600,11 +5599,11 @@
       </c>
       <c r="AA66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Comparator - </v>
+        <v xml:space="preserve">Counter - </v>
       </c>
       <c r="AB66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v>Up</v>
       </c>
       <c r="AC66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5622,16 +5621,19 @@
     <row r="67" spans="8:31">
       <c r="H67" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - UART</v>
+        <v>ICs - Logic - Comparator - Digital</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J67" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K67" t="s">
-        <v>162</v>
+        <v>116</v>
+      </c>
+      <c r="L67" t="s">
+        <v>98</v>
       </c>
       <c r="P67" s="6" t="b">
         <v>0</v>
@@ -5667,15 +5669,15 @@
       </c>
       <c r="Z67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>UART</v>
+        <v xml:space="preserve">Comparator - </v>
       </c>
       <c r="AB67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5693,7 +5695,7 @@
     <row r="68" spans="8:31">
       <c r="H68" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Trancievers</v>
+        <v>ICs - Interface  - UART</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>100</v>
@@ -5702,7 +5704,7 @@
         <v>119</v>
       </c>
       <c r="K68" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="P68" s="6" t="b">
         <v>0</v>
@@ -5742,7 +5744,7 @@
       </c>
       <c r="AA68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Trancievers</v>
+        <v>UART</v>
       </c>
       <c r="AB68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5764,7 +5766,7 @@
     <row r="69" spans="8:31">
       <c r="H69" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Serializer</v>
+        <v>ICs - Interface  - Trancievers</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>100</v>
@@ -5773,7 +5775,7 @@
         <v>119</v>
       </c>
       <c r="K69" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="P69" s="6" t="b">
         <v>0</v>
@@ -5813,7 +5815,7 @@
       </c>
       <c r="AA69" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Serializer</v>
+        <v>Trancievers</v>
       </c>
       <c r="AB69" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5835,7 +5837,7 @@
     <row r="70" spans="8:31">
       <c r="H70" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Recievers</v>
+        <v>ICs - Interface  - Serializer</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>100</v>
@@ -5844,7 +5846,7 @@
         <v>119</v>
       </c>
       <c r="K70" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="P70" s="6" t="b">
         <v>0</v>
@@ -5884,7 +5886,7 @@
       </c>
       <c r="AA70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Recievers</v>
+        <v>Serializer</v>
       </c>
       <c r="AB70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5906,7 +5908,7 @@
     <row r="71" spans="8:31">
       <c r="H71" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - IO Expander</v>
+        <v>ICs - Interface  - Recievers</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>100</v>
@@ -5915,7 +5917,7 @@
         <v>119</v>
       </c>
       <c r="K71" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="P71" s="6" t="b">
         <v>0</v>
@@ -5955,7 +5957,7 @@
       </c>
       <c r="AA71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>IO Expander</v>
+        <v>Recievers</v>
       </c>
       <c r="AB71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5977,7 +5979,7 @@
     <row r="72" spans="8:31">
       <c r="H72" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Drivers</v>
+        <v>ICs - Interface  - IO Expander</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>100</v>
@@ -5986,7 +5988,7 @@
         <v>119</v>
       </c>
       <c r="K72" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="P72" s="6" t="b">
         <v>0</v>
@@ -6026,7 +6028,7 @@
       </c>
       <c r="AA72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Drivers</v>
+        <v>IO Expander</v>
       </c>
       <c r="AB72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6048,7 +6050,7 @@
     <row r="73" spans="8:31">
       <c r="H73" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Deserializer</v>
+        <v>ICs - Interface  - Drivers</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>100</v>
@@ -6057,7 +6059,7 @@
         <v>119</v>
       </c>
       <c r="K73" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="P73" s="6" t="b">
         <v>0</v>
@@ -6097,7 +6099,7 @@
       </c>
       <c r="AA73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Deserializer</v>
+        <v>Drivers</v>
       </c>
       <c r="AB73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6119,7 +6121,7 @@
     <row r="74" spans="8:31">
       <c r="H74" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Controller</v>
+        <v>ICs - Interface  - Deserializer</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>100</v>
@@ -6128,7 +6130,7 @@
         <v>119</v>
       </c>
       <c r="K74" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P74" s="6" t="b">
         <v>0</v>
@@ -6168,7 +6170,7 @@
       </c>
       <c r="AA74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Controller</v>
+        <v>Deserializer</v>
       </c>
       <c r="AB74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6190,7 +6192,7 @@
     <row r="75" spans="8:31">
       <c r="H75" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Analog Switch</v>
+        <v>ICs - Interface  - Controller</v>
       </c>
       <c r="I75" s="6" t="s">
         <v>100</v>
@@ -6199,7 +6201,7 @@
         <v>119</v>
       </c>
       <c r="K75" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="P75" s="6" t="b">
         <v>0</v>
@@ -6239,7 +6241,7 @@
       </c>
       <c r="AA75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Analog Switch</v>
+        <v>Controller</v>
       </c>
       <c r="AB75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6261,19 +6263,16 @@
     <row r="76" spans="8:31">
       <c r="H76" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - PolarFire - SOC</v>
+        <v>ICs - Interface  - Analog Switch</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J76" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="K76" t="s">
-        <v>109</v>
-      </c>
-      <c r="L76" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="P76" s="6" t="b">
         <v>0</v>
@@ -6309,15 +6308,15 @@
       </c>
       <c r="Z76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">PolarFire - </v>
+        <v>Analog Switch</v>
       </c>
       <c r="AB76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SOC</v>
+        <v/>
       </c>
       <c r="AC76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6335,7 +6334,7 @@
     <row r="77" spans="8:31">
       <c r="H77" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - FPGA</v>
+        <v>ICs - Embedded - PolarFire - SOC</v>
       </c>
       <c r="I77" s="6" t="s">
         <v>100</v>
@@ -6344,10 +6343,13 @@
         <v>106</v>
       </c>
       <c r="K77" t="s">
-        <v>108</v>
-      </c>
-      <c r="P77" s="6" t="s">
-        <v>184</v>
+        <v>109</v>
+      </c>
+      <c r="L77" t="s">
+        <v>183</v>
+      </c>
+      <c r="P77" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="Q77" t="b">
         <v>0</v>
@@ -6356,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T77" t="b">
         <v>0</v>
@@ -6372,7 +6374,7 @@
       </c>
       <c r="X77" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6384,11 +6386,11 @@
       </c>
       <c r="AA77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>FPGA</v>
+        <v xml:space="preserve">PolarFire - </v>
       </c>
       <c r="AB77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>SOC</v>
       </c>
       <c r="AC77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6406,19 +6408,19 @@
     <row r="78" spans="8:31">
       <c r="H78" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - DAC</v>
+        <v>ICs - Embedded - FPGA</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J78" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K78" t="s">
-        <v>115</v>
-      </c>
-      <c r="P78" s="6" t="b">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="Q78" t="b">
         <v>0</v>
@@ -6427,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" t="b">
         <v>0</v>
@@ -6443,7 +6445,7 @@
       </c>
       <c r="X78" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6451,11 +6453,11 @@
       </c>
       <c r="Z78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v xml:space="preserve">Embedded - </v>
       </c>
       <c r="AA78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DAC</v>
+        <v>FPGA</v>
       </c>
       <c r="AB78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6477,7 +6479,7 @@
     <row r="79" spans="8:31">
       <c r="H79" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - Comparator</v>
+        <v>ICs - Analog - DAC</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>100</v>
@@ -6486,7 +6488,7 @@
         <v>99</v>
       </c>
       <c r="K79" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P79" s="6" t="b">
         <v>0</v>
@@ -6526,7 +6528,7 @@
       </c>
       <c r="AA79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Comparator</v>
+        <v>DAC</v>
       </c>
       <c r="AB79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6548,7 +6550,7 @@
     <row r="80" spans="8:31">
       <c r="H80" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - ADC</v>
+        <v>ICs - Analog - Comparator</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>100</v>
@@ -6557,35 +6559,35 @@
         <v>99</v>
       </c>
       <c r="K80" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P80" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U80" t="b">
         <v>1</v>
       </c>
-      <c r="V80" t="s">
-        <v>184</v>
+      <c r="V80" t="b">
+        <v>0</v>
       </c>
       <c r="W80">
         <v>0</v>
       </c>
       <c r="X80" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6597,7 +6599,7 @@
       </c>
       <c r="AA80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>ADC</v>
+        <v>Comparator</v>
       </c>
       <c r="AB80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6619,56 +6621,56 @@
     <row r="81" spans="8:31">
       <c r="H81" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - SiCFET</v>
+        <v>ICs - Analog - ADC</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J81" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="K81" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="P81" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S81" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="b">
         <v>1</v>
       </c>
       <c r="U81" t="b">
-        <v>0</v>
-      </c>
-      <c r="V81" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V81" t="s">
+        <v>184</v>
       </c>
       <c r="W81">
         <v>0</v>
       </c>
       <c r="X81" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y81" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z81" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA81" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SiCFET</v>
+        <v>ADC</v>
       </c>
       <c r="AB81" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6690,7 +6692,7 @@
     <row r="82" spans="8:31">
       <c r="H82" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - MOSFET</v>
+        <v>Discreet - Transistors - SiCFET</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>89</v>
@@ -6699,25 +6701,25 @@
         <v>194</v>
       </c>
       <c r="K82" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P82" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" t="b">
         <v>1</v>
       </c>
       <c r="U82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V82" t="b">
         <v>0</v>
@@ -6727,7 +6729,7 @@
       </c>
       <c r="X82" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6739,7 +6741,7 @@
       </c>
       <c r="AA82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>MOSFET</v>
+        <v>SiCFET</v>
       </c>
       <c r="AB82" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6761,7 +6763,7 @@
     <row r="83" spans="8:31">
       <c r="H83" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - JFET</v>
+        <v>Discreet - Transistors - MOSFET</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>89</v>
@@ -6770,25 +6772,25 @@
         <v>194</v>
       </c>
       <c r="K83" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P83" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S83" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83" t="b">
         <v>1</v>
       </c>
       <c r="U83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83" t="b">
         <v>0</v>
@@ -6798,7 +6800,7 @@
       </c>
       <c r="X83" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6810,7 +6812,7 @@
       </c>
       <c r="AA83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>JFET</v>
+        <v>MOSFET</v>
       </c>
       <c r="AB83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6832,7 +6834,7 @@
     <row r="84" spans="8:31">
       <c r="H84" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - GaNFET</v>
+        <v>Discreet - Transistors - JFET</v>
       </c>
       <c r="I84" s="6" t="s">
         <v>89</v>
@@ -6841,7 +6843,7 @@
         <v>194</v>
       </c>
       <c r="K84" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P84" s="6" t="b">
         <v>0</v>
@@ -6881,7 +6883,7 @@
       </c>
       <c r="AA84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>GaNFET</v>
+        <v>JFET</v>
       </c>
       <c r="AB84" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6903,7 +6905,7 @@
     <row r="85" spans="8:31">
       <c r="H85" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - BJT - PNP</v>
+        <v>Discreet - Transistors - GaNFET</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>89</v>
@@ -6912,10 +6914,7 @@
         <v>194</v>
       </c>
       <c r="K85" t="s">
-        <v>92</v>
-      </c>
-      <c r="L85" t="s">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="P85" s="6" t="b">
         <v>0</v>
@@ -6930,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="T85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85" t="b">
         <v>0</v>
@@ -6955,11 +6954,11 @@
       </c>
       <c r="AA85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">BJT - </v>
+        <v>GaNFET</v>
       </c>
       <c r="AB85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>PNP</v>
+        <v/>
       </c>
       <c r="AC85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6977,16 +6976,19 @@
     <row r="86" spans="8:31">
       <c r="H86" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Diodes - Standard</v>
+        <v>Discreet - Transistors - BJT - PNP</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J86" t="s">
-        <v>90</v>
+        <v>194</v>
       </c>
       <c r="K86" t="s">
-        <v>63</v>
+        <v>92</v>
+      </c>
+      <c r="L86" t="s">
+        <v>201</v>
       </c>
       <c r="P86" s="6" t="b">
         <v>0</v>
@@ -7001,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="T86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U86" t="b">
         <v>1</v>
@@ -7014,7 +7016,7 @@
       </c>
       <c r="X86" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -7022,15 +7024,15 @@
       </c>
       <c r="Z86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Diodes - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Standard</v>
+        <v xml:space="preserve">BJT - </v>
       </c>
       <c r="AB86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>PNP</v>
       </c>
       <c r="AC86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -7048,13 +7050,16 @@
     <row r="87" spans="8:31">
       <c r="H87" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Contacts - Ring Terminals</v>
+        <v>Discreet - Diodes - Standard</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="J87" t="s">
-        <v>77</v>
+        <v>90</v>
+      </c>
+      <c r="K87" t="s">
+        <v>63</v>
       </c>
       <c r="P87" s="6" t="b">
         <v>0</v>
@@ -7069,10 +7074,10 @@
         <v>0</v>
       </c>
       <c r="T87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V87" t="b">
         <v>0</v>
@@ -7082,19 +7087,19 @@
       </c>
       <c r="X87" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Contacts - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Ring Terminals</v>
+        <v xml:space="preserve">Diodes - </v>
       </c>
       <c r="AA87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Standard</v>
       </c>
       <c r="AB87" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7116,13 +7121,13 @@
     <row r="88" spans="8:31">
       <c r="H88" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Contacts - Ferrules</v>
+        <v>Contacts - Ring Terminals</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>75</v>
       </c>
       <c r="J88" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P88" s="6" t="b">
         <v>0</v>
@@ -7158,7 +7163,7 @@
       </c>
       <c r="Z88" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Ferrules</v>
+        <v>Ring Terminals</v>
       </c>
       <c r="AA88" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7184,13 +7189,13 @@
     <row r="89" spans="8:31">
       <c r="H89" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Contacts - Banana Plugs</v>
+        <v>Contacts - Ferrules</v>
       </c>
       <c r="I89" s="6" t="s">
         <v>75</v>
       </c>
       <c r="J89" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P89" s="6" t="b">
         <v>0</v>
@@ -7226,7 +7231,7 @@
       </c>
       <c r="Z89" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Banana Plugs</v>
+        <v>Ferrules</v>
       </c>
       <c r="AA89" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7252,49 +7257,49 @@
     <row r="90" spans="8:31">
       <c r="H90" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Test Points</v>
+        <v>Contacts - Banana Plugs</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="J90" t="s">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="P90" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U90" t="b">
-        <v>1</v>
-      </c>
-      <c r="V90" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V90" t="b">
+        <v>0</v>
       </c>
       <c r="W90">
         <v>0</v>
       </c>
       <c r="X90" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Contacts - </v>
       </c>
       <c r="Z90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Test Points</v>
+        <v>Banana Plugs</v>
       </c>
       <c r="AA90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7320,16 +7325,13 @@
     <row r="91" spans="8:31">
       <c r="H91" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Terminal Blocks - Wire to Board</v>
+        <v>Connectors - Test Points</v>
       </c>
       <c r="I91" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J91" t="s">
-        <v>61</v>
-      </c>
-      <c r="K91" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="P91" s="6" t="b">
         <v>1</v>
@@ -7365,11 +7367,11 @@
       </c>
       <c r="Z91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Terminal Blocks - </v>
+        <v>Test Points</v>
       </c>
       <c r="AA91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Wire to Board</v>
+        <v/>
       </c>
       <c r="AB91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7391,13 +7393,16 @@
     <row r="92" spans="8:31">
       <c r="H92" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - SD Card Socket</v>
+        <v>Connectors - Terminal Blocks - Wire to Board</v>
       </c>
       <c r="I92" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J92" t="s">
-        <v>56</v>
+        <v>61</v>
+      </c>
+      <c r="K92" t="s">
+        <v>215</v>
       </c>
       <c r="P92" s="6" t="b">
         <v>1</v>
@@ -7433,11 +7438,11 @@
       </c>
       <c r="Z92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>SD Card Socket</v>
+        <v xml:space="preserve">Terminal Blocks - </v>
       </c>
       <c r="AA92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Wire to Board</v>
       </c>
       <c r="AB92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -7459,41 +7464,41 @@
     <row r="93" spans="8:31">
       <c r="H93" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Screw Connectors</v>
+        <v>Connectors - SD Card Socket</v>
       </c>
       <c r="I93" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J93" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="P93" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S93" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U93" t="b">
-        <v>0</v>
-      </c>
-      <c r="V93" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V93" t="s">
+        <v>184</v>
       </c>
       <c r="W93">
         <v>0</v>
       </c>
       <c r="X93" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -7501,7 +7506,7 @@
       </c>
       <c r="Z93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Screw Connectors</v>
+        <v>SD Card Socket</v>
       </c>
       <c r="AA93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7527,13 +7532,13 @@
     <row r="94" spans="8:31">
       <c r="H94" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Power Entry Modules</v>
+        <v>Connectors - Screw Connectors</v>
       </c>
       <c r="I94" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J94" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="P94" s="6" t="b">
         <v>0</v>
@@ -7569,7 +7574,7 @@
       </c>
       <c r="Z94" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Power Entry Modules</v>
+        <v>Screw Connectors</v>
       </c>
       <c r="AA94" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7595,13 +7600,13 @@
     <row r="95" spans="8:31">
       <c r="H95" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Jumpers</v>
+        <v>Connectors - Power Entry Modules</v>
       </c>
       <c r="I95" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J95" t="s">
-        <v>187</v>
+        <v>60</v>
       </c>
       <c r="P95" s="6" t="b">
         <v>0</v>
@@ -7637,7 +7642,7 @@
       </c>
       <c r="Z95" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Jumpers</v>
+        <v>Power Entry Modules</v>
       </c>
       <c r="AA95" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7663,13 +7668,13 @@
     <row r="96" spans="8:31">
       <c r="H96" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Flat Flex</v>
+        <v>Connectors - Jumpers</v>
       </c>
       <c r="I96" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J96" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="P96" s="6" t="b">
         <v>0</v>
@@ -7681,7 +7686,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T96" t="b">
         <v>0</v>
@@ -7697,7 +7702,7 @@
       </c>
       <c r="X96" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -7705,7 +7710,7 @@
       </c>
       <c r="Z96" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Flat Flex</v>
+        <v>Jumpers</v>
       </c>
       <c r="AA96" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -7731,22 +7736,13 @@
     <row r="97" spans="8:31">
       <c r="H97" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Male - PCB Mount</v>
+        <v>Connectors - Flat Flex</v>
       </c>
       <c r="I97" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J97" t="s">
-        <v>66</v>
-      </c>
-      <c r="K97" t="s">
-        <v>63</v>
-      </c>
-      <c r="L97" t="s">
-        <v>67</v>
-      </c>
-      <c r="M97" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="P97" s="6" t="b">
         <v>0</v>
@@ -7758,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" t="b">
         <v>0</v>
@@ -7774,7 +7770,7 @@
       </c>
       <c r="X97" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -7782,19 +7778,19 @@
       </c>
       <c r="Z97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">D-Sub - </v>
+        <v>Flat Flex</v>
       </c>
       <c r="AA97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v/>
       </c>
       <c r="AB97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Male - </v>
+        <v/>
       </c>
       <c r="AC97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>PCB Mount</v>
+        <v/>
       </c>
       <c r="AD97" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -7808,7 +7804,7 @@
     <row r="98" spans="8:31">
       <c r="H98" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Male - Inline</v>
+        <v>Connectors - D-Sub - Standard - Male - PCB Mount</v>
       </c>
       <c r="I98" s="6" t="s">
         <v>34</v>
@@ -7823,27 +7819,27 @@
         <v>67</v>
       </c>
       <c r="M98" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P98" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q98" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R98" s="30" t="b">
+      <c r="Q98" t="b">
+        <v>0</v>
+      </c>
+      <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T98" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U98" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V98" s="30" t="b">
+      <c r="T98" t="b">
+        <v>0</v>
+      </c>
+      <c r="U98" t="b">
+        <v>0</v>
+      </c>
+      <c r="V98" t="b">
         <v>0</v>
       </c>
       <c r="W98">
@@ -7871,7 +7867,7 @@
       </c>
       <c r="AC98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>Inline</v>
+        <v>PCB Mount</v>
       </c>
       <c r="AD98" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -7885,7 +7881,7 @@
     <row r="99" spans="8:31">
       <c r="H99" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Female - PCB Mount</v>
+        <v>Connectors - D-Sub - Standard - Male - Inline</v>
       </c>
       <c r="I99" s="6" t="s">
         <v>34</v>
@@ -7897,30 +7893,30 @@
         <v>63</v>
       </c>
       <c r="L99" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M99" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P99" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q99" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R99" s="30" t="b">
+      <c r="Q99" t="b">
+        <v>0</v>
+      </c>
+      <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T99" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U99" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V99" s="30" t="b">
+      <c r="T99" t="b">
+        <v>0</v>
+      </c>
+      <c r="U99" t="b">
+        <v>0</v>
+      </c>
+      <c r="V99" t="b">
         <v>0</v>
       </c>
       <c r="W99">
@@ -7944,11 +7940,11 @@
       </c>
       <c r="AB99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Female - </v>
+        <v xml:space="preserve">Male - </v>
       </c>
       <c r="AC99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>PCB Mount</v>
+        <v>Inline</v>
       </c>
       <c r="AD99" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -7962,7 +7958,7 @@
     <row r="100" spans="8:31">
       <c r="H100" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Standard - Female - Inline</v>
+        <v>Connectors - D-Sub - Standard - Female - PCB Mount</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>34</v>
@@ -7977,27 +7973,27 @@
         <v>68</v>
       </c>
       <c r="M100" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P100" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q100" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R100" s="30" t="b">
+      <c r="Q100" t="b">
+        <v>0</v>
+      </c>
+      <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T100" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U100" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V100" s="30" t="b">
+      <c r="T100" t="b">
+        <v>0</v>
+      </c>
+      <c r="U100" t="b">
+        <v>0</v>
+      </c>
+      <c r="V100" t="b">
         <v>0</v>
       </c>
       <c r="W100">
@@ -8025,7 +8021,7 @@
       </c>
       <c r="AC100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v>Inline</v>
+        <v>PCB Mount</v>
       </c>
       <c r="AD100" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -8039,7 +8035,7 @@
     <row r="101" spans="8:31">
       <c r="H101" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Hybrid - Male - Inline</v>
+        <v>Connectors - D-Sub - Standard - Female - Inline</v>
       </c>
       <c r="I101" s="6" t="s">
         <v>34</v>
@@ -8048,10 +8044,10 @@
         <v>66</v>
       </c>
       <c r="K101" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L101" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M101" t="s">
         <v>70</v>
@@ -8059,22 +8055,22 @@
       <c r="P101" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q101" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R101" s="30" t="b">
+      <c r="Q101" t="b">
+        <v>0</v>
+      </c>
+      <c r="R101" t="b">
         <v>0</v>
       </c>
       <c r="S101" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T101" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U101" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V101" s="30" t="b">
+      <c r="T101" t="b">
+        <v>0</v>
+      </c>
+      <c r="U101" t="b">
+        <v>0</v>
+      </c>
+      <c r="V101" t="b">
         <v>0</v>
       </c>
       <c r="W101">
@@ -8094,11 +8090,11 @@
       </c>
       <c r="AA101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Hybrid - </v>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AB101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Male - </v>
+        <v xml:space="preserve">Female - </v>
       </c>
       <c r="AC101" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8116,7 +8112,7 @@
     <row r="102" spans="8:31">
       <c r="H102" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Hybrid - Female - Inline</v>
+        <v>Connectors - D-Sub - Hybrid - Male - Inline</v>
       </c>
       <c r="I102" s="6" t="s">
         <v>34</v>
@@ -8128,7 +8124,7 @@
         <v>64</v>
       </c>
       <c r="L102" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M102" t="s">
         <v>70</v>
@@ -8136,22 +8132,22 @@
       <c r="P102" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q102" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R102" s="30" t="b">
+      <c r="Q102" t="b">
+        <v>0</v>
+      </c>
+      <c r="R102" t="b">
         <v>0</v>
       </c>
       <c r="S102" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T102" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U102" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V102" s="30" t="b">
+      <c r="T102" t="b">
+        <v>0</v>
+      </c>
+      <c r="U102" t="b">
+        <v>0</v>
+      </c>
+      <c r="V102" t="b">
         <v>0</v>
       </c>
       <c r="W102">
@@ -8175,7 +8171,7 @@
       </c>
       <c r="AB102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v xml:space="preserve">Female - </v>
+        <v xml:space="preserve">Male - </v>
       </c>
       <c r="AC102" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8193,7 +8189,7 @@
     <row r="103" spans="8:31">
       <c r="H103" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - D-Sub - Backshells</v>
+        <v>Connectors - D-Sub - Hybrid - Female - Inline</v>
       </c>
       <c r="I103" s="6" t="s">
         <v>34</v>
@@ -8202,27 +8198,33 @@
         <v>66</v>
       </c>
       <c r="K103" t="s">
-        <v>65</v>
+        <v>64</v>
+      </c>
+      <c r="L103" t="s">
+        <v>68</v>
+      </c>
+      <c r="M103" t="s">
+        <v>70</v>
       </c>
       <c r="P103" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q103" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R103" s="30" t="b">
+      <c r="Q103" t="b">
+        <v>0</v>
+      </c>
+      <c r="R103" t="b">
         <v>0</v>
       </c>
       <c r="S103" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T103" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U103" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V103" s="30" t="b">
+      <c r="T103" t="b">
+        <v>0</v>
+      </c>
+      <c r="U103" t="b">
+        <v>0</v>
+      </c>
+      <c r="V103" t="b">
         <v>0</v>
       </c>
       <c r="W103">
@@ -8242,15 +8244,15 @@
       </c>
       <c r="AA103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Backshells</v>
+        <v xml:space="preserve">Hybrid - </v>
       </c>
       <c r="AB103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v xml:space="preserve">Female - </v>
       </c>
       <c r="AC103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
+        <v>Inline</v>
       </c>
       <c r="AD103" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
@@ -8264,33 +8266,36 @@
     <row r="104" spans="8:31">
       <c r="H104" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Coaxial</v>
+        <v>Connectors - D-Sub - Backshells</v>
       </c>
       <c r="I104" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J104" t="s">
-        <v>58</v>
+        <v>66</v>
+      </c>
+      <c r="K104" t="s">
+        <v>65</v>
       </c>
       <c r="P104" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q104" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R104" s="30" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q104" t="b">
+        <v>0</v>
+      </c>
+      <c r="R104" t="b">
+        <v>0</v>
       </c>
       <c r="S104" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T104" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U104" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V104" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T104" t="b">
+        <v>0</v>
+      </c>
+      <c r="U104" t="b">
+        <v>0</v>
+      </c>
+      <c r="V104" t="b">
         <v>0</v>
       </c>
       <c r="W104">
@@ -8298,7 +8303,7 @@
       </c>
       <c r="X104" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -8306,11 +8311,11 @@
       </c>
       <c r="Z104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Coaxial</v>
+        <v xml:space="preserve">D-Sub - </v>
       </c>
       <c r="AA104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Backshells</v>
       </c>
       <c r="AB104" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8332,33 +8337,33 @@
     <row r="105" spans="8:31">
       <c r="H105" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Card Edge</v>
+        <v>Connectors - Coaxial</v>
       </c>
       <c r="I105" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J105" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P105" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R105" s="30" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q105" t="b">
+        <v>1</v>
+      </c>
+      <c r="R105" t="b">
+        <v>1</v>
       </c>
       <c r="S105" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T105" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U105" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V105" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T105" t="b">
+        <v>1</v>
+      </c>
+      <c r="U105" t="b">
+        <v>1</v>
+      </c>
+      <c r="V105" t="b">
         <v>0</v>
       </c>
       <c r="W105">
@@ -8366,7 +8371,7 @@
       </c>
       <c r="X105" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -8374,7 +8379,7 @@
       </c>
       <c r="Z105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Card Edge</v>
+        <v>Coaxial</v>
       </c>
       <c r="AA105" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -8400,36 +8405,33 @@
     <row r="106" spans="8:31">
       <c r="H106" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Battery Holders - Cylindrical</v>
+        <v>Connectors - Card Edge</v>
       </c>
       <c r="I106" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J106" t="s">
-        <v>206</v>
-      </c>
-      <c r="K106" t="s">
-        <v>208</v>
+        <v>57</v>
       </c>
       <c r="P106" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q106" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R106" s="30" t="b">
+      <c r="Q106" t="b">
+        <v>0</v>
+      </c>
+      <c r="R106" t="b">
         <v>0</v>
       </c>
       <c r="S106" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T106" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U106" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V106" s="30" t="b">
+      <c r="T106" t="b">
+        <v>0</v>
+      </c>
+      <c r="U106" t="b">
+        <v>0</v>
+      </c>
+      <c r="V106" t="b">
         <v>0</v>
       </c>
       <c r="W106">
@@ -8445,11 +8447,11 @@
       </c>
       <c r="Z106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Battery Holders - </v>
+        <v>Card Edge</v>
       </c>
       <c r="AA106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Cylindrical</v>
+        <v/>
       </c>
       <c r="AB106" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8471,7 +8473,7 @@
     <row r="107" spans="8:31">
       <c r="H107" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Battery Holders - Coin Cell</v>
+        <v>Connectors - Battery Holders - Cylindrical</v>
       </c>
       <c r="I107" s="6" t="s">
         <v>34</v>
@@ -8480,35 +8482,35 @@
         <v>206</v>
       </c>
       <c r="K107" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P107" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q107" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R107" s="30" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q107" t="b">
+        <v>0</v>
+      </c>
+      <c r="R107" t="b">
+        <v>0</v>
       </c>
       <c r="S107" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T107" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U107" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V107" s="30" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="T107" t="b">
+        <v>0</v>
+      </c>
+      <c r="U107" t="b">
+        <v>0</v>
+      </c>
+      <c r="V107" t="b">
+        <v>0</v>
       </c>
       <c r="W107">
         <v>0</v>
       </c>
       <c r="X107" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -8520,7 +8522,7 @@
       </c>
       <c r="AA107" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Coin Cell</v>
+        <v>Cylindrical</v>
       </c>
       <c r="AB107" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8542,41 +8544,44 @@
     <row r="108" spans="8:31">
       <c r="H108" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Banana Jacks</v>
+        <v>Connectors - Battery Holders - Coin Cell</v>
       </c>
       <c r="I108" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J108" t="s">
-        <v>59</v>
+        <v>206</v>
+      </c>
+      <c r="K108" t="s">
+        <v>207</v>
       </c>
       <c r="P108" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R108" s="30" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q108" t="b">
+        <v>1</v>
+      </c>
+      <c r="R108" t="b">
+        <v>1</v>
       </c>
       <c r="S108" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T108" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U108" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V108" s="30" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T108" t="b">
+        <v>1</v>
+      </c>
+      <c r="U108" t="b">
+        <v>1</v>
+      </c>
+      <c r="V108" t="s">
+        <v>184</v>
       </c>
       <c r="W108">
         <v>0</v>
       </c>
       <c r="X108" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -8584,11 +8589,11 @@
       </c>
       <c r="Z108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Banana Jacks</v>
+        <v xml:space="preserve">Battery Holders - </v>
       </c>
       <c r="AA108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Coin Cell</v>
       </c>
       <c r="AB108" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -8610,39 +8615,33 @@
     <row r="109" spans="8:31">
       <c r="H109" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - VCOs - VCXO</v>
+        <v>Connectors - Banana Jacks</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="J109" t="s">
-        <v>124</v>
-      </c>
-      <c r="K109" t="s">
-        <v>129</v>
-      </c>
-      <c r="L109" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="P109" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q109" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R109" s="30" t="b">
+      <c r="Q109" t="b">
+        <v>0</v>
+      </c>
+      <c r="R109" t="b">
         <v>0</v>
       </c>
       <c r="S109" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T109" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U109" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V109" s="30" t="b">
+      <c r="T109" t="b">
+        <v>0</v>
+      </c>
+      <c r="U109" t="b">
+        <v>0</v>
+      </c>
+      <c r="V109" t="b">
         <v>0</v>
       </c>
       <c r="W109">
@@ -8650,23 +8649,23 @@
       </c>
       <c r="X109" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v>Banana Jacks</v>
       </c>
       <c r="AA109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">VCOs - </v>
+        <v/>
       </c>
       <c r="AB109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>VCXO</v>
+        <v/>
       </c>
       <c r="AC109" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8684,7 +8683,7 @@
     <row r="110" spans="8:31">
       <c r="H110" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - VCOs - VCTCXO</v>
+        <v>Clock&amp;Timing - Oscillators  - VCOs - VCXO</v>
       </c>
       <c r="I110" s="6" t="s">
         <v>153</v>
@@ -8696,27 +8695,27 @@
         <v>129</v>
       </c>
       <c r="L110" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P110" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q110" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R110" s="30" t="b">
+      <c r="Q110" t="b">
+        <v>0</v>
+      </c>
+      <c r="R110" t="b">
         <v>0</v>
       </c>
       <c r="S110" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="T110" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U110" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V110" s="30" t="b">
+      <c r="T110" t="b">
+        <v>1</v>
+      </c>
+      <c r="U110" t="b">
+        <v>0</v>
+      </c>
+      <c r="V110" t="b">
         <v>0</v>
       </c>
       <c r="W110">
@@ -8740,7 +8739,7 @@
       </c>
       <c r="AB110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>VCTCXO</v>
+        <v>VCXO</v>
       </c>
       <c r="AC110" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8758,7 +8757,7 @@
     <row r="111" spans="8:31">
       <c r="H111" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - VCOs - VCO</v>
+        <v>Clock&amp;Timing - Oscillators  - VCOs - VCTCXO</v>
       </c>
       <c r="I111" s="6" t="s">
         <v>153</v>
@@ -8770,7 +8769,7 @@
         <v>129</v>
       </c>
       <c r="L111" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="P111" s="6" t="b">
         <v>0</v>
@@ -8814,7 +8813,7 @@
       </c>
       <c r="AB111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>VCO</v>
+        <v>VCTCXO</v>
       </c>
       <c r="AC111" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8832,7 +8831,7 @@
     <row r="112" spans="8:31">
       <c r="H112" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - TCXO</v>
+        <v>Clock&amp;Timing - Oscillators  - VCOs - VCO</v>
       </c>
       <c r="I112" s="6" t="s">
         <v>153</v>
@@ -8841,10 +8840,10 @@
         <v>124</v>
       </c>
       <c r="K112" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L112" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="P112" s="6" t="b">
         <v>0</v>
@@ -8884,11 +8883,11 @@
       </c>
       <c r="AA112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Fixed - </v>
+        <v xml:space="preserve">VCOs - </v>
       </c>
       <c r="AB112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>TCXO</v>
+        <v>VCO</v>
       </c>
       <c r="AC112" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8906,7 +8905,7 @@
     <row r="113" spans="8:31">
       <c r="H113" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - Logic_Out</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - TCXO</v>
       </c>
       <c r="I113" s="6" t="s">
         <v>153</v>
@@ -8918,35 +8917,35 @@
         <v>125</v>
       </c>
       <c r="L113" t="s">
-        <v>205</v>
+        <v>127</v>
       </c>
       <c r="P113" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S113" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T113" t="b">
         <v>1</v>
       </c>
       <c r="U113" t="b">
-        <v>1</v>
-      </c>
-      <c r="V113" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V113" t="b">
+        <v>0</v>
       </c>
       <c r="W113">
         <v>0</v>
       </c>
       <c r="X113" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -8962,7 +8961,7 @@
       </c>
       <c r="AB113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Logic_Out</v>
+        <v>TCXO</v>
       </c>
       <c r="AC113" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -8980,7 +8979,7 @@
     <row r="114" spans="8:31">
       <c r="H114" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - Ceramic Resonator</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - Logic_Out</v>
       </c>
       <c r="I114" s="6" t="s">
         <v>153</v>
@@ -8992,35 +8991,35 @@
         <v>125</v>
       </c>
       <c r="L114" t="s">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="P114" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S114" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T114" t="b">
         <v>1</v>
       </c>
       <c r="U114" t="b">
-        <v>0</v>
-      </c>
-      <c r="V114" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V114" t="s">
+        <v>184</v>
       </c>
       <c r="W114">
         <v>0</v>
       </c>
       <c r="X114" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -9036,7 +9035,7 @@
       </c>
       <c r="AB114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Ceramic Resonator</v>
+        <v>Logic_Out</v>
       </c>
       <c r="AC114" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -9054,16 +9053,19 @@
     <row r="115" spans="8:31">
       <c r="H115" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - ICs - DDS</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - Ceramic Resonator</v>
       </c>
       <c r="I115" s="6" t="s">
         <v>153</v>
       </c>
       <c r="J115" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="K115" t="s">
-        <v>123</v>
+        <v>125</v>
+      </c>
+      <c r="L115" t="s">
+        <v>128</v>
       </c>
       <c r="P115" s="6" t="b">
         <v>0</v>
@@ -9078,10 +9080,10 @@
         <v>0</v>
       </c>
       <c r="T115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V115" t="b">
         <v>0</v>
@@ -9099,15 +9101,15 @@
       </c>
       <c r="Z115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DDS</v>
+        <v xml:space="preserve">Fixed - </v>
       </c>
       <c r="AB115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Ceramic Resonator</v>
       </c>
       <c r="AC115" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -9125,53 +9127,56 @@
     <row r="116" spans="8:31">
       <c r="H116" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Capacitors - Polarized</v>
+        <v>Clock&amp;Timing - ICs - DDS</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>27</v>
+        <v>153</v>
       </c>
       <c r="J116" t="s">
-        <v>28</v>
+        <v>100</v>
+      </c>
+      <c r="K116" t="s">
+        <v>123</v>
       </c>
       <c r="P116" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S116" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T116" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U116" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V116" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="T116" t="b">
+        <v>0</v>
+      </c>
+      <c r="U116" t="b">
+        <v>1</v>
+      </c>
+      <c r="V116" t="b">
+        <v>0</v>
       </c>
       <c r="W116">
         <v>0</v>
       </c>
       <c r="X116" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Capacitors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Polarized</v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="AA116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>DDS</v>
       </c>
       <c r="AB116" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9193,13 +9198,13 @@
     <row r="117" spans="8:31">
       <c r="H117" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Voltage References - Burried Zener</v>
+        <v>Capacitors - Polarized</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="J117" t="s">
-        <v>186</v>
+        <v>28</v>
       </c>
       <c r="P117" s="6" t="b">
         <v>1</v>
@@ -9219,23 +9224,23 @@
       <c r="U117" t="b">
         <v>1</v>
       </c>
-      <c r="V117" t="b">
-        <v>1</v>
+      <c r="V117" t="s">
+        <v>184</v>
       </c>
       <c r="W117">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X117" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>100</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y117" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Voltage References - </v>
+        <v xml:space="preserve">Capacitors - </v>
       </c>
       <c r="Z117" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Burried Zener</v>
+        <v>Polarized</v>
       </c>
       <c r="AA117" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9261,13 +9266,13 @@
     <row r="118" spans="8:31">
       <c r="H118" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Pads</v>
+        <v>Voltage References - Burried Zener</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>45</v>
+        <v>185</v>
       </c>
       <c r="J118" t="s">
-        <v>47</v>
+        <v>186</v>
       </c>
       <c r="P118" s="6" t="b">
         <v>1</v>
@@ -9299,11 +9304,11 @@
       </c>
       <c r="Y118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Thermal - </v>
+        <v xml:space="preserve">Voltage References - </v>
       </c>
       <c r="Z118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Pads</v>
+        <v>Burried Zener</v>
       </c>
       <c r="AA118" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9329,13 +9334,13 @@
     <row r="119" spans="8:31">
       <c r="H119" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Thermal - Heat Sinks</v>
+        <v>Thermal - Pads</v>
       </c>
       <c r="I119" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J119" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P119" s="6" t="b">
         <v>1</v>
@@ -9371,7 +9376,7 @@
       </c>
       <c r="Z119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Heat Sinks</v>
+        <v>Pads</v>
       </c>
       <c r="AA119" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9397,13 +9402,13 @@
     <row r="120" spans="8:31">
       <c r="H120" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Switches - Tactile</v>
+        <v>Thermal - Heat Sinks</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="J120" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="P120" s="6" t="b">
         <v>1</v>
@@ -9435,11 +9440,11 @@
       </c>
       <c r="Y120" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Switches - </v>
+        <v xml:space="preserve">Thermal - </v>
       </c>
       <c r="Z120" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Tactile</v>
+        <v>Heat Sinks</v>
       </c>
       <c r="AA120" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9465,13 +9470,13 @@
     <row r="121" spans="8:31">
       <c r="H121" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Switches - Slide</v>
+        <v>Switches - Tactile</v>
       </c>
       <c r="I121" s="6" t="s">
         <v>181</v>
       </c>
       <c r="J121" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="P121" s="6" t="b">
         <v>1</v>
@@ -9507,7 +9512,7 @@
       </c>
       <c r="Z121" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Slide</v>
+        <v>Tactile</v>
       </c>
       <c r="AA121" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9533,13 +9538,13 @@
     <row r="122" spans="8:31">
       <c r="H122" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Switches - Push</v>
+        <v>Switches - Slide</v>
       </c>
       <c r="I122" s="6" t="s">
         <v>181</v>
       </c>
       <c r="J122" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="b">
         <v>1</v>
@@ -9575,7 +9580,7 @@
       </c>
       <c r="Z122" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Push</v>
+        <v>Slide</v>
       </c>
       <c r="AA122" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9601,16 +9606,13 @@
     <row r="123" spans="8:31">
       <c r="H123" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Single - SMD</v>
+        <v>Switches - Push</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>42</v>
+        <v>181</v>
       </c>
       <c r="J123" t="s">
-        <v>43</v>
-      </c>
-      <c r="K123" t="s">
-        <v>44</v>
+        <v>203</v>
       </c>
       <c r="P123" s="6" t="b">
         <v>1</v>
@@ -9642,15 +9644,15 @@
       </c>
       <c r="Y123" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Resistors - </v>
+        <v xml:space="preserve">Switches - </v>
       </c>
       <c r="Z123" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Single - </v>
+        <v>Push</v>
       </c>
       <c r="AA123" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SMD</v>
+        <v/>
       </c>
       <c r="AB123" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9672,13 +9674,16 @@
     <row r="124" spans="8:31">
       <c r="H124" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Resistors - Isolated Array</v>
+        <v>Resistors - Single - SMD</v>
       </c>
       <c r="I124" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J124" t="s">
-        <v>50</v>
+        <v>43</v>
+      </c>
+      <c r="K124" t="s">
+        <v>44</v>
       </c>
       <c r="P124" s="6" t="b">
         <v>1</v>
@@ -9714,11 +9719,11 @@
       </c>
       <c r="Z124" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Isolated Array</v>
+        <v xml:space="preserve">Single - </v>
       </c>
       <c r="AA124" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>SMD</v>
       </c>
       <c r="AB124" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -9740,13 +9745,13 @@
     <row r="125" spans="8:31">
       <c r="H125" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - Wall Wart</v>
+        <v>Resistors - Isolated Array</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="J125" t="s">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="P125" s="6" t="b">
         <v>1</v>
@@ -9778,11 +9783,11 @@
       </c>
       <c r="Y125" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">PSUs - </v>
+        <v xml:space="preserve">Resistors - </v>
       </c>
       <c r="Z125" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Wall Wart</v>
+        <v>Isolated Array</v>
       </c>
       <c r="AA125" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -9808,39 +9813,33 @@
     <row r="126" spans="8:31">
       <c r="H126" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>PSUs - PCB Mount - DC-DC - Non-Isolated</v>
+        <v>PSUs - Wall Wart</v>
       </c>
       <c r="I126" s="6" t="s">
         <v>81</v>
       </c>
       <c r="J126" t="s">
-        <v>69</v>
-      </c>
-      <c r="K126" t="s">
-        <v>83</v>
-      </c>
-      <c r="L126" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="P126" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q126" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R126" s="30" t="b">
+      <c r="Q126" t="b">
+        <v>1</v>
+      </c>
+      <c r="R126" t="b">
         <v>1</v>
       </c>
       <c r="S126" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T126" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U126" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V126" s="30" t="b">
+      <c r="T126" t="b">
+        <v>1</v>
+      </c>
+      <c r="U126" t="b">
+        <v>1</v>
+      </c>
+      <c r="V126" t="b">
         <v>1</v>
       </c>
       <c r="W126">
@@ -9856,15 +9855,15 @@
       </c>
       <c r="Z126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">PCB Mount - </v>
+        <v>Wall Wart</v>
       </c>
       <c r="AA126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">DC-DC - </v>
+        <v/>
       </c>
       <c r="AB126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Non-Isolated</v>
+        <v/>
       </c>
       <c r="AC126" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -9882,33 +9881,39 @@
     <row r="127" spans="8:31">
       <c r="H127" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - TVS Diode</v>
+        <v>PSUs - PCB Mount - DC-DC - Non-Isolated</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="J127" t="s">
-        <v>79</v>
+        <v>69</v>
+      </c>
+      <c r="K127" t="s">
+        <v>83</v>
+      </c>
+      <c r="L127" t="s">
+        <v>85</v>
       </c>
       <c r="P127" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q127" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R127" s="30" t="b">
+      <c r="Q127" t="b">
+        <v>1</v>
+      </c>
+      <c r="R127" t="b">
         <v>1</v>
       </c>
       <c r="S127" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T127" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U127" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V127" s="30" t="b">
+      <c r="T127" t="b">
+        <v>1</v>
+      </c>
+      <c r="U127" t="b">
+        <v>1</v>
+      </c>
+      <c r="V127" t="b">
         <v>1</v>
       </c>
       <c r="W127">
@@ -9920,19 +9925,19 @@
       </c>
       <c r="Y127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Protection - </v>
+        <v xml:space="preserve">PSUs - </v>
       </c>
       <c r="Z127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>TVS Diode</v>
+        <v xml:space="preserve">PCB Mount - </v>
       </c>
       <c r="AA127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">DC-DC - </v>
       </c>
       <c r="AB127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Non-Isolated</v>
       </c>
       <c r="AC127" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -9950,33 +9955,33 @@
     <row r="128" spans="8:31">
       <c r="H128" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - MOVs</v>
+        <v>Protection - TVS Diode</v>
       </c>
       <c r="I128" s="6" t="s">
         <v>38</v>
       </c>
       <c r="J128" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="P128" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q128" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R128" s="30" t="b">
+      <c r="Q128" t="b">
+        <v>1</v>
+      </c>
+      <c r="R128" t="b">
         <v>1</v>
       </c>
       <c r="S128" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T128" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U128" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V128" s="30" t="b">
+      <c r="T128" t="b">
+        <v>1</v>
+      </c>
+      <c r="U128" t="b">
+        <v>1</v>
+      </c>
+      <c r="V128" t="b">
         <v>1</v>
       </c>
       <c r="W128">
@@ -9992,7 +9997,7 @@
       </c>
       <c r="Z128" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>MOVs</v>
+        <v>TVS Diode</v>
       </c>
       <c r="AA128" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10018,33 +10023,33 @@
     <row r="129" spans="8:31">
       <c r="H129" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - GDT</v>
+        <v>Protection - MOVs</v>
       </c>
       <c r="I129" s="6" t="s">
         <v>38</v>
       </c>
       <c r="J129" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P129" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q129" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R129" s="30" t="b">
+      <c r="Q129" t="b">
+        <v>1</v>
+      </c>
+      <c r="R129" t="b">
         <v>1</v>
       </c>
       <c r="S129" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T129" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U129" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V129" s="30" t="b">
+      <c r="T129" t="b">
+        <v>1</v>
+      </c>
+      <c r="U129" t="b">
+        <v>1</v>
+      </c>
+      <c r="V129" t="b">
         <v>1</v>
       </c>
       <c r="W129">
@@ -10060,7 +10065,7 @@
       </c>
       <c r="Z129" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>GDT</v>
+        <v>MOVs</v>
       </c>
       <c r="AA129" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10086,33 +10091,33 @@
     <row r="130" spans="8:31">
       <c r="H130" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Protection - Fuses</v>
+        <v>Protection - GDT</v>
       </c>
       <c r="I130" s="6" t="s">
         <v>38</v>
       </c>
       <c r="J130" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P130" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q130" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R130" s="30" t="b">
+      <c r="Q130" t="b">
+        <v>1</v>
+      </c>
+      <c r="R130" t="b">
         <v>1</v>
       </c>
       <c r="S130" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T130" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U130" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V130" s="30" t="b">
+      <c r="T130" t="b">
+        <v>1</v>
+      </c>
+      <c r="U130" t="b">
+        <v>1</v>
+      </c>
+      <c r="V130" t="b">
         <v>1</v>
       </c>
       <c r="W130">
@@ -10128,7 +10133,7 @@
       </c>
       <c r="Z130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Fuses</v>
+        <v>GDT</v>
       </c>
       <c r="AA130" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10154,33 +10159,33 @@
     <row r="131" spans="8:31">
       <c r="H131" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Screws</v>
+        <v>Protection - Fuses</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="J131" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="P131" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q131" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R131" s="30" t="b">
+      <c r="Q131" t="b">
+        <v>1</v>
+      </c>
+      <c r="R131" t="b">
         <v>1</v>
       </c>
       <c r="S131" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T131" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U131" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V131" s="30" t="b">
+      <c r="T131" t="b">
+        <v>1</v>
+      </c>
+      <c r="U131" t="b">
+        <v>1</v>
+      </c>
+      <c r="V131" t="b">
         <v>1</v>
       </c>
       <c r="W131">
@@ -10192,11 +10197,11 @@
       </c>
       <c r="Y131" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Mechanical  - </v>
+        <v xml:space="preserve">Protection - </v>
       </c>
       <c r="Z131" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Screws</v>
+        <v>Fuses</v>
       </c>
       <c r="AA131" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10222,33 +10227,33 @@
     <row r="132" spans="8:31">
       <c r="H132" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Mechanical  - Feet</v>
+        <v>Mechanical  - Screws</v>
       </c>
       <c r="I132" s="6" t="s">
         <v>133</v>
       </c>
       <c r="J132" t="s">
-        <v>197</v>
+        <v>136</v>
       </c>
       <c r="P132" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q132" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R132" s="30" t="b">
+      <c r="Q132" t="b">
+        <v>1</v>
+      </c>
+      <c r="R132" t="b">
         <v>1</v>
       </c>
       <c r="S132" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T132" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U132" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V132" s="30" t="b">
+      <c r="T132" t="b">
+        <v>1</v>
+      </c>
+      <c r="U132" t="b">
+        <v>1</v>
+      </c>
+      <c r="V132" t="b">
         <v>1</v>
       </c>
       <c r="W132">
@@ -10264,7 +10269,7 @@
       </c>
       <c r="Z132" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Feet</v>
+        <v>Screws</v>
       </c>
       <c r="AA132" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10290,19 +10295,13 @@
     <row r="133" spans="8:31">
       <c r="H133" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>LEDs - Standard - Indicator - Through Hole</v>
+        <v>Mechanical  - Feet</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="J133" t="s">
-        <v>63</v>
-      </c>
-      <c r="K133" t="s">
-        <v>151</v>
-      </c>
-      <c r="L133" t="s">
-        <v>52</v>
+        <v>197</v>
       </c>
       <c r="P133" s="6" t="b">
         <v>1</v>
@@ -10334,19 +10333,19 @@
       </c>
       <c r="Y133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">LEDs - </v>
+        <v xml:space="preserve">Mechanical  - </v>
       </c>
       <c r="Z133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Standard - </v>
+        <v>Feet</v>
       </c>
       <c r="AA133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Indicator - </v>
+        <v/>
       </c>
       <c r="AB133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Through Hole</v>
+        <v/>
       </c>
       <c r="AC133" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10364,7 +10363,7 @@
     <row r="134" spans="8:31">
       <c r="H134" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>LEDs - Standard - Indicator - SMD</v>
+        <v>LEDs - Standard - Indicator - Through Hole</v>
       </c>
       <c r="I134" s="6" t="s">
         <v>152</v>
@@ -10376,7 +10375,7 @@
         <v>151</v>
       </c>
       <c r="L134" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="P134" s="6" t="b">
         <v>1</v>
@@ -10420,7 +10419,7 @@
       </c>
       <c r="AB134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SMD</v>
+        <v>Through Hole</v>
       </c>
       <c r="AC134" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10438,13 +10437,19 @@
     <row r="135" spans="8:31">
       <c r="H135" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Inductors - Ferrite Bead</v>
+        <v>LEDs - Standard - Indicator - SMD</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>37</v>
+        <v>152</v>
       </c>
       <c r="J135" t="s">
-        <v>202</v>
+        <v>63</v>
+      </c>
+      <c r="K135" t="s">
+        <v>151</v>
+      </c>
+      <c r="L135" t="s">
+        <v>44</v>
       </c>
       <c r="P135" s="6" t="b">
         <v>1</v>
@@ -10476,19 +10481,19 @@
       </c>
       <c r="Y135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Inductors - </v>
+        <v xml:space="preserve">LEDs - </v>
       </c>
       <c r="Z135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Ferrite Bead</v>
+        <v xml:space="preserve">Standard - </v>
       </c>
       <c r="AA135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v xml:space="preserve">Indicator - </v>
       </c>
       <c r="AB135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>SMD</v>
       </c>
       <c r="AC135" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10506,11 +10511,14 @@
     <row r="136" spans="8:31">
       <c r="H136" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Inductors</v>
+        <v>Inductors - Ferrite Bead</v>
       </c>
       <c r="I136" s="6" t="s">
         <v>37</v>
       </c>
+      <c r="J136" t="s">
+        <v>202</v>
+      </c>
       <c r="P136" s="6" t="b">
         <v>1</v>
       </c>
@@ -10541,11 +10549,11 @@
       </c>
       <c r="Y136" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v>Inductors</v>
+        <v xml:space="preserve">Inductors - </v>
       </c>
       <c r="Z136" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v/>
+        <v>Ferrite Bead</v>
       </c>
       <c r="AA136" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -10571,16 +10579,10 @@
     <row r="137" spans="8:31">
       <c r="H137" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Linear Regulation</v>
+        <v>Inductors</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J137" t="s">
-        <v>88</v>
-      </c>
-      <c r="K137" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="P137" s="6" t="b">
         <v>1</v>
@@ -10612,15 +10614,15 @@
       </c>
       <c r="Y137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v>Inductors</v>
       </c>
       <c r="Z137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v/>
       </c>
       <c r="AA137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Linear Regulation</v>
+        <v/>
       </c>
       <c r="AB137" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10642,7 +10644,7 @@
     <row r="138" spans="8:31">
       <c r="H138" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Ideal Diodes</v>
+        <v>ICs - Power - Linear Regulation</v>
       </c>
       <c r="I138" s="6" t="s">
         <v>100</v>
@@ -10651,7 +10653,7 @@
         <v>88</v>
       </c>
       <c r="K138" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P138" s="6" t="b">
         <v>1</v>
@@ -10691,7 +10693,7 @@
       </c>
       <c r="AA138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Ideal Diodes</v>
+        <v>Linear Regulation</v>
       </c>
       <c r="AB138" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10713,19 +10715,16 @@
     <row r="139" spans="8:31">
       <c r="H139" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - MCU - Module</v>
+        <v>ICs - Power - Ideal Diodes</v>
       </c>
       <c r="I139" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J139" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="K139" t="s">
-        <v>107</v>
-      </c>
-      <c r="L139" t="s">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="P139" s="6" t="b">
         <v>1</v>
@@ -10761,15 +10760,15 @@
       </c>
       <c r="Z139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">MCU - </v>
+        <v>Ideal Diodes</v>
       </c>
       <c r="AB139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Module</v>
+        <v/>
       </c>
       <c r="AC139" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10787,7 +10786,7 @@
     <row r="140" spans="8:31">
       <c r="H140" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - MCU</v>
+        <v>ICs - Embedded - MCU - Module</v>
       </c>
       <c r="I140" s="6" t="s">
         <v>100</v>
@@ -10798,6 +10797,9 @@
       <c r="K140" t="s">
         <v>107</v>
       </c>
+      <c r="L140" t="s">
+        <v>188</v>
+      </c>
       <c r="P140" s="6" t="b">
         <v>1</v>
       </c>
@@ -10836,11 +10838,11 @@
       </c>
       <c r="AA140" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>MCU</v>
+        <v xml:space="preserve">MCU - </v>
       </c>
       <c r="AB140" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Module</v>
       </c>
       <c r="AC140" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -10858,16 +10860,16 @@
     <row r="141" spans="8:31">
       <c r="H141" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - OP Amp</v>
+        <v>ICs - Embedded - MCU</v>
       </c>
       <c r="I141" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J141" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K141" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="P141" s="6" t="b">
         <v>1</v>
@@ -10903,11 +10905,11 @@
       </c>
       <c r="Z141" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v xml:space="preserve">Embedded - </v>
       </c>
       <c r="AA141" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>OP Amp</v>
+        <v>MCU</v>
       </c>
       <c r="AB141" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -10929,19 +10931,16 @@
     <row r="142" spans="8:31">
       <c r="H142" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - BJT - NPN</v>
+        <v>ICs - Analog - OP Amp</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J142" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="K142" t="s">
-        <v>92</v>
-      </c>
-      <c r="L142" t="s">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="P142" s="6" t="b">
         <v>1</v>
@@ -10973,19 +10972,19 @@
       </c>
       <c r="Y142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">BJT - </v>
+        <v>OP Amp</v>
       </c>
       <c r="AB142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>NPN</v>
+        <v/>
       </c>
       <c r="AC142" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -11003,16 +11002,19 @@
     <row r="143" spans="8:31">
       <c r="H143" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Diodes - Schottky</v>
+        <v>Discreet - Transistors - BJT - NPN</v>
       </c>
       <c r="I143" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J143" t="s">
-        <v>90</v>
+        <v>194</v>
       </c>
       <c r="K143" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="L143" t="s">
+        <v>200</v>
       </c>
       <c r="P143" s="6" t="b">
         <v>1</v>
@@ -11048,15 +11050,15 @@
       </c>
       <c r="Z143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Diodes - </v>
+        <v xml:space="preserve">Transistors - </v>
       </c>
       <c r="AA143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Schottky</v>
+        <v xml:space="preserve">BJT - </v>
       </c>
       <c r="AB143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>NPN</v>
       </c>
       <c r="AC143" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -11074,13 +11076,16 @@
     <row r="144" spans="8:31">
       <c r="H144" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - USB</v>
+        <v>Discreet - Diodes - Schottky</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="J144" t="s">
-        <v>54</v>
+        <v>90</v>
+      </c>
+      <c r="K144" t="s">
+        <v>91</v>
       </c>
       <c r="P144" s="6" t="b">
         <v>1</v>
@@ -11112,15 +11117,15 @@
       </c>
       <c r="Y144" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
+        <v xml:space="preserve">Discreet - </v>
       </c>
       <c r="Z144" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>USB</v>
+        <v xml:space="preserve">Diodes - </v>
       </c>
       <c r="AA144" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Schottky</v>
       </c>
       <c r="AB144" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -11142,13 +11147,13 @@
     <row r="145" spans="8:31">
       <c r="H145" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - RJ</v>
+        <v>Connectors - USB</v>
       </c>
       <c r="I145" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J145" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="P145" s="6" t="b">
         <v>1</v>
@@ -11184,7 +11189,7 @@
       </c>
       <c r="Z145" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>RJ</v>
+        <v>USB</v>
       </c>
       <c r="AA145" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11210,13 +11215,13 @@
     <row r="146" spans="8:31">
       <c r="H146" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Rectangular</v>
+        <v>Connectors - RJ</v>
       </c>
       <c r="I146" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J146" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P146" s="6" t="b">
         <v>1</v>
@@ -11252,7 +11257,7 @@
       </c>
       <c r="Z146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Rectangular</v>
+        <v>RJ</v>
       </c>
       <c r="AA146" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11278,13 +11283,13 @@
     <row r="147" spans="8:31">
       <c r="H147" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Programming</v>
+        <v>Connectors - Rectangular</v>
       </c>
       <c r="I147" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J147" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="P147" s="6" t="b">
         <v>1</v>
@@ -11320,7 +11325,7 @@
       </c>
       <c r="Z147" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Programming</v>
+        <v>Rectangular</v>
       </c>
       <c r="AA147" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11346,16 +11351,13 @@
     <row r="148" spans="8:31">
       <c r="H148" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Pads - Through Hole</v>
+        <v>Connectors - Programming</v>
       </c>
       <c r="I148" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J148" t="s">
-        <v>47</v>
-      </c>
-      <c r="K148" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="P148" s="6" t="b">
         <v>1</v>
@@ -11391,11 +11393,11 @@
       </c>
       <c r="Z148" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Pads - </v>
+        <v>Programming</v>
       </c>
       <c r="AA148" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Through Hole</v>
+        <v/>
       </c>
       <c r="AB148" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -11417,7 +11419,7 @@
     <row r="149" spans="8:31">
       <c r="H149" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Pads - SMD</v>
+        <v>Connectors - Pads - Through Hole</v>
       </c>
       <c r="I149" s="6" t="s">
         <v>34</v>
@@ -11426,7 +11428,7 @@
         <v>47</v>
       </c>
       <c r="K149" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="P149" s="6" t="b">
         <v>1</v>
@@ -11466,7 +11468,7 @@
       </c>
       <c r="AA149" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SMD</v>
+        <v>Through Hole</v>
       </c>
       <c r="AB149" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -11488,13 +11490,16 @@
     <row r="150" spans="8:31">
       <c r="H150" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Mezzanine</v>
+        <v>Connectors - Pads - SMD</v>
       </c>
       <c r="I150" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J150" t="s">
-        <v>179</v>
+        <v>47</v>
+      </c>
+      <c r="K150" t="s">
+        <v>44</v>
       </c>
       <c r="P150" s="6" t="b">
         <v>1</v>
@@ -11530,11 +11535,11 @@
       </c>
       <c r="Z150" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Mezzanine</v>
+        <v xml:space="preserve">Pads - </v>
       </c>
       <c r="AA150" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>SMD</v>
       </c>
       <c r="AB150" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -11556,13 +11561,13 @@
     <row r="151" spans="8:31">
       <c r="H151" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - IC socket</v>
+        <v>Connectors - Mezzanine</v>
       </c>
       <c r="I151" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J151" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="P151" s="6" t="b">
         <v>1</v>
@@ -11598,7 +11603,7 @@
       </c>
       <c r="Z151" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>IC socket</v>
+        <v>Mezzanine</v>
       </c>
       <c r="AA151" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11624,33 +11629,33 @@
     <row r="152" spans="8:31">
       <c r="H152" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Barrel Jack</v>
+        <v>Connectors - IC socket</v>
       </c>
       <c r="I152" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J152" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="P152" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q152" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R152" s="30" t="b">
+      <c r="Q152" t="b">
+        <v>1</v>
+      </c>
+      <c r="R152" t="b">
         <v>1</v>
       </c>
       <c r="S152" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="T152" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U152" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V152" s="30" t="b">
+      <c r="T152" t="b">
+        <v>1</v>
+      </c>
+      <c r="U152" t="b">
+        <v>1</v>
+      </c>
+      <c r="V152" t="b">
         <v>1</v>
       </c>
       <c r="W152">
@@ -11666,7 +11671,7 @@
       </c>
       <c r="Z152" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Barrel Jack</v>
+        <v>IC socket</v>
       </c>
       <c r="AA152" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
@@ -11692,19 +11697,13 @@
     <row r="153" spans="8:31">
       <c r="H153" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - Oscillators  - Fixed - XO</v>
+        <v>Connectors - Barrel Jack</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="J153" t="s">
-        <v>124</v>
-      </c>
-      <c r="K153" t="s">
-        <v>125</v>
-      </c>
-      <c r="L153" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="P153" s="6" t="b">
         <v>1</v>
@@ -11736,19 +11735,19 @@
       </c>
       <c r="Y153" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Clock&amp;Timing - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z153" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Oscillators  - </v>
+        <v>Barrel Jack</v>
       </c>
       <c r="AA153" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Fixed - </v>
+        <v/>
       </c>
       <c r="AB153" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>XO</v>
+        <v/>
       </c>
       <c r="AC153" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -11766,16 +11765,19 @@
     <row r="154" spans="8:31">
       <c r="H154" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Clock&amp;Timing - ICs - Generators &amp; Synthisizers</v>
+        <v>Clock&amp;Timing - Oscillators  - Fixed - XO</v>
       </c>
       <c r="I154" s="6" t="s">
         <v>153</v>
       </c>
       <c r="J154" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="K154" t="s">
-        <v>140</v>
+        <v>125</v>
+      </c>
+      <c r="L154" t="s">
+        <v>126</v>
       </c>
       <c r="P154" s="6" t="b">
         <v>1</v>
@@ -11811,15 +11813,15 @@
       </c>
       <c r="Z154" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">ICs - </v>
+        <v xml:space="preserve">Oscillators  - </v>
       </c>
       <c r="AA154" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Generators &amp; Synthisizers</v>
+        <v xml:space="preserve">Fixed - </v>
       </c>
       <c r="AB154" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>XO</v>
       </c>
       <c r="AC154" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -11837,13 +11839,16 @@
     <row r="155" spans="8:31">
       <c r="H155" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Capacitors - Unpolarized</v>
+        <v>Clock&amp;Timing - ICs - Generators &amp; Synthisizers</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>27</v>
+        <v>153</v>
       </c>
       <c r="J155" t="s">
-        <v>33</v>
+        <v>100</v>
+      </c>
+      <c r="K155" t="s">
+        <v>140</v>
       </c>
       <c r="P155" s="6" t="b">
         <v>1</v>
@@ -11875,15 +11880,15 @@
       </c>
       <c r="Y155" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Capacitors - </v>
+        <v xml:space="preserve">Clock&amp;Timing - </v>
       </c>
       <c r="Z155" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Unpolarized</v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="AA155" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Generators &amp; Synthisizers</v>
       </c>
       <c r="AB155" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -11905,13 +11910,13 @@
     <row r="156" spans="8:31">
       <c r="H156" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Cables - Premade</v>
+        <v>Capacitors - Unpolarized</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J156" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P156" s="6" t="b">
         <v>1</v>
@@ -11943,29 +11948,97 @@
       </c>
       <c r="Y156" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Capacitors - </v>
+      </c>
+      <c r="Z156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v>Unpolarized</v>
+      </c>
+      <c r="AA156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE156" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="8:31">
+      <c r="H157" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Cables - Premade</v>
+      </c>
+      <c r="I157" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J157" t="s">
+        <v>31</v>
+      </c>
+      <c r="P157" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q157" t="b">
+        <v>1</v>
+      </c>
+      <c r="R157" t="b">
+        <v>1</v>
+      </c>
+      <c r="S157" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T157" t="b">
+        <v>1</v>
+      </c>
+      <c r="U157" t="b">
+        <v>1</v>
+      </c>
+      <c r="V157" t="b">
+        <v>1</v>
+      </c>
+      <c r="W157">
+        <v>-1</v>
+      </c>
+      <c r="X157" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>100</v>
+      </c>
+      <c r="Y157" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Cables - </v>
       </c>
-      <c r="Z156" t="str">
+      <c r="Z157" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Premade</v>
       </c>
-      <c r="AA156" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB156" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC156" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD156" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE156" t="str">
+      <c r="AA157" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB157" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC157" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD157" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE157" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
         <v/>
       </c>
@@ -11988,7 +12061,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H156">
+  <conditionalFormatting sqref="H12:H157">
     <cfRule type="expression" dxfId="4" priority="2">
       <formula>IF($W12 = -1, 1, 0)</formula>
     </cfRule>
@@ -11998,7 +12071,7 @@
       <formula>IF($W12 &gt;= $E$18, 1, 0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P12:V156">
+  <conditionalFormatting sqref="P12:V157">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="TRALSE">
       <formula>NOT(ISERROR(SEARCH("TRALSE",P12)))</formula>
     </cfRule>
@@ -12012,7 +12085,7 @@
       <formula>NOT(ISERROR(SEARCH("TRUE",P12)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W12:W156">
+  <conditionalFormatting sqref="W12:W157">
     <cfRule type="cellIs" priority="77" stopIfTrue="1" operator="equal">
       <formula>-1</formula>
     </cfRule>
@@ -12025,7 +12098,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X12:X156">
+  <conditionalFormatting sqref="X12:X157">
     <cfRule type="expression" priority="9" stopIfTrue="1">
       <formula>IF(COUNTA(P12:W12)&gt;0,0,1)</formula>
     </cfRule>
